--- a/card_design.xlsx
+++ b/card_design.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\life\board_game\project_six_dynasty\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9A12994-8786-43E8-B134-732766E17B06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3802D31B-3439-4055-81A7-D42DBA793E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="811" xr2:uid="{F283CFD4-9FFB-4A79-AF0F-7443CC209F7A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1061" uniqueCount="511">
   <si>
     <t>归属</t>
   </si>
@@ -335,10 +335,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>主动：1军力，弃1张手牌，然后摸1张手牌。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>刘牢之</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -527,10 +523,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>仅限东晋玩家打出。[僭越]重洗当前君主牌，并根据牌面描述重置司马家威望，获得1威望，然后存档此牌。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>幕僚-名将</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -781,10 +773,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>安逸</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>清君侧</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -972,10 +960,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>仅限东晋玩家打出。获得7军力。存档此牌。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>璇玑图</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -984,10 +968,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>仅限北方玩家打出。获得7军力。存档此牌。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>凿壁偷光</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1116,10 +1096,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>弃置任意数量的手牌，然后摸弃置数量+1的手牌。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>大阅户人</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1156,10 +1132,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>整顿军队</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>主动：1军力。被动：每次[进军]后，获得1vp。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1180,10 +1152,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>主动：弃置1张朝堂区的[流民]，然后补充1张牌到朝堂区，获得1军力。登场：先动值5。转化[京口][广陵]。获得1功绩和1威望。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>主动：选择1项：弃1张手牌，然后摸1张牌；或者弃置1张候选策略牌，然后补充1张牌到朝堂区。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1228,10 +1196,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>3军力。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>阳骛</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1288,10 +1252,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>仅限东晋玩家打出。选择1个东晋玩家，降低1级顺位，然后存档此牌。[僭越]额外降低1级顺位。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>控制[西凉]时，可以打出。存档此牌。将部队储备区的2个部队放回游戏盒中。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1300,14 +1260,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>仅限东晋玩家打出。支付7军力。选择威望、功绩或者顺位，提高1级，其他所有东晋玩家降低1级。[僭越]司马家威望降低1级，获得4vp。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>仅限东晋玩家打出。降低1点[威望]或[功绩]，转化1个司马家地点。[僭越]可以转化1个东晋玩家地点。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>摸2张牌，然后存档此牌。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1320,22 +1272,10 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>主动：弃1张手牌，然后摸1张牌，免费执行1次[占据]。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>主动：选择1项：摸2张手牌，然后弃2张手牌；或者弃置2张候选策略牌，然后补充2张牌到朝堂区</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>在本国弃牌区放置1张[流民]。转化1个非[江南][荆襄]区域的中立地点。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>仅限东晋玩家打出。转化[太原][平阳]，然后存档此牌。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>行动：2军力2vp，然后补充1张牌到朝堂区。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1356,10 +1296,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>行动：2军力。从东晋面板获得[北伐]标记。被动：[北伐]不能被存档或征发。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>总督区</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1368,10 +1304,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>主动：支付2军力，提高1级顺位等级。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>被动：每当任意玩家打出[艺术]牌或执行[艺术]策略时，获得2vp。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1404,10 +1336,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>行动：2军力，存档此牌。被动：此牌在朝堂区中时，北方和晋玩家不能相互使用[进军]。仅限北方玩家打出。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>传播1次文化，获得2vp。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1432,10 +1360,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>主动：从展示区获得1张[文化]牌。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>检索2次[策略]，然后存档此牌。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1444,10 +1368,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>主动：征发1张[军事]候选策略牌。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>强制：选择1个[玄学]区域的地点，转为中立控制。摸1张牌。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1488,22 +1408,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>儒学贡献超过5，且儒学区域最多</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>玄学贡献超过5，且玄学区域最多</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>佛学贡献超过5，且佛学区域最多</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>仅限东晋玩家打出。占据[洛阳]时，可以打出。存档此牌。[僭越]交换东晋首都和洛阳的部队。获得1[威望]。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>友方控制[巴蜀]时，可以打出。存档此牌，传播1次[儒学]。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1512,10 +1416,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>强制：在东晋弃牌区各放置1张[流民]，北方玩家弃1张手牌。将主版图弃牌区洗回牌库。摸1张牌。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>衣冠南渡</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1532,10 +1432,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>行动：传播1次文化。获得4vp。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>友方控制[江南]时，可以打出。传播1次[儒学]，存档此牌。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1568,10 +1464,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>X vp，X=[佛学]区域数</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>行动：传播1次[玄学]。获得X vp，X=存档区牌数。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1580,10 +1472,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>仅限东晋玩家打出。[佛学]贡献度&gt;1时，可以打出。支付2vp，然后转化1个东晋地点。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>检索2次[文化]，然后存档此牌。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1620,18 +1508,10 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>主动：没有手牌时可以使用，摸1张牌。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>被动：每当友方传播1次文化时，获得1vp。主动：选择1个版图上的文化标记翻面。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>仅限东晋玩家打出。被动：结算[僭越]效果时，获得2vp。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>求田问舍</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1764,10 +1644,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>被动：每次打出[军事]牌或执行[军事]策略，摸1张牌并获得1vp。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>2军力1vp</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1784,14 +1660,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>行动：3军力，存档此牌。被动：此牌在朝堂区中时，使用快速行动执行[进军]时，费用减1。使用快速行动执行[占据]时，费用加1或支付2vp。仅限北方玩家打出。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>仅限东晋玩家打出。行动：3军力。[僭越]其他每个东晋玩家各弃1张手牌。3军力。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>被动：每次结算[转化]后，摸1张牌并获得1vp。登场：先动值6。获得4军力。获得2威望。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1800,22 +1668,10 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>行动：支付1张手牌，提高1级顺位，传播1次[玄学]。被动：[加官进爵]不能被存档、征发或弃置。[宰辅]选择[加官进爵]时，需要额外支付1手牌。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>行动：2军力。选择1个玩家，随机抽取他的1张手牌。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>行动：2军力。本回合执行[进军]时，费用减1。被动：需要控制[幽燕]，才能打出、执行或征发。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>行动：2军力。本回合执行[进军]时，费用减1。被动：控制[西凉]时，才能打出、执行或征发。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>行动：提高1级[佛学]贡献度，从供应轨移除1个[佛学]标记，获得4vp。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1840,26 +1696,10 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>行动：支付1军力，传播1次[儒学]，征发1张[内政]候选策略牌。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>控制[关中]时，可以打出。提高2级佛学贡献度，从供应轨移除2个[佛学]标记，存档此牌。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>仅限东晋玩家打出。提高1级顺位，然后存档此牌。[僭越]额外提高1级顺位。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>仅限东晋玩家打出。转化1个东晋地点，然后存档此牌。[僭越]获得1威望。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>仅限东晋玩家打出。存档1个幕僚，然后选择1个友方玩家的幕僚，该玩家存档被选择的幕僚。[僭越]改为选择1个友方玩家的幕僚，该玩家存档被选择的幕僚。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>[威望]最高的东晋玩家，失去2[威望]。[僭越]改为选择1个东晋玩家，失去2[威望]，存档此牌。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1872,30 +1712,14 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>[加固]1次。1军力。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>行动：2军力。弃置1朝堂区的[流民]并在朝堂区补1张牌，然后获得2军力。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>具装甲骑</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>东晋行动：2军力。免费[加固]2次。北方行动：转化1个中立地点，获得1军力。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>通用</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>仅限东晋玩家打出。行动：选择1项：转化1个相邻中立地点。获得2军力。或者弃置1张朝堂区的[流民]牌并补充1张牌到朝堂区，获得4军力。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>行动：征发2张候选策略牌并补充1张牌到朝堂区。获得1军力。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1916,10 +1740,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>行动：摸3张牌。如果你的[内政]标记数&gt;3，额外摸1张牌。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>行动：免费[进军]1次。获得3军力。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1932,18 +1752,10 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>强制：选择1个[幕僚]区空位最少的玩家，该玩家选择1个费用最高的[幕僚]存档。将主版图弃牌区洗回牌库。摸1张牌。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>具有至少4个不同的标记时，可以打出。存档此牌。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>行动：摸2张牌。如果[内政]标记数&gt;3，额外摸1张牌。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>拥有3个权谋标记</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1992,10 +1804,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>被动：幕僚区空位总数为6。主动：如果拥有4种不同的标记各1个，获得1个朝堂行动；否则，可以打出1张幕僚牌，然后摸1张牌。登场：先动值7。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>存档此牌。终局：获得X vp，X=北方和东晋国家牌库中[流民]的数量。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -2008,7 +1816,195 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>行动：支付3vp，转化2个相邻中立地点。</t>
+    <t>摸2张牌。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>被动：幕僚区空位总数为6。主动：如果拥有4种不同的标记各1个，获得1个朝堂行动；否则，可以打出1张幕僚牌。登场：先动值7。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>强制：选择1个[幕僚]区空位最少的玩家，该玩家选择1个费用最高的[幕僚]存档。摸1张牌。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>强制：在东晋弃牌区各放置1张[流民]，北方玩家弃1张手牌。摸1张牌。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>儒学贡献超过5，且儒学轨道露出的空格最多</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>玄学贡献超过5，且玄学轨道露出的空格最多</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>佛学贡献超过5，且佛学轨道露出的空格最多</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动：支付1张手牌，提高1级顺位，传播1次[玄学]。被动：[加官进爵]不能被存档、征发或弃置。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>主动：打出1张[军事]牌或征发1张[军事]候选策略牌，然后摸1张牌。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动：2军力。从东晋面板获得[北伐]标记。被动：[北伐]不能被存档、征发或弃置。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动：2军力。本回合执行[进军]时，获得1vp。被动：需要控制[幽燕]，才能打出、执行或征发。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动：2军力。本回合执行[进军]时，获得1vp。被动：控制[西凉]时，才能打出、执行或征发。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动：2军力，存档此牌。被动：此牌在朝堂区中时，北方和晋玩家不能相互使用[进军]。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>拔才取士</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>主动：2军力，弃1张手牌，然后摸1张手牌。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>主动：弃1张手牌，然后摸1张牌。可以支付2军力，转化1个相邻中立地点。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动：转化1个相邻中立地点。获得2军力。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动：3军力，存档此牌。被动：此牌在朝堂区中时，使用快速行动执行[进军]时，费用减1。使用快速行动执行[占据]时，费用加1或支付2vp。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动：转化1个相邻中立地点，然后可以打出1张幕僚牌。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>被动：每次存档或弃置[流民]时，获得1军力。登场：先动值5。转化[京口][广陵]。获得1功绩和1威望。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>主动：打出1张[文化]牌或征发1张[文化]候选策略牌。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>主动：弃1张手牌，弃置1张候选策略牌，然后摸1张手牌并补充1张牌到朝堂区</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>主动：打出1张[军事]牌或征发1张[军事]候选策略牌。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>[僭越]重洗当前君主牌，并根据牌面描述重置司马家威望，获得1威望，然后存档此牌。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>占据[洛阳]时，可以打出。存档此牌。[僭越]交换东晋首都和洛阳的部队。获得1[威望]。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>转化[太原][平阳]，然后存档此牌。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动：3军力。[僭越]其他每个东晋玩家各弃1张手牌。3军力。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以依次打出2张手牌。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动：传播1次文化，然后可以打出1张手牌。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>存档1张幕僚牌，然后存档此牌。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动：支付1vp，传播1次[儒学]，可以打出1张手牌。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>[佛学]贡献度&gt;1时，可以打出。支付2vp，然后转化1个东晋地点。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>转化1个东晋地点，然后存档此牌。[僭越]获得1威望。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>提高1级顺位，然后存档此牌。[僭越]额外提高1级顺位。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择1个东晋玩家，降低1级顺位，然后存档此牌。[僭越]额外降低1级顺位。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>主动：没有手牌时可以使用，摸1张牌，获得1军力。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>主动：支付1军力，提高1级顺位等级。被动：需要[儒学]等级&gt;1，才能打出。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>被动：结算[僭越]效果时，获得3vp。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动：3军力。摸1张牌。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>东晋行动：3军力。免费[加固]1次。北方行动：转化1个中立地点，获得1军力。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得7军力。存档此牌。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动：摸3张牌。如果你的[内政]标记数&gt;2，额外摸1张牌。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动：摸2张牌。如果[内政]标记数&gt;2，额外摸1张牌。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>存档1个幕僚，然后选择1个友方玩家的幕僚，该玩家存档被选择的幕僚。[僭越]改为选择1个友方玩家的幕僚，该玩家存档被选择的幕僚。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>支付7军力。选择威望、功绩或者顺位，提高1级，其他所有东晋玩家降低1级。[僭越]司马家威望降低1级，获得4vp。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>降低1点[威望]或[功绩]，转化1个司马家地点。[僭越]可以转化1个东晋玩家地点。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>中庸</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -3032,10 +3028,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F1" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="G1" t="s">
         <v>4</v>
@@ -3050,7 +3046,7 @@
         <v>7</v>
       </c>
       <c r="K1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L1" t="s">
         <v>8</v>
@@ -3062,70 +3058,70 @@
         <v>80</v>
       </c>
       <c r="O1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="Q1" t="s">
+        <v>138</v>
+      </c>
+      <c r="R1" t="s">
+        <v>139</v>
+      </c>
+      <c r="S1" t="s">
         <v>140</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
+        <v>172</v>
+      </c>
+      <c r="U1" t="s">
         <v>141</v>
       </c>
-      <c r="S1" t="s">
+      <c r="V1" t="s">
         <v>142</v>
       </c>
-      <c r="T1" t="s">
-        <v>174</v>
-      </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>143</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>144</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>145</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>146</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>147</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" t="s">
         <v>148</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
+        <v>151</v>
+      </c>
+      <c r="AD1" t="s">
         <v>149</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AE1" t="s">
+        <v>173</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>286</v>
+      </c>
+      <c r="AG1" t="s">
         <v>150</v>
       </c>
-      <c r="AC1" t="s">
-        <v>153</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>151</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>175</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>292</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>152</v>
-      </c>
       <c r="AH1" t="s">
+        <v>158</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>159</v>
+      </c>
+      <c r="AJ1" t="s">
         <v>160</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>161</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.3">
@@ -3134,15 +3130,15 @@
       </c>
       <c r="C2" s="1">
         <f>AVERAGE(C12:C165)</f>
-        <v>1.4351145038167938</v>
+        <v>1.4122137404580153</v>
       </c>
       <c r="I2">
         <f t="shared" ref="I2:O2" si="0">SUM(I3:I165)</f>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J2">
         <f t="shared" si="0"/>
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K2">
         <f t="shared" si="0"/>
@@ -3150,15 +3146,15 @@
       </c>
       <c r="L2">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="M2">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="N2">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O2">
         <f t="shared" si="0"/>
@@ -3234,11 +3230,11 @@
       </c>
       <c r="AH2">
         <f>SUM(AH3:AH165)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI2">
         <f>SUM(AI3:AI165)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ2">
         <f>SUM(AJ3:AJ165)</f>
@@ -3259,7 +3255,7 @@
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F3" t="s">
         <v>13</v>
@@ -3267,8 +3263,8 @@
       <c r="G3" t="s">
         <v>14</v>
       </c>
-      <c r="H3">
-        <v>2</v>
+      <c r="H3" t="s">
+        <v>470</v>
       </c>
       <c r="P3">
         <f>SUM(Q3:AE3)</f>
@@ -3289,7 +3285,7 @@
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
@@ -3310,22 +3306,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>445</v>
+        <v>415</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>441</v>
+        <v>411</v>
       </c>
       <c r="E5" t="s">
-        <v>442</v>
+        <v>412</v>
       </c>
       <c r="F5" t="s">
-        <v>443</v>
+        <v>413</v>
       </c>
       <c r="G5" t="s">
-        <v>444</v>
+        <v>414</v>
       </c>
       <c r="H5">
         <v>2</v>
@@ -3348,13 +3344,13 @@
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F6" t="s">
         <v>63</v>
       </c>
       <c r="G6" t="s">
-        <v>491</v>
+        <v>446</v>
       </c>
       <c r="H6">
         <v>2</v>
@@ -3381,13 +3377,13 @@
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F7" t="s">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="G7" t="s">
-        <v>491</v>
+        <v>446</v>
       </c>
       <c r="H7">
         <v>2</v>
@@ -3414,10 +3410,10 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F8" t="s">
-        <v>348</v>
+        <v>473</v>
       </c>
       <c r="G8" t="s">
         <v>62</v>
@@ -3447,13 +3443,13 @@
         <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F9" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="G9" t="s">
-        <v>499</v>
+        <v>452</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -3474,7 +3470,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>440</v>
+        <v>410</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -3483,13 +3479,13 @@
         <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F10" t="s">
-        <v>460</v>
+        <v>426</v>
       </c>
       <c r="G10" t="s">
-        <v>451</v>
+        <v>420</v>
       </c>
       <c r="H10">
         <v>-9</v>
@@ -3516,10 +3512,10 @@
         <v>24</v>
       </c>
       <c r="E11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F11" t="s">
-        <v>464</v>
+        <v>428</v>
       </c>
       <c r="L11">
         <v>1</v>
@@ -3543,10 +3539,10 @@
         <v>26</v>
       </c>
       <c r="E12" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F12" t="s">
-        <v>500</v>
+        <v>453</v>
       </c>
       <c r="H12">
         <v>8</v>
@@ -3576,13 +3572,10 @@
         <v>26</v>
       </c>
       <c r="E13" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F13" t="s">
-        <v>338</v>
-      </c>
-      <c r="G13" t="s">
-        <v>14</v>
+        <v>326</v>
       </c>
       <c r="H13">
         <v>6</v>
@@ -3606,24 +3599,24 @@
         <v>88</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" t="s">
         <v>82</v>
       </c>
       <c r="E14" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F14" t="s">
-        <v>511</v>
+        <v>482</v>
       </c>
       <c r="G14" t="s">
-        <v>216</v>
+        <v>452</v>
       </c>
       <c r="H14">
-        <v>-9</v>
-      </c>
-      <c r="J14">
+        <v>-6</v>
+      </c>
+      <c r="L14">
         <v>1</v>
       </c>
       <c r="P14">
@@ -3648,10 +3641,10 @@
         <v>24</v>
       </c>
       <c r="E15" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F15" t="s">
-        <v>465</v>
+        <v>429</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -3675,13 +3668,13 @@
         <v>12</v>
       </c>
       <c r="E16" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F16" t="s">
-        <v>360</v>
+        <v>476</v>
       </c>
       <c r="G16" t="s">
-        <v>359</v>
+        <v>342</v>
       </c>
       <c r="H16">
         <v>2</v>
@@ -3714,13 +3707,13 @@
         <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F17" t="s">
-        <v>461</v>
+        <v>474</v>
       </c>
       <c r="G17" t="s">
-        <v>446</v>
+        <v>416</v>
       </c>
       <c r="H17">
         <v>-12</v>
@@ -3744,19 +3737,19 @@
         <v>69</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" t="s">
         <v>70</v>
       </c>
       <c r="E18" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F18" t="s">
-        <v>89</v>
+        <v>478</v>
       </c>
       <c r="H18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L18">
         <v>1</v>
@@ -3783,10 +3776,10 @@
         <v>24</v>
       </c>
       <c r="E19" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F19" t="s">
-        <v>501</v>
+        <v>454</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -3810,10 +3803,10 @@
         <v>12</v>
       </c>
       <c r="E20" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F20" t="s">
-        <v>455</v>
+        <v>481</v>
       </c>
       <c r="G20" t="s">
         <v>62</v>
@@ -3843,19 +3836,19 @@
         <v>76</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" t="s">
         <v>70</v>
       </c>
       <c r="E21" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F21" t="s">
-        <v>339</v>
+        <v>479</v>
       </c>
       <c r="H21">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L21">
         <v>1</v>
@@ -3873,7 +3866,7 @@
         <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -3882,10 +3875,10 @@
         <v>67</v>
       </c>
       <c r="E22" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F22" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="H22">
         <v>5</v>
@@ -3915,13 +3908,10 @@
         <v>26</v>
       </c>
       <c r="E23" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F23" t="s">
-        <v>447</v>
-      </c>
-      <c r="G23" t="s">
-        <v>14</v>
+        <v>417</v>
       </c>
       <c r="H23">
         <v>6</v>
@@ -3951,10 +3941,10 @@
         <v>70</v>
       </c>
       <c r="E24" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F24" t="s">
-        <v>504</v>
+        <v>457</v>
       </c>
       <c r="H24">
         <v>6</v>
@@ -3975,19 +3965,19 @@
         <v>34</v>
       </c>
       <c r="B25" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C25">
         <v>1</v>
       </c>
       <c r="D25" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E25" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F25" t="s">
-        <v>448</v>
+        <v>418</v>
       </c>
       <c r="H25">
         <v>4</v>
@@ -4014,13 +4004,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E26" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F26" t="s">
-        <v>449</v>
+        <v>419</v>
       </c>
       <c r="H26">
         <v>4</v>
@@ -4050,10 +4040,10 @@
         <v>67</v>
       </c>
       <c r="E27" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F27" t="s">
-        <v>505</v>
+        <v>458</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -4080,10 +4070,10 @@
         <v>24</v>
       </c>
       <c r="E28" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F28" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="K28">
         <v>1</v>
@@ -4107,10 +4097,10 @@
         <v>26</v>
       </c>
       <c r="E29" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F29" t="s">
-        <v>506</v>
+        <v>459</v>
       </c>
       <c r="G29" t="s">
         <v>14</v>
@@ -4143,10 +4133,10 @@
         <v>26</v>
       </c>
       <c r="E30" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F30" t="s">
-        <v>372</v>
+        <v>352</v>
       </c>
       <c r="G30" t="s">
         <v>14</v>
@@ -4170,22 +4160,22 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C31">
         <v>2</v>
       </c>
       <c r="D31" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E31" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F31" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="G31" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="H31">
         <v>-6</v>
@@ -4209,7 +4199,7 @@
         <v>40</v>
       </c>
       <c r="B32" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C32" t="s">
         <v>14</v>
@@ -4218,10 +4208,10 @@
         <v>24</v>
       </c>
       <c r="E32" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F32" t="s">
-        <v>366</v>
+        <v>348</v>
       </c>
       <c r="I32">
         <v>1</v>
@@ -4245,10 +4235,10 @@
         <v>26</v>
       </c>
       <c r="E33" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F33" t="s">
-        <v>450</v>
+        <v>472</v>
       </c>
       <c r="H33">
         <v>8</v>
@@ -4272,16 +4262,16 @@
         <v>42</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34" t="s">
         <v>26</v>
       </c>
       <c r="E34" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F34" t="s">
-        <v>367</v>
+        <v>484</v>
       </c>
       <c r="G34" t="s">
         <v>14</v>
@@ -4314,10 +4304,10 @@
         <v>44</v>
       </c>
       <c r="E35" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F35" t="s">
-        <v>368</v>
+        <v>349</v>
       </c>
       <c r="G35" t="s">
         <v>14</v>
@@ -4350,10 +4340,10 @@
         <v>24</v>
       </c>
       <c r="E36" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F36" t="s">
-        <v>304</v>
+        <v>483</v>
       </c>
       <c r="L36">
         <v>1</v>
@@ -4377,13 +4367,13 @@
         <v>70</v>
       </c>
       <c r="E37" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F37" t="s">
-        <v>340</v>
+        <v>485</v>
       </c>
       <c r="H37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L37">
         <v>1</v>
@@ -4401,7 +4391,7 @@
         <v>45</v>
       </c>
       <c r="B38" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C38">
         <v>2</v>
@@ -4410,13 +4400,13 @@
         <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F38" t="s">
-        <v>452</v>
+        <v>421</v>
       </c>
       <c r="G38" t="s">
-        <v>451</v>
+        <v>420</v>
       </c>
       <c r="H38">
         <v>-9</v>
@@ -4437,19 +4427,19 @@
         <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C39">
         <v>0</v>
       </c>
       <c r="D39" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E39" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F39" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="H39">
         <v>0</v>
@@ -4479,10 +4469,10 @@
         <v>24</v>
       </c>
       <c r="E40" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F40" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="I40">
         <v>1</v>
@@ -4506,10 +4496,10 @@
         <v>44</v>
       </c>
       <c r="E41" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F41" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="G41" t="s">
         <v>14</v>
@@ -4545,13 +4535,13 @@
         <v>12</v>
       </c>
       <c r="E42" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F42" t="s">
-        <v>462</v>
+        <v>475</v>
       </c>
       <c r="G42" t="s">
-        <v>446</v>
+        <v>416</v>
       </c>
       <c r="H42">
         <v>-12</v>
@@ -4572,7 +4562,7 @@
         <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C43">
         <v>2</v>
@@ -4581,10 +4571,10 @@
         <v>70</v>
       </c>
       <c r="E43" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F43" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="H43">
         <v>6</v>
@@ -4605,7 +4595,7 @@
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C44" t="s">
         <v>14</v>
@@ -4614,10 +4604,10 @@
         <v>24</v>
       </c>
       <c r="E44" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F44" t="s">
-        <v>453</v>
+        <v>422</v>
       </c>
       <c r="K44">
         <v>1</v>
@@ -4641,10 +4631,10 @@
         <v>44</v>
       </c>
       <c r="E45" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F45" t="s">
-        <v>369</v>
+        <v>350</v>
       </c>
       <c r="H45">
         <v>0</v>
@@ -4674,10 +4664,10 @@
         <v>26</v>
       </c>
       <c r="E46" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F46" t="s">
-        <v>370</v>
+        <v>486</v>
       </c>
       <c r="H46">
         <v>6</v>
@@ -4698,7 +4688,7 @@
         <v>49</v>
       </c>
       <c r="B47" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -4707,10 +4697,10 @@
         <v>67</v>
       </c>
       <c r="E47" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F47" t="s">
-        <v>139</v>
+        <v>487</v>
       </c>
       <c r="H47">
         <v>4</v>
@@ -4746,10 +4736,10 @@
         <v>24</v>
       </c>
       <c r="E48" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F48" t="s">
-        <v>507</v>
+        <v>464</v>
       </c>
       <c r="J48">
         <v>1</v>
@@ -4773,13 +4763,13 @@
         <v>26</v>
       </c>
       <c r="E49" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F49" t="s">
-        <v>454</v>
+        <v>423</v>
       </c>
       <c r="H49">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J49">
         <v>1</v>
@@ -4806,10 +4796,10 @@
         <v>26</v>
       </c>
       <c r="E50" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F50" t="s">
-        <v>350</v>
+        <v>334</v>
       </c>
       <c r="G50" t="s">
         <v>14</v>
@@ -4842,13 +4832,13 @@
         <v>12</v>
       </c>
       <c r="E51" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F51" t="s">
-        <v>456</v>
+        <v>490</v>
       </c>
       <c r="G51" t="s">
-        <v>439</v>
+        <v>409</v>
       </c>
       <c r="H51">
         <v>-9</v>
@@ -4884,10 +4874,10 @@
         <v>24</v>
       </c>
       <c r="E52" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F52" t="s">
-        <v>457</v>
+        <v>424</v>
       </c>
       <c r="J52">
         <v>1</v>
@@ -4908,13 +4898,13 @@
         <v>2</v>
       </c>
       <c r="D53" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E53" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F53" t="s">
-        <v>342</v>
+        <v>489</v>
       </c>
       <c r="H53">
         <v>2</v>
@@ -4941,16 +4931,16 @@
         <v>58</v>
       </c>
       <c r="C54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D54" t="s">
         <v>26</v>
       </c>
       <c r="E54" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F54" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="H54">
         <v>4</v>
@@ -4980,7 +4970,7 @@
         <v>67</v>
       </c>
       <c r="E55" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F55" t="s">
         <v>68</v>
@@ -5001,10 +4991,10 @@
     </row>
     <row r="56" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="B56" t="s">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="C56" t="s">
         <v>14</v>
@@ -5013,10 +5003,10 @@
         <v>24</v>
       </c>
       <c r="E56" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F56" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="L56">
         <v>1</v>
@@ -5028,10 +5018,10 @@
     </row>
     <row r="57" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="B57" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -5040,10 +5030,10 @@
         <v>67</v>
       </c>
       <c r="E57" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F57" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H57">
         <v>1</v>
@@ -5061,10 +5051,10 @@
     </row>
     <row r="58" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="B58" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C58">
         <v>2</v>
@@ -5073,13 +5063,13 @@
         <v>82</v>
       </c>
       <c r="E58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F58" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="G58" t="s">
-        <v>399</v>
+        <v>373</v>
       </c>
       <c r="H58">
         <v>-9</v>
@@ -5097,10 +5087,10 @@
     </row>
     <row r="59" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="B59" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -5109,10 +5099,10 @@
         <v>70</v>
       </c>
       <c r="E59" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F59" t="s">
-        <v>458</v>
+        <v>425</v>
       </c>
       <c r="H59">
         <v>4</v>
@@ -5130,10 +5120,10 @@
     </row>
     <row r="60" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B60" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -5142,10 +5132,10 @@
         <v>44</v>
       </c>
       <c r="E60" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F60" t="s">
-        <v>492</v>
+        <v>465</v>
       </c>
       <c r="H60">
         <v>0</v>
@@ -5160,7 +5150,7 @@
     </row>
     <row r="61" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B61" t="s">
         <v>59</v>
@@ -5172,10 +5162,10 @@
         <v>44</v>
       </c>
       <c r="E61" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F61" t="s">
-        <v>365</v>
+        <v>347</v>
       </c>
       <c r="H61">
         <v>0</v>
@@ -5190,7 +5180,7 @@
     </row>
     <row r="62" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B62" t="s">
         <v>60</v>
@@ -5202,10 +5192,10 @@
         <v>44</v>
       </c>
       <c r="E62" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F62" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="H62">
         <v>0</v>
@@ -5220,10 +5210,10 @@
     </row>
     <row r="63" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B63" t="s">
-        <v>397</v>
+        <v>371</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -5232,10 +5222,10 @@
         <v>67</v>
       </c>
       <c r="E63" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F63" t="s">
-        <v>371</v>
+        <v>351</v>
       </c>
       <c r="H63">
         <v>0</v>
@@ -5253,22 +5243,22 @@
     </row>
     <row r="64" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B64" t="s">
-        <v>388</v>
+        <v>363</v>
       </c>
       <c r="C64">
         <v>0</v>
       </c>
       <c r="D64" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E64" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F64" t="s">
-        <v>387</v>
+        <v>466</v>
       </c>
       <c r="H64">
         <v>0</v>
@@ -5283,22 +5273,22 @@
     </row>
     <row r="65" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B65" t="s">
-        <v>398</v>
+        <v>372</v>
       </c>
       <c r="C65">
         <v>0</v>
       </c>
       <c r="D65" t="s">
-        <v>394</v>
+        <v>368</v>
       </c>
       <c r="E65" t="s">
-        <v>395</v>
+        <v>369</v>
       </c>
       <c r="F65" t="s">
-        <v>396</v>
+        <v>370</v>
       </c>
       <c r="H65">
         <v>0</v>
@@ -5319,7 +5309,7 @@
     </row>
     <row r="66" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B66" t="s">
         <v>61</v>
@@ -5331,10 +5321,10 @@
         <v>44</v>
       </c>
       <c r="E66" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F66" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="H66">
         <v>9</v>
@@ -5352,7 +5342,7 @@
     </row>
     <row r="67" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B67" t="s">
         <v>86</v>
@@ -5364,10 +5354,10 @@
         <v>67</v>
       </c>
       <c r="E67" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F67" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="H67">
         <v>9</v>
@@ -5385,7 +5375,7 @@
     </row>
     <row r="68" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B68" t="s">
         <v>87</v>
@@ -5397,10 +5387,10 @@
         <v>67</v>
       </c>
       <c r="E68" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F68" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="H68">
         <v>9</v>
@@ -5418,10 +5408,10 @@
     </row>
     <row r="69" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B69" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -5430,10 +5420,10 @@
         <v>67</v>
       </c>
       <c r="E69" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F69" t="s">
-        <v>384</v>
+        <v>488</v>
       </c>
       <c r="H69">
         <v>7</v>
@@ -5457,22 +5447,22 @@
     </row>
     <row r="70" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B70" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C70">
         <v>2</v>
       </c>
       <c r="D70" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="E70" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="F70" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="H70">
         <v>4</v>
@@ -5481,7 +5471,7 @@
         <v>1</v>
       </c>
       <c r="P70">
-        <f t="shared" ref="P70:P101" si="4">SUM(Q70:AE70)</f>
+        <f t="shared" ref="P70:P100" si="4">SUM(Q70:AE70)</f>
         <v>1</v>
       </c>
       <c r="AA70">
@@ -5493,22 +5483,22 @@
     </row>
     <row r="71" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B71" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="C71">
         <v>3</v>
       </c>
       <c r="D71" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="E71" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="F71" t="s">
-        <v>493</v>
+        <v>447</v>
       </c>
       <c r="H71">
         <v>16</v>
@@ -5526,22 +5516,22 @@
     </row>
     <row r="72" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B72" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C72">
         <v>2</v>
       </c>
       <c r="D72" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="E72" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="F72" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="H72">
         <v>13</v>
@@ -5559,22 +5549,22 @@
     </row>
     <row r="73" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B73" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="C73">
         <v>2</v>
       </c>
       <c r="D73" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="E73" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="F73" t="s">
-        <v>386</v>
+        <v>362</v>
       </c>
       <c r="H73">
         <v>12</v>
@@ -5592,7 +5582,7 @@
     </row>
     <row r="74" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B74" t="s">
         <v>72</v>
@@ -5604,10 +5594,10 @@
         <v>70</v>
       </c>
       <c r="E74" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F74" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H74">
         <v>3</v>
@@ -5625,10 +5615,10 @@
     </row>
     <row r="75" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B75" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C75">
         <v>2</v>
@@ -5637,10 +5627,10 @@
         <v>70</v>
       </c>
       <c r="E75" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F75" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="H75">
         <v>4</v>
@@ -5658,10 +5648,10 @@
     </row>
     <row r="76" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B76" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C76">
         <v>3</v>
@@ -5670,10 +5660,10 @@
         <v>70</v>
       </c>
       <c r="E76" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F76" t="s">
-        <v>353</v>
+        <v>336</v>
       </c>
       <c r="H76">
         <v>6</v>
@@ -5691,7 +5681,7 @@
     </row>
     <row r="77" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B77" t="s">
         <v>73</v>
@@ -5703,10 +5693,10 @@
         <v>67</v>
       </c>
       <c r="E77" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F77" t="s">
-        <v>389</v>
+        <v>364</v>
       </c>
       <c r="H77">
         <v>7</v>
@@ -5727,7 +5717,7 @@
     </row>
     <row r="78" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B78" t="s">
         <v>74</v>
@@ -5739,10 +5729,10 @@
         <v>67</v>
       </c>
       <c r="E78" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F78" t="s">
-        <v>390</v>
+        <v>365</v>
       </c>
       <c r="H78">
         <v>7</v>
@@ -5763,22 +5753,22 @@
     </row>
     <row r="79" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B79" t="s">
         <v>75</v>
       </c>
       <c r="C79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D79" t="s">
         <v>67</v>
       </c>
       <c r="E79" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F79" t="s">
-        <v>312</v>
+        <v>493</v>
       </c>
       <c r="H79">
         <v>9</v>
@@ -5796,7 +5786,7 @@
     </row>
     <row r="80" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B80" t="s">
         <v>85</v>
@@ -5808,10 +5798,10 @@
         <v>67</v>
       </c>
       <c r="E80" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F80" t="s">
-        <v>508</v>
+        <v>460</v>
       </c>
       <c r="H80">
         <v>9</v>
@@ -5829,10 +5819,10 @@
     </row>
     <row r="81" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B81" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -5841,10 +5831,10 @@
         <v>67</v>
       </c>
       <c r="E81" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F81" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H81">
         <v>5</v>
@@ -5865,22 +5855,22 @@
     </row>
     <row r="82" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B82" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C82">
         <v>1</v>
       </c>
       <c r="D82" t="s">
+        <v>184</v>
+      </c>
+      <c r="E82" t="s">
         <v>186</v>
       </c>
-      <c r="E82" t="s">
-        <v>188</v>
-      </c>
       <c r="F82" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="H82">
         <v>6</v>
@@ -5898,25 +5888,25 @@
     </row>
     <row r="83" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B83" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C83">
         <v>2</v>
       </c>
       <c r="D83" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E83" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F83" t="s">
-        <v>312</v>
+        <v>364</v>
       </c>
       <c r="H83">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I83">
         <v>1</v>
@@ -5928,25 +5918,28 @@
       <c r="X83">
         <v>1</v>
       </c>
+      <c r="AI83">
+        <v>1</v>
+      </c>
     </row>
     <row r="84" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B84" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C84">
         <v>2</v>
       </c>
       <c r="D84" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E84" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F84" t="s">
-        <v>391</v>
+        <v>366</v>
       </c>
       <c r="H84">
         <v>4</v>
@@ -5967,22 +5960,22 @@
     </row>
     <row r="85" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B85" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C85">
         <v>3</v>
       </c>
       <c r="D85" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E85" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F85" t="s">
-        <v>509</v>
+        <v>461</v>
       </c>
       <c r="H85">
         <v>8</v>
@@ -6000,22 +5993,22 @@
     </row>
     <row r="86" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B86" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C86">
         <v>2</v>
       </c>
       <c r="D86" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E86" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F86" t="s">
-        <v>393</v>
+        <v>367</v>
       </c>
       <c r="H86">
         <v>6</v>
@@ -6036,22 +6029,22 @@
     </row>
     <row r="87" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B87" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C87">
         <v>1</v>
       </c>
       <c r="D87" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E87" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F87" t="s">
-        <v>463</v>
+        <v>427</v>
       </c>
       <c r="G87" t="s">
         <v>83</v>
@@ -6075,30 +6068,30 @@
     </row>
     <row r="88" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B88" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C88">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D88" t="s">
         <v>82</v>
       </c>
       <c r="E88" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F88" t="s">
+        <v>492</v>
+      </c>
+      <c r="G88" t="s">
         <v>392</v>
-      </c>
-      <c r="G88" t="s">
-        <v>399</v>
       </c>
       <c r="H88">
         <v>-9</v>
       </c>
-      <c r="I88">
+      <c r="L88">
         <v>1</v>
       </c>
       <c r="P88">
@@ -6111,10 +6104,10 @@
     </row>
     <row r="89" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B89" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C89">
         <v>1</v>
@@ -6123,13 +6116,13 @@
         <v>82</v>
       </c>
       <c r="E89" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F89" t="s">
-        <v>466</v>
+        <v>430</v>
       </c>
       <c r="G89" t="s">
-        <v>401</v>
+        <v>83</v>
       </c>
       <c r="H89">
         <v>-6</v>
@@ -6150,10 +6143,10 @@
     </row>
     <row r="90" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B90" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C90">
         <v>3</v>
@@ -6162,13 +6155,13 @@
         <v>12</v>
       </c>
       <c r="E90" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F90" t="s">
-        <v>467</v>
+        <v>431</v>
       </c>
       <c r="G90" t="s">
-        <v>422</v>
+        <v>392</v>
       </c>
       <c r="H90">
         <v>-12</v>
@@ -6189,10 +6182,10 @@
     </row>
     <row r="91" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B91" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C91">
         <v>3</v>
@@ -6201,13 +6194,13 @@
         <v>12</v>
       </c>
       <c r="E91" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F91" t="s">
-        <v>400</v>
+        <v>374</v>
       </c>
       <c r="G91" t="s">
-        <v>468</v>
+        <v>432</v>
       </c>
       <c r="H91">
         <v>-12</v>
@@ -6228,22 +6221,22 @@
     </row>
     <row r="92" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B92" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="C92">
         <v>1</v>
       </c>
       <c r="D92" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E92" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F92" t="s">
-        <v>469</v>
+        <v>494</v>
       </c>
       <c r="G92" t="s">
         <v>62</v>
@@ -6267,25 +6260,25 @@
     </row>
     <row r="93" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B93" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C93">
         <v>3</v>
       </c>
       <c r="D93" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E93" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F93" t="s">
-        <v>503</v>
+        <v>456</v>
       </c>
       <c r="G93" t="s">
-        <v>468</v>
+        <v>432</v>
       </c>
       <c r="H93">
         <v>-12</v>
@@ -6303,25 +6296,25 @@
     </row>
     <row r="94" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B94" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C94">
         <v>2</v>
       </c>
       <c r="D94" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E94" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F94" t="s">
-        <v>402</v>
+        <v>375</v>
       </c>
       <c r="G94" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="H94">
         <v>-9</v>
@@ -6345,10 +6338,10 @@
     </row>
     <row r="95" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B95" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -6357,10 +6350,10 @@
         <v>67</v>
       </c>
       <c r="E95" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F95" t="s">
-        <v>403</v>
+        <v>376</v>
       </c>
       <c r="H95">
         <v>2</v>
@@ -6381,10 +6374,10 @@
     </row>
     <row r="96" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B96" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -6393,15 +6386,18 @@
         <v>67</v>
       </c>
       <c r="E96" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F96" t="s">
-        <v>404</v>
+        <v>495</v>
       </c>
       <c r="H96">
         <v>0</v>
       </c>
       <c r="K96">
+        <v>1</v>
+      </c>
+      <c r="M96">
         <v>1</v>
       </c>
       <c r="P96">
@@ -6417,10 +6413,10 @@
     </row>
     <row r="97" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B97" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C97">
         <v>2</v>
@@ -6429,15 +6425,18 @@
         <v>67</v>
       </c>
       <c r="E97" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F97" t="s">
-        <v>472</v>
+        <v>496</v>
       </c>
       <c r="H97">
         <v>1</v>
       </c>
       <c r="K97">
+        <v>1</v>
+      </c>
+      <c r="M97">
         <v>1</v>
       </c>
       <c r="O97">
@@ -6453,10 +6452,10 @@
     </row>
     <row r="98" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B98" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -6465,10 +6464,10 @@
         <v>67</v>
       </c>
       <c r="E98" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F98" t="s">
-        <v>471</v>
+        <v>497</v>
       </c>
       <c r="H98">
         <v>0</v>
@@ -6492,22 +6491,22 @@
     </row>
     <row r="99" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B99" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="C99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D99" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="E99" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="F99" t="s">
-        <v>331</v>
+        <v>498</v>
       </c>
       <c r="H99">
         <v>3</v>
@@ -6528,27 +6527,30 @@
     </row>
     <row r="100" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B100" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="C100">
         <v>0</v>
       </c>
       <c r="D100" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="E100" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="F100" t="s">
-        <v>410</v>
+        <v>382</v>
       </c>
       <c r="H100">
         <v>1</v>
       </c>
       <c r="K100">
+        <v>1</v>
+      </c>
+      <c r="M100">
         <v>1</v>
       </c>
       <c r="P100">
@@ -6561,24 +6563,27 @@
     </row>
     <row r="101" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B101" t="s">
-        <v>407</v>
+        <v>379</v>
       </c>
       <c r="C101">
         <v>0</v>
       </c>
       <c r="D101" t="s">
-        <v>394</v>
+        <v>368</v>
       </c>
       <c r="E101" t="s">
-        <v>408</v>
+        <v>380</v>
       </c>
       <c r="F101" t="s">
-        <v>473</v>
+        <v>507</v>
       </c>
       <c r="K101">
+        <v>1</v>
+      </c>
+      <c r="M101">
         <v>1</v>
       </c>
       <c r="O101">
@@ -6590,22 +6595,22 @@
     </row>
     <row r="102" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B102" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="C102">
         <v>0</v>
       </c>
       <c r="D102" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="E102" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="F102" t="s">
-        <v>474</v>
+        <v>434</v>
       </c>
       <c r="H102">
         <v>2</v>
@@ -6613,6 +6618,9 @@
       <c r="K102">
         <v>1</v>
       </c>
+      <c r="M102">
+        <v>1</v>
+      </c>
       <c r="O102">
         <v>1</v>
       </c>
@@ -6626,27 +6634,30 @@
     </row>
     <row r="103" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B103" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="C103">
         <v>0</v>
       </c>
       <c r="D103" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="E103" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="F103" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="H103">
         <v>1</v>
       </c>
       <c r="K103">
+        <v>1</v>
+      </c>
+      <c r="M103">
         <v>1</v>
       </c>
       <c r="O103">
@@ -6662,10 +6673,10 @@
     </row>
     <row r="104" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B104" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -6674,10 +6685,10 @@
         <v>67</v>
       </c>
       <c r="E104" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F104" t="s">
-        <v>405</v>
+        <v>377</v>
       </c>
       <c r="H104">
         <v>0</v>
@@ -6695,10 +6706,10 @@
     </row>
     <row r="105" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B105" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -6707,10 +6718,10 @@
         <v>44</v>
       </c>
       <c r="E105" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F105" t="s">
-        <v>406</v>
+        <v>378</v>
       </c>
       <c r="H105">
         <v>0</v>
@@ -6728,22 +6739,22 @@
     </row>
     <row r="106" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B106" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C106">
         <v>1</v>
       </c>
       <c r="D106" t="s">
-        <v>411</v>
+        <v>383</v>
       </c>
       <c r="E106" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F106" t="s">
-        <v>475</v>
+        <v>435</v>
       </c>
       <c r="H106">
         <v>4</v>
@@ -6761,10 +6772,10 @@
     </row>
     <row r="107" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B107" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C107">
         <v>2</v>
@@ -6773,10 +6784,10 @@
         <v>67</v>
       </c>
       <c r="E107" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F107" t="s">
-        <v>420</v>
+        <v>390</v>
       </c>
       <c r="H107">
         <v>0</v>
@@ -6797,10 +6808,10 @@
     </row>
     <row r="108" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B108" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C108">
         <v>2</v>
@@ -6809,10 +6820,10 @@
         <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F108" t="s">
-        <v>470</v>
+        <v>433</v>
       </c>
       <c r="H108">
         <v>6</v>
@@ -6833,22 +6844,22 @@
     </row>
     <row r="109" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B109" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="C109">
         <v>2</v>
       </c>
       <c r="D109" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E109" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F109" t="s">
-        <v>412</v>
+        <v>384</v>
       </c>
       <c r="H109">
         <v>0</v>
@@ -6869,25 +6880,25 @@
     </row>
     <row r="110" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B110" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C110">
         <v>3</v>
       </c>
       <c r="D110" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E110" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F110" t="s">
-        <v>413</v>
+        <v>385</v>
       </c>
       <c r="H110">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I110">
         <v>1</v>
@@ -6905,22 +6916,22 @@
     </row>
     <row r="111" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B111" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C111">
         <v>0</v>
       </c>
       <c r="D111" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E111" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F111" t="s">
-        <v>476</v>
+        <v>436</v>
       </c>
       <c r="H111">
         <v>7</v>
@@ -6938,25 +6949,25 @@
     </row>
     <row r="112" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B112" t="s">
+        <v>175</v>
+      </c>
+      <c r="C112">
+        <v>0</v>
+      </c>
+      <c r="D112" t="s">
+        <v>176</v>
+      </c>
+      <c r="E112" t="s">
         <v>177</v>
       </c>
-      <c r="C112">
-        <v>0</v>
-      </c>
-      <c r="D112" t="s">
-        <v>178</v>
-      </c>
-      <c r="E112" t="s">
-        <v>179</v>
-      </c>
       <c r="F112" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="H112">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L112">
         <v>1</v>
@@ -6971,25 +6982,25 @@
     </row>
     <row r="113" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B113" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="C113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D113" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E113" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F113" t="s">
-        <v>180</v>
+        <v>297</v>
       </c>
       <c r="H113">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L113">
         <v>1</v>
@@ -7004,22 +7015,22 @@
     </row>
     <row r="114" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B114" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C114">
         <v>0</v>
       </c>
       <c r="D114" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E114" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F114" t="s">
-        <v>351</v>
+        <v>500</v>
       </c>
       <c r="H114">
         <v>2</v>
@@ -7034,25 +7045,28 @@
       <c r="R114">
         <v>1</v>
       </c>
+      <c r="AH114">
+        <v>1</v>
+      </c>
     </row>
     <row r="115" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B115" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C115">
         <v>0</v>
       </c>
       <c r="D115" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E115" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F115" t="s">
-        <v>414</v>
+        <v>499</v>
       </c>
       <c r="H115">
         <v>2</v>
@@ -7070,25 +7084,25 @@
     </row>
     <row r="116" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B116" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C116">
         <v>1</v>
       </c>
       <c r="D116" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E116" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F116" t="s">
-        <v>415</v>
+        <v>386</v>
       </c>
       <c r="H116">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I116">
         <v>1</v>
@@ -7103,25 +7117,25 @@
     </row>
     <row r="117" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B117" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C117">
         <v>1</v>
       </c>
       <c r="D117" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E117" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F117" t="s">
-        <v>419</v>
+        <v>389</v>
       </c>
       <c r="H117">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I117">
         <v>1</v>
@@ -7139,22 +7153,22 @@
     </row>
     <row r="118" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B118" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C118">
         <v>0</v>
       </c>
       <c r="D118" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E118" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F118" t="s">
-        <v>418</v>
+        <v>388</v>
       </c>
       <c r="H118">
         <v>2</v>
@@ -7172,25 +7186,25 @@
     </row>
     <row r="119" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B119" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C119">
         <v>1</v>
       </c>
       <c r="D119" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E119" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F119" t="s">
-        <v>416</v>
+        <v>501</v>
       </c>
       <c r="H119">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K119">
         <v>1</v>
@@ -7205,25 +7219,25 @@
     </row>
     <row r="120" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B120" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C120">
         <v>1</v>
       </c>
       <c r="D120" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E120" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F120" t="s">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="G120" t="s">
-        <v>477</v>
+        <v>62</v>
       </c>
       <c r="H120">
         <v>-6</v>
@@ -7241,22 +7255,22 @@
     </row>
     <row r="121" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B121" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C121">
         <v>1</v>
       </c>
       <c r="D121" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E121" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F121" t="s">
-        <v>510</v>
+        <v>462</v>
       </c>
       <c r="G121" t="s">
         <v>62</v>
@@ -7277,10 +7291,10 @@
     </row>
     <row r="122" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B122" t="s">
-        <v>423</v>
+        <v>393</v>
       </c>
       <c r="C122">
         <v>3</v>
@@ -7289,13 +7303,13 @@
         <v>12</v>
       </c>
       <c r="E122" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F122" t="s">
-        <v>421</v>
+        <v>391</v>
       </c>
       <c r="G122" t="s">
-        <v>422</v>
+        <v>392</v>
       </c>
       <c r="H122">
         <v>-12</v>
@@ -7316,25 +7330,25 @@
     </row>
     <row r="123" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B123" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C123">
         <v>2</v>
       </c>
       <c r="D123" t="s">
+        <v>210</v>
+      </c>
+      <c r="E123" t="s">
+        <v>211</v>
+      </c>
+      <c r="F123" t="s">
+        <v>502</v>
+      </c>
+      <c r="G123" t="s">
         <v>213</v>
-      </c>
-      <c r="E123" t="s">
-        <v>214</v>
-      </c>
-      <c r="F123" t="s">
-        <v>478</v>
-      </c>
-      <c r="G123" t="s">
-        <v>216</v>
       </c>
       <c r="H123">
         <v>-9</v>
@@ -7352,10 +7366,10 @@
     </row>
     <row r="124" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B124" t="s">
-        <v>479</v>
+        <v>437</v>
       </c>
       <c r="C124">
         <v>3</v>
@@ -7364,13 +7378,13 @@
         <v>12</v>
       </c>
       <c r="E124" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F124" t="s">
-        <v>489</v>
+        <v>444</v>
       </c>
       <c r="G124" t="s">
-        <v>446</v>
+        <v>416</v>
       </c>
       <c r="H124">
         <v>-9</v>
@@ -7388,22 +7402,22 @@
     </row>
     <row r="125" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B125" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C125">
         <v>1</v>
       </c>
       <c r="D125" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E125" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F125" t="s">
-        <v>480</v>
+        <v>503</v>
       </c>
       <c r="G125" t="s">
         <v>62</v>
@@ -7424,28 +7438,28 @@
     </row>
     <row r="126" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A126" s="4" t="s">
-        <v>481</v>
+        <v>438</v>
       </c>
       <c r="B126" t="s">
         <v>88</v>
       </c>
       <c r="C126">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D126" t="s">
         <v>82</v>
       </c>
       <c r="E126" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F126" t="s">
-        <v>511</v>
+        <v>482</v>
       </c>
       <c r="G126" t="s">
-        <v>216</v>
+        <v>452</v>
       </c>
       <c r="H126">
-        <v>-9</v>
+        <v>-6</v>
       </c>
       <c r="J126">
         <v>1</v>
@@ -7460,25 +7474,25 @@
     </row>
     <row r="127" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B127" t="s">
-        <v>349</v>
+        <v>333</v>
       </c>
       <c r="C127">
         <v>2</v>
       </c>
       <c r="D127" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E127" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="F127" t="s">
-        <v>483</v>
+        <v>439</v>
       </c>
       <c r="G127" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="H127">
         <v>-9</v>
@@ -7496,25 +7510,25 @@
     </row>
     <row r="128" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B128" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C128">
         <v>2</v>
       </c>
       <c r="D128" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E128" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="F128" t="s">
-        <v>484</v>
+        <v>440</v>
       </c>
       <c r="G128" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="H128">
         <v>-9</v>
@@ -7532,25 +7546,25 @@
     </row>
     <row r="129" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B129" t="s">
-        <v>487</v>
+        <v>443</v>
       </c>
       <c r="C129">
         <v>2</v>
       </c>
       <c r="D129" t="s">
-        <v>441</v>
+        <v>411</v>
       </c>
       <c r="E129" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F129" t="s">
-        <v>488</v>
+        <v>505</v>
       </c>
       <c r="G129" t="s">
-        <v>451</v>
+        <v>420</v>
       </c>
       <c r="H129">
         <v>-9</v>
@@ -7564,10 +7578,10 @@
     </row>
     <row r="130" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B130" t="s">
-        <v>479</v>
+        <v>437</v>
       </c>
       <c r="C130">
         <v>3</v>
@@ -7576,13 +7590,13 @@
         <v>12</v>
       </c>
       <c r="E130" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F130" t="s">
-        <v>489</v>
+        <v>444</v>
       </c>
       <c r="G130" t="s">
-        <v>490</v>
+        <v>445</v>
       </c>
       <c r="H130">
         <v>-9</v>
@@ -7600,25 +7614,25 @@
     </row>
     <row r="131" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B131" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C131">
         <v>2</v>
       </c>
       <c r="D131" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E131" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="F131" t="s">
-        <v>485</v>
+        <v>441</v>
       </c>
       <c r="G131" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="H131">
         <v>-9</v>
@@ -7636,7 +7650,7 @@
     </row>
     <row r="132" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B132" t="s">
         <v>81</v>
@@ -7648,13 +7662,13 @@
         <v>82</v>
       </c>
       <c r="E132" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F132" t="s">
-        <v>486</v>
+        <v>442</v>
       </c>
       <c r="G132" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="H132">
         <v>-9</v>
@@ -7672,10 +7686,10 @@
     </row>
     <row r="133" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B133" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -7684,10 +7698,10 @@
         <v>44</v>
       </c>
       <c r="E133" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F133" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="H133">
         <v>1</v>
@@ -7705,27 +7719,30 @@
     </row>
     <row r="134" spans="1:34" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B134" t="s">
-        <v>429</v>
+        <v>399</v>
       </c>
       <c r="C134">
         <v>3</v>
       </c>
       <c r="D134" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E134" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F134" t="s">
-        <v>252</v>
+        <v>504</v>
       </c>
       <c r="H134">
         <v>1</v>
       </c>
       <c r="J134">
+        <v>1</v>
+      </c>
+      <c r="M134">
         <v>1</v>
       </c>
       <c r="P134">
@@ -7738,27 +7755,30 @@
     </row>
     <row r="135" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B135" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C135">
         <v>3</v>
       </c>
       <c r="D135" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E135" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F135" t="s">
-        <v>255</v>
+        <v>504</v>
       </c>
       <c r="H135">
         <v>1</v>
       </c>
       <c r="J135">
+        <v>1</v>
+      </c>
+      <c r="N135">
         <v>1</v>
       </c>
       <c r="P135">
@@ -7771,22 +7791,22 @@
     </row>
     <row r="136" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B136" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C136">
         <v>0</v>
       </c>
       <c r="D136" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E136" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F136" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="H136">
         <v>13</v>
@@ -7804,22 +7824,22 @@
     </row>
     <row r="137" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B137" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C137">
         <v>0</v>
       </c>
       <c r="D137" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E137" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F137" t="s">
-        <v>425</v>
+        <v>395</v>
       </c>
       <c r="H137">
         <v>0</v>
@@ -7837,22 +7857,22 @@
     </row>
     <row r="138" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B138" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="C138">
         <v>0</v>
       </c>
       <c r="D138" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E138" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F138" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="H138">
         <v>11</v>
@@ -7870,22 +7890,22 @@
     </row>
     <row r="139" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B139" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="C139">
         <v>0</v>
       </c>
       <c r="D139" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E139" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F139" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="H139">
         <v>0</v>
@@ -7903,22 +7923,22 @@
     </row>
     <row r="140" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A140" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B140" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C140">
         <v>1</v>
       </c>
       <c r="D140" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E140" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F140" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="H140">
         <v>12</v>
@@ -7936,22 +7956,22 @@
     </row>
     <row r="141" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B141" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="C141">
         <v>0</v>
       </c>
       <c r="D141" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E141" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F141" t="s">
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="H141">
         <v>9</v>
@@ -7969,22 +7989,22 @@
     </row>
     <row r="142" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B142" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C142">
         <v>1</v>
       </c>
       <c r="D142" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E142" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F142" t="s">
-        <v>428</v>
+        <v>398</v>
       </c>
       <c r="H142">
         <v>0</v>
@@ -8008,22 +8028,22 @@
     </row>
     <row r="143" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B143" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C143">
         <v>0</v>
       </c>
       <c r="D143" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E143" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F143" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="H143">
         <v>0</v>
@@ -8041,22 +8061,22 @@
     </row>
     <row r="144" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A144" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B144" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="C144">
         <v>0</v>
       </c>
       <c r="D144" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="E144" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="F144" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="H144">
         <v>2</v>
@@ -8074,22 +8094,22 @@
     </row>
     <row r="145" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B145" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="C145">
         <v>2</v>
       </c>
       <c r="D145" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="E145" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="F145" t="s">
-        <v>424</v>
+        <v>394</v>
       </c>
       <c r="H145">
         <v>1</v>
@@ -8110,22 +8130,22 @@
     </row>
     <row r="146" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A146" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B146" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C146">
         <v>0</v>
       </c>
       <c r="D146" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="E146" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="F146" t="s">
-        <v>288</v>
+        <v>491</v>
       </c>
       <c r="H146">
         <v>0</v>
@@ -8143,22 +8163,22 @@
     </row>
     <row r="147" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B147" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="C147">
         <v>0</v>
       </c>
       <c r="D147" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="E147" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="F147" t="s">
-        <v>502</v>
+        <v>455</v>
       </c>
       <c r="H147">
         <v>0</v>
@@ -8176,22 +8196,22 @@
     </row>
     <row r="148" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="B148" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C148">
         <v>0</v>
       </c>
       <c r="D148" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="E148" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="F148" t="s">
-        <v>334</v>
+        <v>508</v>
       </c>
       <c r="H148">
         <v>0</v>
@@ -8215,22 +8235,22 @@
     </row>
     <row r="149" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="B149" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="C149">
         <v>3</v>
       </c>
       <c r="D149" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="E149" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="F149" t="s">
-        <v>361</v>
+        <v>343</v>
       </c>
       <c r="H149">
         <v>0</v>
@@ -8248,27 +8268,27 @@
     </row>
     <row r="150" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A150" s="4" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="B150" t="s">
-        <v>298</v>
+        <v>477</v>
       </c>
       <c r="C150">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D150" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="E150" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="F150" t="s">
-        <v>316</v>
+        <v>463</v>
       </c>
       <c r="H150">
         <v>0</v>
       </c>
-      <c r="J150">
+      <c r="L150">
         <v>1</v>
       </c>
       <c r="P150">
@@ -8281,22 +8301,22 @@
     </row>
     <row r="151" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A151" s="4" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="B151" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="C151">
         <v>0</v>
       </c>
       <c r="D151" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="E151" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="F151" t="s">
-        <v>335</v>
+        <v>509</v>
       </c>
       <c r="H151">
         <v>0</v>
@@ -8320,22 +8340,22 @@
     </row>
     <row r="152" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A152" s="4" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="B152" t="s">
-        <v>417</v>
+        <v>387</v>
       </c>
       <c r="C152">
         <v>3</v>
       </c>
       <c r="D152" t="s">
-        <v>394</v>
+        <v>368</v>
       </c>
       <c r="E152" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="F152" t="s">
-        <v>427</v>
+        <v>397</v>
       </c>
       <c r="H152">
         <v>0</v>
@@ -8357,7 +8377,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8A19A05-2163-4188-81D2-4CFBD35C3367}">
-  <dimension ref="A1:AJ17"/>
+  <dimension ref="A1:AJ18"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.3">
@@ -8374,10 +8394,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F1" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="G1" t="s">
         <v>4</v>
@@ -8392,7 +8412,7 @@
         <v>7</v>
       </c>
       <c r="K1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L1" t="s">
         <v>8</v>
@@ -8404,75 +8424,75 @@
         <v>80</v>
       </c>
       <c r="O1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="Q1" t="s">
+        <v>138</v>
+      </c>
+      <c r="R1" t="s">
+        <v>139</v>
+      </c>
+      <c r="S1" t="s">
         <v>140</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
+        <v>172</v>
+      </c>
+      <c r="U1" t="s">
         <v>141</v>
       </c>
-      <c r="S1" t="s">
+      <c r="V1" t="s">
         <v>142</v>
       </c>
-      <c r="T1" t="s">
-        <v>174</v>
-      </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>143</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>144</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>145</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>146</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>147</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" t="s">
         <v>148</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
+        <v>151</v>
+      </c>
+      <c r="AD1" t="s">
         <v>149</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AE1" t="s">
+        <v>173</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>286</v>
+      </c>
+      <c r="AG1" t="s">
         <v>150</v>
       </c>
-      <c r="AC1" t="s">
-        <v>153</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>151</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>175</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>292</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>152</v>
-      </c>
       <c r="AH1" t="s">
+        <v>158</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>159</v>
+      </c>
+      <c r="AJ1" t="s">
         <v>160</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>161</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -8481,10 +8501,10 @@
         <v>67</v>
       </c>
       <c r="E2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -8502,7 +8522,7 @@
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -8511,10 +8531,10 @@
         <v>67</v>
       </c>
       <c r="E3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="L3">
         <v>1</v>
@@ -8532,7 +8552,7 @@
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -8541,10 +8561,10 @@
         <v>82</v>
       </c>
       <c r="E4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F4" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="G4" t="s">
         <v>83</v>
@@ -8568,19 +8588,19 @@
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="E5" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="F5" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -8595,10 +8615,10 @@
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B6" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -8607,10 +8627,10 @@
         <v>82</v>
       </c>
       <c r="E6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F6" t="s">
-        <v>347</v>
+        <v>332</v>
       </c>
       <c r="G6" t="s">
         <v>64</v>
@@ -8634,22 +8654,22 @@
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B7" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="F7" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -8670,10 +8690,10 @@
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B8" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -8682,10 +8702,10 @@
         <v>67</v>
       </c>
       <c r="E8" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F8" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -8703,10 +8723,10 @@
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B9" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -8715,10 +8735,10 @@
         <v>70</v>
       </c>
       <c r="E9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F9" t="s">
-        <v>352</v>
+        <v>335</v>
       </c>
       <c r="H9">
         <v>2</v>
@@ -8736,7 +8756,7 @@
         <v>34</v>
       </c>
       <c r="B10" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -8745,10 +8765,10 @@
         <v>70</v>
       </c>
       <c r="E10" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F10" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H10">
         <v>6</v>
@@ -8769,50 +8789,50 @@
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C12" t="s">
         <v>122</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>123</v>
-      </c>
-      <c r="D12" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="C13" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="D13" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B15" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C15">
         <v>2</v>
       </c>
       <c r="D15" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E15" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F15" t="s">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="G15" t="s">
         <v>62</v>
@@ -8833,7 +8853,7 @@
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B16" t="s">
         <v>55</v>
@@ -8845,10 +8865,10 @@
         <v>12</v>
       </c>
       <c r="E16" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F16" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="G16" t="s">
         <v>21</v>
@@ -8875,25 +8895,25 @@
     </row>
     <row r="17" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B17" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C17">
         <v>3</v>
       </c>
       <c r="D17" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E17" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="F17" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="G17" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="H17">
         <v>-12</v>
@@ -8912,6 +8932,39 @@
         <v>1</v>
       </c>
       <c r="AH17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="B18" t="s">
+        <v>308</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18" t="s">
+        <v>139</v>
+      </c>
+      <c r="F18" t="s">
+        <v>178</v>
+      </c>
+      <c r="H18">
+        <v>3</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="P18">
+        <f t="shared" ref="P18" si="1">SUM(Q18:AE18)</f>
+        <v>1</v>
+      </c>
+      <c r="R18">
         <v>1</v>
       </c>
     </row>
@@ -8933,245 +8986,246 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" t="s">
         <v>106</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>107</v>
-      </c>
-      <c r="D1" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D2" t="s">
         <v>109</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D2" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C3" t="s">
         <v>114</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>115</v>
-      </c>
-      <c r="D3" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C4" t="s">
         <v>117</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>118</v>
-      </c>
-      <c r="D4" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D5" t="s">
         <v>120</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C5" t="s">
-        <v>125</v>
-      </c>
-      <c r="D5" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>125</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C6" t="s">
         <v>126</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>127</v>
-      </c>
-      <c r="D6" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>128</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C7" t="s">
         <v>129</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>130</v>
-      </c>
-      <c r="D7" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>354</v>
+        <v>337</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="C8" t="s">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="D8" t="s">
-        <v>435</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>437</v>
+        <v>407</v>
       </c>
       <c r="C9" t="s">
-        <v>497</v>
+        <v>450</v>
       </c>
       <c r="D9" t="s">
-        <v>438</v>
+        <v>408</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>437</v>
+        <v>407</v>
       </c>
       <c r="C10" t="s">
-        <v>497</v>
+        <v>450</v>
       </c>
       <c r="D10" t="s">
-        <v>438</v>
+        <v>408</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>374</v>
+        <v>354</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>375</v>
+        <v>355</v>
       </c>
       <c r="C11" t="s">
-        <v>376</v>
+        <v>356</v>
       </c>
       <c r="D11" t="s">
-        <v>377</v>
+        <v>357</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C12" t="s">
-        <v>495</v>
+        <v>448</v>
       </c>
       <c r="D12" t="s">
-        <v>496</v>
+        <v>449</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="C13" t="s">
-        <v>378</v>
+        <v>358</v>
       </c>
       <c r="D13" t="s">
-        <v>381</v>
+        <v>467</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="C14" t="s">
-        <v>379</v>
+        <v>359</v>
       </c>
       <c r="D14" t="s">
-        <v>382</v>
+        <v>468</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="C15" t="s">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="D15" t="s">
-        <v>383</v>
+        <v>469</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>357</v>
+        <v>340</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="C16" t="s">
-        <v>498</v>
+        <v>451</v>
       </c>
       <c r="D16" t="s">
-        <v>436</v>
+        <v>406</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>431</v>
+        <v>401</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>432</v>
+        <v>402</v>
       </c>
       <c r="C17" t="s">
-        <v>434</v>
+        <v>404</v>
       </c>
       <c r="D17" t="s">
-        <v>433</v>
+        <v>403</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -9185,16 +9239,16 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E1">
         <v>1</v>
@@ -9217,7 +9271,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -9226,30 +9280,30 @@
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>373</v>
+        <v>353</v>
       </c>
       <c r="E2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="J2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -9258,27 +9312,27 @@
         <v>6</v>
       </c>
       <c r="E3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F3" t="s">
+        <v>195</v>
+      </c>
+      <c r="G3" t="s">
+        <v>199</v>
+      </c>
+      <c r="H3" t="s">
+        <v>196</v>
+      </c>
+      <c r="I3" t="s">
         <v>197</v>
       </c>
-      <c r="F3" t="s">
+      <c r="J3" t="s">
         <v>197</v>
-      </c>
-      <c r="G3" t="s">
-        <v>201</v>
-      </c>
-      <c r="H3" t="s">
-        <v>198</v>
-      </c>
-      <c r="I3" t="s">
-        <v>199</v>
-      </c>
-      <c r="J3" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -9287,27 +9341,27 @@
         <v>5</v>
       </c>
       <c r="E4" t="s">
+        <v>195</v>
+      </c>
+      <c r="F4" t="s">
+        <v>195</v>
+      </c>
+      <c r="G4" t="s">
+        <v>194</v>
+      </c>
+      <c r="H4" t="s">
+        <v>194</v>
+      </c>
+      <c r="I4" t="s">
+        <v>199</v>
+      </c>
+      <c r="J4" t="s">
         <v>196</v>
-      </c>
-      <c r="F4" t="s">
-        <v>196</v>
-      </c>
-      <c r="G4" t="s">
-        <v>197</v>
-      </c>
-      <c r="H4" t="s">
-        <v>201</v>
-      </c>
-      <c r="I4" t="s">
-        <v>198</v>
-      </c>
-      <c r="J4" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -9316,27 +9370,27 @@
         <v>7</v>
       </c>
       <c r="E5" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F5" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H5" t="s">
+        <v>199</v>
+      </c>
+      <c r="I5" t="s">
+        <v>199</v>
+      </c>
+      <c r="J5" t="s">
         <v>196</v>
-      </c>
-      <c r="H5" t="s">
-        <v>201</v>
-      </c>
-      <c r="I5" t="s">
-        <v>201</v>
-      </c>
-      <c r="J5" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>204</v>
+        <v>510</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -9345,22 +9399,22 @@
         <v>5</v>
       </c>
       <c r="E6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F6" t="s">
+        <v>195</v>
+      </c>
+      <c r="G6" t="s">
+        <v>194</v>
+      </c>
+      <c r="H6" t="s">
         <v>197</v>
       </c>
-      <c r="F6" t="s">
+      <c r="I6" t="s">
         <v>196</v>
       </c>
-      <c r="G6" t="s">
-        <v>199</v>
-      </c>
-      <c r="H6" t="s">
-        <v>199</v>
-      </c>
-      <c r="I6" t="s">
-        <v>198</v>
-      </c>
       <c r="J6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>

--- a/card_design.xlsx
+++ b/card_design.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\life\board_game\project_six_dynasty\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3802D31B-3439-4055-81A7-D42DBA793E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50AB68B4-DE26-4894-AB58-704670847573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="811" xr2:uid="{F283CFD4-9FFB-4A79-AF0F-7443CC209F7A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1061" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1067" uniqueCount="512">
   <si>
     <t>归属</t>
   </si>
@@ -988,10 +988,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>选择一项：将[关中]的1个地点转化为中立占据，然后将此牌洗回牌库；或者支付5军力，存档此牌。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>卫夫人</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1204,10 +1200,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>选择一项：将[江南]或[荆襄]的1个地点转化为中立占据，然后将此牌洗回牌库；或者支付4军力，存档此牌。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>6/16</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1368,10 +1360,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>强制：选择1个[玄学]区域的地点，转为中立控制。摸1张牌。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>被动：当你的[威望]是并列最高时，也可以执行[僭越]效果。每次执行[僭越]效果时，获得X vp，X=你的[权谋]标记数。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1464,10 +1452,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>行动：传播1次[玄学]。获得X vp，X=存档区牌数。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>选择1个东晋玩家，该玩家失去1军力。然后，获得1军力。[僭越]存档此牌，获得1军力。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1564,10 +1548,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>选择一项：将[巴蜀]区域的1个地点转为中立占据，然后将此牌洗回牌库；或者支付3军力，然后存档此牌。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>世说新语</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1888,10 +1868,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>行动：3军力，存档此牌。被动：此牌在朝堂区中时，使用快速行动执行[进军]时，费用减1。使用快速行动执行[占据]时，费用加1或支付2vp。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>行动：转化1个相邻中立地点，然后可以打出1张幕僚牌。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1964,10 +1940,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>主动：支付1军力，提高1级顺位等级。被动：需要[儒学]等级&gt;1，才能打出。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>被动：结算[僭越]效果时，获得3vp。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -2005,6 +1977,38 @@
   </si>
   <si>
     <t>中庸</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动：3军力，存档此牌。被动：每回合前3次[进军]时，费用减1。区域奖励改为0/1vp。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动：选择1个东晋玩家，给予其1张手牌。传播1次文化，转化1个相邻中立地点。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动：传播1次[玄学]。打出1张不含[军事]标记的手牌。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择一项：将[关中]的1个未加固地点转化为中立占据，然后将此牌洗回牌库；或者支付5军力，存档此牌。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>强制：选择1个[玄学]区域的未加固地点，转为中立控制。摸1张牌。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择一项：将[江南]或[荆襄]的1个未加固地点转化为中立占据，然后将此牌洗回牌库；或者支付4军力，存档此牌。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择一项：将[巴蜀]区域的1个未加固地点转为中立占据，然后将此牌洗回牌库；或者支付3军力，然后存档此牌。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>主动：支付1军力1vp，提高1级顺位等级。被动：需要[儒学]等级&gt;0，才能打出。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -3109,7 +3113,7 @@
         <v>173</v>
       </c>
       <c r="AF1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AG1" t="s">
         <v>150</v>
@@ -3138,7 +3142,7 @@
       </c>
       <c r="J2">
         <f t="shared" si="0"/>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K2">
         <f t="shared" si="0"/>
@@ -3264,7 +3268,7 @@
         <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="P3">
         <f>SUM(Q3:AE3)</f>
@@ -3294,7 +3298,10 @@
         <v>17</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
       </c>
       <c r="P4">
         <f>SUM(Q4:AE4)</f>
@@ -3306,25 +3313,25 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="E5" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="F5" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="G5" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -3350,10 +3357,10 @@
         <v>63</v>
       </c>
       <c r="G6" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L6">
         <v>1</v>
@@ -3380,13 +3387,13 @@
         <v>169</v>
       </c>
       <c r="F7" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="G7" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L7">
         <v>1</v>
@@ -3413,7 +3420,7 @@
         <v>169</v>
       </c>
       <c r="F8" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="G8" t="s">
         <v>62</v>
@@ -3446,10 +3453,10 @@
         <v>169</v>
       </c>
       <c r="F9" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="G9" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -3470,7 +3477,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -3482,10 +3489,10 @@
         <v>169</v>
       </c>
       <c r="F10" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="G10" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="H10">
         <v>-9</v>
@@ -3515,7 +3522,7 @@
         <v>170</v>
       </c>
       <c r="F11" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="L11">
         <v>1</v>
@@ -3542,10 +3549,10 @@
         <v>138</v>
       </c>
       <c r="F12" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="H12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -3575,10 +3582,10 @@
         <v>140</v>
       </c>
       <c r="F13" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="H13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L13">
         <v>1</v>
@@ -3608,10 +3615,10 @@
         <v>143</v>
       </c>
       <c r="F14" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="G14" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="H14">
         <v>-6</v>
@@ -3644,7 +3651,7 @@
         <v>170</v>
       </c>
       <c r="F15" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -3662,7 +3669,7 @@
         <v>29</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" t="s">
         <v>12</v>
@@ -3671,10 +3678,10 @@
         <v>143</v>
       </c>
       <c r="F16" t="s">
-        <v>476</v>
+        <v>505</v>
       </c>
       <c r="G16" t="s">
-        <v>342</v>
+        <v>447</v>
       </c>
       <c r="H16">
         <v>2</v>
@@ -3710,10 +3717,10 @@
         <v>141</v>
       </c>
       <c r="F17" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="G17" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="H17">
         <v>-12</v>
@@ -3746,10 +3753,10 @@
         <v>138</v>
       </c>
       <c r="F18" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="H18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L18">
         <v>1</v>
@@ -3779,7 +3786,7 @@
         <v>170</v>
       </c>
       <c r="F19" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -3797,7 +3804,7 @@
         <v>33</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" t="s">
         <v>12</v>
@@ -3806,7 +3813,7 @@
         <v>143</v>
       </c>
       <c r="F20" t="s">
-        <v>481</v>
+        <v>504</v>
       </c>
       <c r="G20" t="s">
         <v>62</v>
@@ -3845,10 +3852,10 @@
         <v>139</v>
       </c>
       <c r="F21" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="H21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L21">
         <v>1</v>
@@ -3878,10 +3885,10 @@
         <v>147</v>
       </c>
       <c r="F22" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H22">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -3911,10 +3918,10 @@
         <v>140</v>
       </c>
       <c r="F23" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="H23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -3944,10 +3951,10 @@
         <v>172</v>
       </c>
       <c r="F24" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="H24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I24">
         <v>1</v>
@@ -3977,10 +3984,10 @@
         <v>205</v>
       </c>
       <c r="F25" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="H25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K25">
         <v>1</v>
@@ -4010,10 +4017,10 @@
         <v>140</v>
       </c>
       <c r="F26" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="H26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K26">
         <v>1</v>
@@ -4043,7 +4050,10 @@
         <v>146</v>
       </c>
       <c r="F27" t="s">
-        <v>458</v>
+        <v>453</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -4073,7 +4083,7 @@
         <v>171</v>
       </c>
       <c r="F28" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="K28">
         <v>1</v>
@@ -4100,13 +4110,13 @@
         <v>172</v>
       </c>
       <c r="F29" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="G29" t="s">
         <v>14</v>
       </c>
       <c r="H29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I29">
         <v>1</v>
@@ -4136,13 +4146,13 @@
         <v>140</v>
       </c>
       <c r="F30" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="G30" t="s">
         <v>14</v>
       </c>
       <c r="H30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K30">
         <v>1</v>
@@ -4172,7 +4182,7 @@
         <v>224</v>
       </c>
       <c r="F31" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="G31" t="s">
         <v>213</v>
@@ -4211,7 +4221,7 @@
         <v>171</v>
       </c>
       <c r="F32" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="I32">
         <v>1</v>
@@ -4238,10 +4248,10 @@
         <v>138</v>
       </c>
       <c r="F33" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="H33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -4271,13 +4281,13 @@
         <v>172</v>
       </c>
       <c r="F34" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="G34" t="s">
         <v>14</v>
       </c>
       <c r="H34">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I34">
         <v>1</v>
@@ -4307,7 +4317,7 @@
         <v>148</v>
       </c>
       <c r="F35" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="G35" t="s">
         <v>14</v>
@@ -4343,7 +4353,7 @@
         <v>171</v>
       </c>
       <c r="F36" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="L36">
         <v>1</v>
@@ -4370,10 +4380,10 @@
         <v>139</v>
       </c>
       <c r="F37" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="H37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L37">
         <v>1</v>
@@ -4403,10 +4413,10 @@
         <v>141</v>
       </c>
       <c r="F38" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="G38" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="H38">
         <v>-9</v>
@@ -4439,7 +4449,7 @@
         <v>217</v>
       </c>
       <c r="F39" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="H39">
         <v>0</v>
@@ -4472,7 +4482,7 @@
         <v>171</v>
       </c>
       <c r="F40" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I40">
         <v>1</v>
@@ -4499,7 +4509,7 @@
         <v>147</v>
       </c>
       <c r="F41" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G41" t="s">
         <v>14</v>
@@ -4538,10 +4548,10 @@
         <v>141</v>
       </c>
       <c r="F42" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="G42" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="H42">
         <v>-12</v>
@@ -4574,10 +4584,10 @@
         <v>138</v>
       </c>
       <c r="F43" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J43">
         <v>1</v>
@@ -4607,7 +4617,7 @@
         <v>171</v>
       </c>
       <c r="F44" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="K44">
         <v>1</v>
@@ -4634,7 +4644,7 @@
         <v>148</v>
       </c>
       <c r="F45" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="H45">
         <v>0</v>
@@ -4667,10 +4677,10 @@
         <v>138</v>
       </c>
       <c r="F46" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="H46">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J46">
         <v>1</v>
@@ -4700,7 +4710,7 @@
         <v>173</v>
       </c>
       <c r="F47" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="H47">
         <v>4</v>
@@ -4739,7 +4749,7 @@
         <v>171</v>
       </c>
       <c r="F48" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="J48">
         <v>1</v>
@@ -4766,10 +4776,10 @@
         <v>138</v>
       </c>
       <c r="F49" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="H49">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J49">
         <v>1</v>
@@ -4799,13 +4809,13 @@
         <v>139</v>
       </c>
       <c r="F50" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="G50" t="s">
         <v>14</v>
       </c>
       <c r="H50">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L50">
         <v>1</v>
@@ -4835,10 +4845,10 @@
         <v>141</v>
       </c>
       <c r="F51" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="G51" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="H51">
         <v>-9</v>
@@ -4877,7 +4887,7 @@
         <v>171</v>
       </c>
       <c r="F52" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="J52">
         <v>1</v>
@@ -4904,10 +4914,10 @@
         <v>146</v>
       </c>
       <c r="F53" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="H53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J53">
         <v>1</v>
@@ -4940,10 +4950,10 @@
         <v>140</v>
       </c>
       <c r="F54" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K54">
         <v>1</v>
@@ -4976,7 +4986,7 @@
         <v>68</v>
       </c>
       <c r="H55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J55">
         <v>1</v>
@@ -4991,10 +5001,10 @@
     </row>
     <row r="56" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B56" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C56" t="s">
         <v>14</v>
@@ -5006,7 +5016,7 @@
         <v>171</v>
       </c>
       <c r="F56" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="L56">
         <v>1</v>
@@ -5018,7 +5028,7 @@
     </row>
     <row r="57" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B57" t="s">
         <v>97</v>
@@ -5036,7 +5046,7 @@
         <v>98</v>
       </c>
       <c r="H57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57">
         <v>1</v>
@@ -5051,7 +5061,7 @@
     </row>
     <row r="58" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B58" t="s">
         <v>101</v>
@@ -5066,10 +5076,10 @@
         <v>141</v>
       </c>
       <c r="F58" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G58" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="H58">
         <v>-9</v>
@@ -5087,7 +5097,7 @@
     </row>
     <row r="59" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B59" t="s">
         <v>99</v>
@@ -5102,10 +5112,10 @@
         <v>138</v>
       </c>
       <c r="F59" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="H59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J59">
         <v>1</v>
@@ -5120,10 +5130,10 @@
     </row>
     <row r="60" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B60" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -5135,7 +5145,7 @@
         <v>149</v>
       </c>
       <c r="F60" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="H60">
         <v>0</v>
@@ -5150,7 +5160,7 @@
     </row>
     <row r="61" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B61" t="s">
         <v>59</v>
@@ -5165,7 +5175,7 @@
         <v>149</v>
       </c>
       <c r="F61" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="H61">
         <v>0</v>
@@ -5180,7 +5190,7 @@
     </row>
     <row r="62" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B62" t="s">
         <v>60</v>
@@ -5210,10 +5220,10 @@
     </row>
     <row r="63" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B63" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -5225,7 +5235,7 @@
         <v>149</v>
       </c>
       <c r="F63" t="s">
-        <v>351</v>
+        <v>508</v>
       </c>
       <c r="H63">
         <v>0</v>
@@ -5243,10 +5253,10 @@
     </row>
     <row r="64" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B64" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -5258,7 +5268,7 @@
         <v>220</v>
       </c>
       <c r="F64" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="H64">
         <v>0</v>
@@ -5273,22 +5283,22 @@
     </row>
     <row r="65" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B65" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C65">
         <v>0</v>
       </c>
       <c r="D65" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="E65" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="F65" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="H65">
         <v>0</v>
@@ -5309,7 +5319,7 @@
     </row>
     <row r="66" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B66" t="s">
         <v>61</v>
@@ -5324,7 +5334,7 @@
         <v>147</v>
       </c>
       <c r="F66" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H66">
         <v>9</v>
@@ -5342,7 +5352,7 @@
     </row>
     <row r="67" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B67" t="s">
         <v>86</v>
@@ -5357,10 +5367,10 @@
         <v>147</v>
       </c>
       <c r="F67" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="H67">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J67">
         <v>1</v>
@@ -5375,7 +5385,7 @@
     </row>
     <row r="68" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B68" t="s">
         <v>87</v>
@@ -5390,10 +5400,10 @@
         <v>147</v>
       </c>
       <c r="F68" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="H68">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J68">
         <v>1</v>
@@ -5408,7 +5418,7 @@
     </row>
     <row r="69" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B69" t="s">
         <v>103</v>
@@ -5423,7 +5433,7 @@
         <v>147</v>
       </c>
       <c r="F69" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="H69">
         <v>7</v>
@@ -5447,25 +5457,25 @@
     </row>
     <row r="70" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B70" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C70">
         <v>2</v>
       </c>
       <c r="D70" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E70" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F70" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="H70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I70">
         <v>1</v>
@@ -5483,25 +5493,25 @@
     </row>
     <row r="71" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B71" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C71">
         <v>3</v>
       </c>
       <c r="D71" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E71" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F71" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="H71">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I71">
         <v>1</v>
@@ -5516,25 +5526,25 @@
     </row>
     <row r="72" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B72" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C72">
         <v>2</v>
       </c>
       <c r="D72" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E72" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F72" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H72">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I72">
         <v>1</v>
@@ -5549,25 +5559,25 @@
     </row>
     <row r="73" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B73" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C73">
         <v>2</v>
       </c>
       <c r="D73" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E73" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F73" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="H73">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I73">
         <v>1</v>
@@ -5582,7 +5592,7 @@
     </row>
     <row r="74" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B74" t="s">
         <v>72</v>
@@ -5615,7 +5625,7 @@
     </row>
     <row r="75" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B75" t="s">
         <v>152</v>
@@ -5630,10 +5640,10 @@
         <v>138</v>
       </c>
       <c r="F75" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H75">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J75">
         <v>1</v>
@@ -5648,7 +5658,7 @@
     </row>
     <row r="76" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B76" t="s">
         <v>154</v>
@@ -5663,10 +5673,10 @@
         <v>138</v>
       </c>
       <c r="F76" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H76">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K76">
         <v>1</v>
@@ -5681,7 +5691,7 @@
     </row>
     <row r="77" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B77" t="s">
         <v>73</v>
@@ -5696,10 +5706,10 @@
         <v>144</v>
       </c>
       <c r="F77" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="H77">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I77">
         <v>1</v>
@@ -5717,7 +5727,7 @@
     </row>
     <row r="78" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B78" t="s">
         <v>74</v>
@@ -5732,10 +5742,10 @@
         <v>144</v>
       </c>
       <c r="F78" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="H78">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I78">
         <v>1</v>
@@ -5753,7 +5763,7 @@
     </row>
     <row r="79" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B79" t="s">
         <v>75</v>
@@ -5768,10 +5778,10 @@
         <v>144</v>
       </c>
       <c r="F79" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="H79">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I79">
         <v>1</v>
@@ -5786,7 +5796,7 @@
     </row>
     <row r="80" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B80" t="s">
         <v>85</v>
@@ -5801,10 +5811,10 @@
         <v>144</v>
       </c>
       <c r="F80" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="H80">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I80">
         <v>1</v>
@@ -5819,7 +5829,7 @@
     </row>
     <row r="81" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B81" t="s">
         <v>93</v>
@@ -5855,7 +5865,7 @@
     </row>
     <row r="82" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B82" t="s">
         <v>185</v>
@@ -5870,10 +5880,10 @@
         <v>186</v>
       </c>
       <c r="F82" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H82">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I82">
         <v>1</v>
@@ -5888,7 +5898,7 @@
     </row>
     <row r="83" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B83" t="s">
         <v>249</v>
@@ -5903,10 +5913,10 @@
         <v>244</v>
       </c>
       <c r="F83" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="H83">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I83">
         <v>1</v>
@@ -5924,7 +5934,7 @@
     </row>
     <row r="84" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B84" t="s">
         <v>245</v>
@@ -5939,10 +5949,10 @@
         <v>244</v>
       </c>
       <c r="F84" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="H84">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I84">
         <v>1</v>
@@ -5960,7 +5970,7 @@
     </row>
     <row r="85" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B85" t="s">
         <v>246</v>
@@ -5975,7 +5985,7 @@
         <v>244</v>
       </c>
       <c r="F85" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="H85">
         <v>8</v>
@@ -5993,7 +6003,7 @@
     </row>
     <row r="86" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B86" t="s">
         <v>247</v>
@@ -6008,10 +6018,10 @@
         <v>244</v>
       </c>
       <c r="F86" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="H86">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I86">
         <v>1</v>
@@ -6029,7 +6039,7 @@
     </row>
     <row r="87" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B87" t="s">
         <v>231</v>
@@ -6044,7 +6054,7 @@
         <v>232</v>
       </c>
       <c r="F87" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="G87" t="s">
         <v>83</v>
@@ -6068,7 +6078,7 @@
     </row>
     <row r="88" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B88" t="s">
         <v>233</v>
@@ -6083,10 +6093,10 @@
         <v>142</v>
       </c>
       <c r="F88" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="G88" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="H88">
         <v>-9</v>
@@ -6104,7 +6114,7 @@
     </row>
     <row r="89" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B89" t="s">
         <v>136</v>
@@ -6119,7 +6129,7 @@
         <v>142</v>
       </c>
       <c r="F89" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="G89" t="s">
         <v>83</v>
@@ -6143,7 +6153,7 @@
     </row>
     <row r="90" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B90" t="s">
         <v>161</v>
@@ -6158,10 +6168,10 @@
         <v>142</v>
       </c>
       <c r="F90" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="G90" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="H90">
         <v>-12</v>
@@ -6182,7 +6192,7 @@
     </row>
     <row r="91" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B91" t="s">
         <v>162</v>
@@ -6197,10 +6207,10 @@
         <v>142</v>
       </c>
       <c r="F91" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="G91" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="H91">
         <v>-12</v>
@@ -6221,10 +6231,10 @@
     </row>
     <row r="92" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B92" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C92">
         <v>1</v>
@@ -6236,7 +6246,7 @@
         <v>225</v>
       </c>
       <c r="F92" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="G92" t="s">
         <v>62</v>
@@ -6260,7 +6270,7 @@
     </row>
     <row r="93" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B93" t="s">
         <v>234</v>
@@ -6275,10 +6285,10 @@
         <v>232</v>
       </c>
       <c r="F93" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="G93" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="H93">
         <v>-12</v>
@@ -6296,7 +6306,7 @@
     </row>
     <row r="94" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B94" t="s">
         <v>236</v>
@@ -6311,7 +6321,7 @@
         <v>232</v>
       </c>
       <c r="F94" t="s">
-        <v>375</v>
+        <v>506</v>
       </c>
       <c r="G94" t="s">
         <v>237</v>
@@ -6338,7 +6348,7 @@
     </row>
     <row r="95" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B95" t="s">
         <v>89</v>
@@ -6353,10 +6363,10 @@
         <v>173</v>
       </c>
       <c r="F95" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="H95">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J95">
         <v>1</v>
@@ -6374,7 +6384,7 @@
     </row>
     <row r="96" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B96" t="s">
         <v>90</v>
@@ -6389,7 +6399,7 @@
         <v>173</v>
       </c>
       <c r="F96" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="H96">
         <v>0</v>
@@ -6413,7 +6423,7 @@
     </row>
     <row r="97" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B97" t="s">
         <v>92</v>
@@ -6428,7 +6438,7 @@
         <v>173</v>
       </c>
       <c r="F97" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="H97">
         <v>1</v>
@@ -6452,7 +6462,7 @@
     </row>
     <row r="98" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B98" t="s">
         <v>102</v>
@@ -6467,7 +6477,7 @@
         <v>173</v>
       </c>
       <c r="F98" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="H98">
         <v>0</v>
@@ -6491,22 +6501,22 @@
     </row>
     <row r="99" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B99" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C99">
         <v>0</v>
       </c>
       <c r="D99" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E99" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F99" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="H99">
         <v>3</v>
@@ -6527,22 +6537,22 @@
     </row>
     <row r="100" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B100" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C100">
         <v>0</v>
       </c>
       <c r="D100" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E100" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F100" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H100">
         <v>1</v>
@@ -6563,22 +6573,25 @@
     </row>
     <row r="101" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B101" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C101">
         <v>0</v>
       </c>
       <c r="D101" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="E101" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="F101" t="s">
-        <v>507</v>
+        <v>500</v>
+      </c>
+      <c r="H101">
+        <v>0</v>
       </c>
       <c r="K101">
         <v>1</v>
@@ -6595,22 +6608,22 @@
     </row>
     <row r="102" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B102" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C102">
         <v>0</v>
       </c>
       <c r="D102" t="s">
+        <v>270</v>
+      </c>
+      <c r="E102" t="s">
         <v>271</v>
       </c>
-      <c r="E102" t="s">
-        <v>272</v>
-      </c>
       <c r="F102" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="H102">
         <v>2</v>
@@ -6634,22 +6647,22 @@
     </row>
     <row r="103" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B103" t="s">
+        <v>273</v>
+      </c>
+      <c r="C103">
+        <v>0</v>
+      </c>
+      <c r="D103" t="s">
+        <v>270</v>
+      </c>
+      <c r="E103" t="s">
+        <v>271</v>
+      </c>
+      <c r="F103" t="s">
         <v>274</v>
-      </c>
-      <c r="C103">
-        <v>0</v>
-      </c>
-      <c r="D103" t="s">
-        <v>271</v>
-      </c>
-      <c r="E103" t="s">
-        <v>272</v>
-      </c>
-      <c r="F103" t="s">
-        <v>275</v>
       </c>
       <c r="H103">
         <v>1</v>
@@ -6673,7 +6686,7 @@
     </row>
     <row r="104" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B104" t="s">
         <v>96</v>
@@ -6688,7 +6701,7 @@
         <v>148</v>
       </c>
       <c r="F104" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H104">
         <v>0</v>
@@ -6706,7 +6719,7 @@
     </row>
     <row r="105" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B105" t="s">
         <v>163</v>
@@ -6721,7 +6734,7 @@
         <v>148</v>
       </c>
       <c r="F105" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="H105">
         <v>0</v>
@@ -6739,7 +6752,7 @@
     </row>
     <row r="106" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B106" t="s">
         <v>164</v>
@@ -6748,16 +6761,16 @@
         <v>1</v>
       </c>
       <c r="D106" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="E106" t="s">
         <v>140</v>
       </c>
       <c r="F106" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="H106">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I106">
         <v>1</v>
@@ -6772,7 +6785,7 @@
     </row>
     <row r="107" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B107" t="s">
         <v>155</v>
@@ -6787,7 +6800,7 @@
         <v>145</v>
       </c>
       <c r="F107" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="H107">
         <v>0</v>
@@ -6808,7 +6821,7 @@
     </row>
     <row r="108" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B108" t="s">
         <v>156</v>
@@ -6823,10 +6836,10 @@
         <v>145</v>
       </c>
       <c r="F108" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="H108">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I108">
         <v>1</v>
@@ -6844,7 +6857,7 @@
     </row>
     <row r="109" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B109" t="s">
         <v>253</v>
@@ -6859,7 +6872,7 @@
         <v>252</v>
       </c>
       <c r="F109" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="H109">
         <v>0</v>
@@ -6880,7 +6893,7 @@
     </row>
     <row r="110" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B110" t="s">
         <v>254</v>
@@ -6895,10 +6908,10 @@
         <v>252</v>
       </c>
       <c r="F110" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="H110">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I110">
         <v>1</v>
@@ -6916,7 +6929,7 @@
     </row>
     <row r="111" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B111" t="s">
         <v>251</v>
@@ -6931,10 +6944,10 @@
         <v>182</v>
       </c>
       <c r="F111" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="H111">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I111">
         <v>1</v>
@@ -6949,7 +6962,7 @@
     </row>
     <row r="112" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B112" t="s">
         <v>175</v>
@@ -6964,10 +6977,10 @@
         <v>177</v>
       </c>
       <c r="F112" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H112">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L112">
         <v>1</v>
@@ -6982,10 +6995,10 @@
     </row>
     <row r="113" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B113" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -6997,10 +7010,10 @@
         <v>177</v>
       </c>
       <c r="F113" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H113">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L113">
         <v>1</v>
@@ -7015,7 +7028,7 @@
     </row>
     <row r="114" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B114" t="s">
         <v>180</v>
@@ -7030,10 +7043,10 @@
         <v>177</v>
       </c>
       <c r="F114" t="s">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="H114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L114">
         <v>1</v>
@@ -7051,7 +7064,7 @@
     </row>
     <row r="115" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B115" t="s">
         <v>181</v>
@@ -7066,10 +7079,10 @@
         <v>177</v>
       </c>
       <c r="F115" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="H115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L115">
         <v>1</v>
@@ -7084,10 +7097,10 @@
     </row>
     <row r="116" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B116" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C116">
         <v>1</v>
@@ -7099,10 +7112,10 @@
         <v>183</v>
       </c>
       <c r="F116" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="H116">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I116">
         <v>1</v>
@@ -7117,7 +7130,7 @@
     </row>
     <row r="117" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B117" t="s">
         <v>187</v>
@@ -7132,10 +7145,10 @@
         <v>183</v>
       </c>
       <c r="F117" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="H117">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I117">
         <v>1</v>
@@ -7153,10 +7166,10 @@
     </row>
     <row r="118" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B118" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -7168,10 +7181,10 @@
         <v>140</v>
       </c>
       <c r="F118" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="H118">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I118">
         <v>1</v>
@@ -7186,7 +7199,7 @@
     </row>
     <row r="119" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B119" t="s">
         <v>206</v>
@@ -7201,10 +7214,10 @@
         <v>205</v>
       </c>
       <c r="F119" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="H119">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K119">
         <v>1</v>
@@ -7219,7 +7232,7 @@
     </row>
     <row r="120" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B120" t="s">
         <v>209</v>
@@ -7234,7 +7247,7 @@
         <v>211</v>
       </c>
       <c r="F120" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="G120" t="s">
         <v>62</v>
@@ -7255,7 +7268,7 @@
     </row>
     <row r="121" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B121" t="s">
         <v>212</v>
@@ -7270,7 +7283,7 @@
         <v>211</v>
       </c>
       <c r="F121" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="G121" t="s">
         <v>62</v>
@@ -7291,10 +7304,10 @@
     </row>
     <row r="122" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B122" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C122">
         <v>3</v>
@@ -7306,10 +7319,10 @@
         <v>141</v>
       </c>
       <c r="F122" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="G122" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="H122">
         <v>-12</v>
@@ -7330,7 +7343,7 @@
     </row>
     <row r="123" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B123" t="s">
         <v>214</v>
@@ -7345,7 +7358,7 @@
         <v>211</v>
       </c>
       <c r="F123" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="G123" t="s">
         <v>213</v>
@@ -7366,10 +7379,10 @@
     </row>
     <row r="124" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B124" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="C124">
         <v>3</v>
@@ -7381,10 +7394,10 @@
         <v>141</v>
       </c>
       <c r="F124" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="G124" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="H124">
         <v>-9</v>
@@ -7402,7 +7415,7 @@
     </row>
     <row r="125" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B125" t="s">
         <v>226</v>
@@ -7417,7 +7430,7 @@
         <v>228</v>
       </c>
       <c r="F125" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="G125" t="s">
         <v>62</v>
@@ -7438,7 +7451,7 @@
     </row>
     <row r="126" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A126" s="4" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="B126" t="s">
         <v>88</v>
@@ -7453,10 +7466,10 @@
         <v>143</v>
       </c>
       <c r="F126" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="G126" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="H126">
         <v>-6</v>
@@ -7474,10 +7487,10 @@
     </row>
     <row r="127" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B127" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C127">
         <v>2</v>
@@ -7489,7 +7502,7 @@
         <v>238</v>
       </c>
       <c r="F127" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="G127" t="s">
         <v>213</v>
@@ -7510,7 +7523,7 @@
     </row>
     <row r="128" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B128" t="s">
         <v>239</v>
@@ -7525,7 +7538,7 @@
         <v>238</v>
       </c>
       <c r="F128" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="G128" t="s">
         <v>235</v>
@@ -7546,25 +7559,25 @@
     </row>
     <row r="129" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B129" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="C129">
         <v>2</v>
       </c>
       <c r="D129" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="E129" t="s">
         <v>143</v>
       </c>
       <c r="F129" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="G129" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="H129">
         <v>-9</v>
@@ -7578,10 +7591,10 @@
     </row>
     <row r="130" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B130" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="C130">
         <v>3</v>
@@ -7593,10 +7606,10 @@
         <v>141</v>
       </c>
       <c r="F130" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="G130" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="H130">
         <v>-9</v>
@@ -7614,7 +7627,7 @@
     </row>
     <row r="131" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B131" t="s">
         <v>242</v>
@@ -7629,7 +7642,7 @@
         <v>238</v>
       </c>
       <c r="F131" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="G131" t="s">
         <v>213</v>
@@ -7650,7 +7663,7 @@
     </row>
     <row r="132" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B132" t="s">
         <v>81</v>
@@ -7665,7 +7678,7 @@
         <v>143</v>
       </c>
       <c r="F132" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="G132" t="s">
         <v>235</v>
@@ -7686,7 +7699,7 @@
     </row>
     <row r="133" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B133" t="s">
         <v>165</v>
@@ -7701,7 +7714,7 @@
         <v>146</v>
       </c>
       <c r="F133" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H133">
         <v>1</v>
@@ -7719,10 +7732,10 @@
     </row>
     <row r="134" spans="1:34" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B134" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="C134">
         <v>3</v>
@@ -7734,10 +7747,10 @@
         <v>248</v>
       </c>
       <c r="F134" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="H134">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J134">
         <v>1</v>
@@ -7755,7 +7768,7 @@
     </row>
     <row r="135" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B135" t="s">
         <v>250</v>
@@ -7770,10 +7783,10 @@
         <v>248</v>
       </c>
       <c r="F135" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="H135">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J135">
         <v>1</v>
@@ -7791,7 +7804,7 @@
     </row>
     <row r="136" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B136" t="s">
         <v>255</v>
@@ -7806,10 +7819,10 @@
         <v>248</v>
       </c>
       <c r="F136" t="s">
-        <v>256</v>
+        <v>507</v>
       </c>
       <c r="H136">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J136">
         <v>1</v>
@@ -7824,10 +7837,10 @@
     </row>
     <row r="137" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B137" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -7839,7 +7852,7 @@
         <v>248</v>
       </c>
       <c r="F137" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="H137">
         <v>0</v>
@@ -7857,10 +7870,10 @@
     </row>
     <row r="138" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B138" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -7872,10 +7885,10 @@
         <v>248</v>
       </c>
       <c r="F138" t="s">
-        <v>310</v>
+        <v>509</v>
       </c>
       <c r="H138">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J138">
         <v>1</v>
@@ -7890,10 +7903,10 @@
     </row>
     <row r="139" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B139" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -7905,7 +7918,7 @@
         <v>248</v>
       </c>
       <c r="F139" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H139">
         <v>0</v>
@@ -7923,10 +7936,10 @@
     </row>
     <row r="140" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A140" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B140" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C140">
         <v>1</v>
@@ -7938,10 +7951,10 @@
         <v>248</v>
       </c>
       <c r="F140" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H140">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J140">
         <v>1</v>
@@ -7956,10 +7969,10 @@
     </row>
     <row r="141" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B141" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -7971,10 +7984,10 @@
         <v>248</v>
       </c>
       <c r="F141" t="s">
-        <v>400</v>
+        <v>510</v>
       </c>
       <c r="H141">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J141">
         <v>1</v>
@@ -7989,10 +8002,10 @@
     </row>
     <row r="142" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B142" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C142">
         <v>1</v>
@@ -8004,7 +8017,7 @@
         <v>248</v>
       </c>
       <c r="F142" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="H142">
         <v>0</v>
@@ -8028,10 +8041,10 @@
     </row>
     <row r="143" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B143" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -8043,7 +8056,7 @@
         <v>248</v>
       </c>
       <c r="F143" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H143">
         <v>0</v>
@@ -8061,25 +8074,25 @@
     </row>
     <row r="144" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A144" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B144" t="s">
+        <v>279</v>
+      </c>
+      <c r="C144">
+        <v>0</v>
+      </c>
+      <c r="D144" t="s">
+        <v>270</v>
+      </c>
+      <c r="E144" t="s">
         <v>280</v>
       </c>
-      <c r="C144">
-        <v>0</v>
-      </c>
-      <c r="D144" t="s">
-        <v>271</v>
-      </c>
-      <c r="E144" t="s">
-        <v>281</v>
-      </c>
       <c r="F144" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="H144">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L144">
         <v>1</v>
@@ -8094,25 +8107,25 @@
     </row>
     <row r="145" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B145" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C145">
         <v>2</v>
       </c>
       <c r="D145" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E145" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F145" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="H145">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L145">
         <v>1</v>
@@ -8130,22 +8143,22 @@
     </row>
     <row r="146" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A146" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B146" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C146">
         <v>0</v>
       </c>
       <c r="D146" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E146" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F146" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="H146">
         <v>0</v>
@@ -8163,22 +8176,22 @@
     </row>
     <row r="147" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B147" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C147">
         <v>0</v>
       </c>
       <c r="D147" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E147" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F147" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="H147">
         <v>0</v>
@@ -8196,22 +8209,22 @@
     </row>
     <row r="148" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B148" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C148">
         <v>0</v>
       </c>
       <c r="D148" t="s">
+        <v>284</v>
+      </c>
+      <c r="E148" t="s">
         <v>285</v>
       </c>
-      <c r="E148" t="s">
-        <v>286</v>
-      </c>
       <c r="F148" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="H148">
         <v>0</v>
@@ -8235,22 +8248,22 @@
     </row>
     <row r="149" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B149" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C149">
         <v>3</v>
       </c>
       <c r="D149" t="s">
+        <v>284</v>
+      </c>
+      <c r="E149" t="s">
         <v>285</v>
       </c>
-      <c r="E149" t="s">
-        <v>286</v>
-      </c>
       <c r="F149" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="H149">
         <v>0</v>
@@ -8268,22 +8281,22 @@
     </row>
     <row r="150" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A150" s="4" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B150" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="C150">
         <v>1</v>
       </c>
       <c r="D150" t="s">
+        <v>284</v>
+      </c>
+      <c r="E150" t="s">
         <v>285</v>
       </c>
-      <c r="E150" t="s">
-        <v>286</v>
-      </c>
       <c r="F150" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="H150">
         <v>0</v>
@@ -8301,22 +8314,22 @@
     </row>
     <row r="151" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A151" s="4" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B151" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C151">
         <v>0</v>
       </c>
       <c r="D151" t="s">
+        <v>284</v>
+      </c>
+      <c r="E151" t="s">
         <v>285</v>
       </c>
-      <c r="E151" t="s">
-        <v>286</v>
-      </c>
       <c r="F151" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H151">
         <v>0</v>
@@ -8340,22 +8353,22 @@
     </row>
     <row r="152" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A152" s="4" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B152" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="C152">
         <v>3</v>
       </c>
       <c r="D152" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="E152" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="F152" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="H152">
         <v>0</v>
@@ -8377,7 +8390,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8A19A05-2163-4188-81D2-4CFBD35C3367}">
-  <dimension ref="A1:AJ18"/>
+  <dimension ref="A1:AJ19"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.3">
@@ -8475,7 +8488,7 @@
         <v>173</v>
       </c>
       <c r="AF1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AG1" t="s">
         <v>150</v>
@@ -8564,7 +8577,7 @@
         <v>143</v>
       </c>
       <c r="F4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G4" t="s">
         <v>83</v>
@@ -8588,19 +8601,19 @@
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
       <c r="D5" t="s">
+        <v>284</v>
+      </c>
+      <c r="E5" t="s">
         <v>285</v>
       </c>
-      <c r="E5" t="s">
-        <v>286</v>
-      </c>
       <c r="F5" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -8615,7 +8628,7 @@
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B6" t="s">
         <v>231</v>
@@ -8630,7 +8643,7 @@
         <v>142</v>
       </c>
       <c r="F6" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G6" t="s">
         <v>64</v>
@@ -8654,10 +8667,10 @@
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -8666,10 +8679,10 @@
         <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -8690,10 +8703,10 @@
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -8705,7 +8718,7 @@
         <v>173</v>
       </c>
       <c r="F8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -8723,10 +8736,10 @@
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -8738,7 +8751,7 @@
         <v>172</v>
       </c>
       <c r="F9" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="H9">
         <v>2</v>
@@ -8806,18 +8819,18 @@
         <v>112</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C13" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D13" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B15" t="s">
         <v>230</v>
@@ -8832,7 +8845,7 @@
         <v>228</v>
       </c>
       <c r="F15" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="G15" t="s">
         <v>62</v>
@@ -8853,7 +8866,7 @@
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B16" t="s">
         <v>55</v>
@@ -8868,7 +8881,7 @@
         <v>143</v>
       </c>
       <c r="F16" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G16" t="s">
         <v>21</v>
@@ -8895,7 +8908,7 @@
     </row>
     <row r="17" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B17" t="s">
         <v>241</v>
@@ -8910,7 +8923,7 @@
         <v>238</v>
       </c>
       <c r="F17" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="G17" t="s">
         <v>213</v>
@@ -8937,10 +8950,10 @@
     </row>
     <row r="18" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B18" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -8961,10 +8974,49 @@
         <v>1</v>
       </c>
       <c r="P18">
-        <f t="shared" ref="P18" si="1">SUM(Q18:AE18)</f>
+        <f t="shared" ref="P18:P19" si="1">SUM(Q18:AE18)</f>
         <v>1</v>
       </c>
       <c r="R18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" t="s">
+        <v>143</v>
+      </c>
+      <c r="F19" t="s">
+        <v>471</v>
+      </c>
+      <c r="G19" t="s">
+        <v>340</v>
+      </c>
+      <c r="H19">
+        <v>2</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="N19">
+        <v>1</v>
+      </c>
+      <c r="P19">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="W19">
         <v>1</v>
       </c>
     </row>
@@ -9017,7 +9069,7 @@
         <v>113</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C3" t="s">
         <v>114</v>
@@ -9031,7 +9083,7 @@
         <v>116</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C4" t="s">
         <v>117</v>
@@ -9059,7 +9111,7 @@
         <v>125</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C6" t="s">
         <v>126</v>
@@ -9073,7 +9125,7 @@
         <v>128</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C7" t="s">
         <v>129</v>
@@ -9084,16 +9136,16 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>335</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>339</v>
-      </c>
       <c r="C8" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D8" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -9101,13 +9153,13 @@
         <v>111</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="C9" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="D9" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -9115,27 +9167,27 @@
         <v>111</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="C10" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="D10" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>351</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C11" t="s">
+        <v>353</v>
+      </c>
+      <c r="D11" t="s">
         <v>354</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="C11" t="s">
-        <v>356</v>
-      </c>
-      <c r="D11" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -9146,10 +9198,10 @@
         <v>131</v>
       </c>
       <c r="C12" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="D12" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -9157,13 +9209,13 @@
         <v>132</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C13" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="D13" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -9171,13 +9223,13 @@
         <v>134</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C14" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="D14" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -9185,41 +9237,41 @@
         <v>135</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C15" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="D15" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C16" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="D16" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="C17" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="D17" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>
@@ -9280,7 +9332,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E2" t="s">
         <v>191</v>
@@ -9390,7 +9442,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="B6">
         <v>1</v>

--- a/card_design.xlsx
+++ b/card_design.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\life\board_game\project_six_dynasty\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50AB68B4-DE26-4894-AB58-704670847573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF582C60-341D-479E-921B-0A9FDF6DE148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="811" xr2:uid="{F283CFD4-9FFB-4A79-AF0F-7443CC209F7A}"/>
   </bookViews>
@@ -1432,10 +1432,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>强制：如果[儒学]区域数&gt;=[玄学]区域数，司马家威望+1；否则司马家威望-1。摸1张牌。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>天师道</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1656,10 +1652,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>主动：弃1张手牌，然后摸1张牌，可以执行1个手牌行动。登场：转化[长安][弘农][安定]（不获得vp）</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>主动：弃1张手牌，然后摸1张牌，可以执行1个牌组行动。登场：转化[蓟][龙城][中山]（不获得vp）</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1760,10 +1752,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>主动：弃1张手牌，然后摸1张牌，获得X军力，X=[军事]标记数（最多6）。登场：转化[盛乐][平城]（不获得vp），获得4军力。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>支付2vp，然后存档1张候选策略牌。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1776,10 +1764,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>幕僚区有空位时，可以打出。获得8军力，然后将此牌洗回牌库。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>主动：获得X vp，X=[文化]标记数。然后，可以支付2vp，摸1张牌。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1980,10 +1964,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>行动：3军力，存档此牌。被动：每回合前3次[进军]时，费用减1。区域奖励改为0/1vp。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>行动：选择1个东晋玩家，给予其1张手牌。传播1次文化，转化1个相邻中立地点。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1992,23 +1972,43 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>选择一项：将[关中]的1个未加固地点转化为中立占据，然后将此牌洗回牌库；或者支付5军力，存档此牌。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>强制：选择1个[玄学]区域的未加固地点，转为中立控制。摸1张牌。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>选择一项：将[江南]或[荆襄]的1个未加固地点转化为中立占据，然后将此牌洗回牌库；或者支付4军力，存档此牌。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>选择一项：将[巴蜀]区域的1个未加固地点转为中立占据，然后将此牌洗回牌库；或者支付3军力，然后存档此牌。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>主动：支付1军力1vp，提高1级顺位等级。被动：需要[儒学]等级&gt;0，才能打出。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>幕僚区有空位时，可以打出。获得8军力。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>主动：弃1张手牌，然后获得X军力，X=[军事]标记数（最多5）。登场：转化[盛乐][平城]（不获得vp），获得4军力。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>主动：弃1张手牌，然后摸1张牌，可以执行1个手牌行动。登场：转化[长安][弘农][安定][平阳]（不获得vp）</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动：3军力，存档此牌。被动：每回合前2次[进军]时，费用减1。区域奖励改为0/1vp。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择一项：将[关中]的1个未加固地点转化为中立占据；或者支付5军力，存档此牌。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择一项：将[江南]或[荆襄]的1个未加固地点转化为中立占据；或者支付4军力，存档此牌。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择一项：将[巴蜀]区域的1个未加固地点转为中立占据；或者支付3军力，然后存档此牌。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>强制：如果[儒学]等级&gt;=[玄学]等级，司马家威望+1；否则司马家威望-1。摸1张牌。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -3268,7 +3268,7 @@
         <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="P3">
         <f>SUM(Q3:AE3)</f>
@@ -3313,22 +3313,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5" t="s">
+        <v>405</v>
+      </c>
+      <c r="E5" t="s">
         <v>406</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>407</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>408</v>
-      </c>
-      <c r="G5" t="s">
-        <v>409</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -3357,7 +3357,7 @@
         <v>63</v>
       </c>
       <c r="G6" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -3387,10 +3387,10 @@
         <v>169</v>
       </c>
       <c r="F7" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="G7" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -3420,7 +3420,7 @@
         <v>169</v>
       </c>
       <c r="F8" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="G8" t="s">
         <v>62</v>
@@ -3453,10 +3453,10 @@
         <v>169</v>
       </c>
       <c r="F9" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="G9" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -3477,7 +3477,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -3489,10 +3489,10 @@
         <v>169</v>
       </c>
       <c r="F10" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G10" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H10">
         <v>-9</v>
@@ -3522,7 +3522,7 @@
         <v>170</v>
       </c>
       <c r="F11" t="s">
-        <v>423</v>
+        <v>506</v>
       </c>
       <c r="L11">
         <v>1</v>
@@ -3549,7 +3549,7 @@
         <v>138</v>
       </c>
       <c r="F12" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="H12">
         <v>7</v>
@@ -3615,10 +3615,10 @@
         <v>143</v>
       </c>
       <c r="F14" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="G14" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H14">
         <v>-6</v>
@@ -3651,7 +3651,7 @@
         <v>170</v>
       </c>
       <c r="F15" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -3678,10 +3678,10 @@
         <v>143</v>
       </c>
       <c r="F16" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="G16" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H16">
         <v>2</v>
@@ -3717,10 +3717,10 @@
         <v>141</v>
       </c>
       <c r="F17" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="G17" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H17">
         <v>-12</v>
@@ -3753,7 +3753,7 @@
         <v>138</v>
       </c>
       <c r="F18" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="H18">
         <v>7</v>
@@ -3786,7 +3786,7 @@
         <v>170</v>
       </c>
       <c r="F19" t="s">
-        <v>449</v>
+        <v>505</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -3813,7 +3813,7 @@
         <v>143</v>
       </c>
       <c r="F20" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="G20" t="s">
         <v>62</v>
@@ -3852,7 +3852,7 @@
         <v>139</v>
       </c>
       <c r="F21" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="H21">
         <v>5</v>
@@ -3918,7 +3918,7 @@
         <v>140</v>
       </c>
       <c r="F23" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H23">
         <v>5</v>
@@ -3951,7 +3951,7 @@
         <v>172</v>
       </c>
       <c r="F24" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="H24">
         <v>5</v>
@@ -3984,7 +3984,7 @@
         <v>205</v>
       </c>
       <c r="F25" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H25">
         <v>3</v>
@@ -4017,7 +4017,7 @@
         <v>140</v>
       </c>
       <c r="F26" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H26">
         <v>3</v>
@@ -4050,7 +4050,7 @@
         <v>146</v>
       </c>
       <c r="F27" t="s">
-        <v>453</v>
+        <v>504</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>172</v>
       </c>
       <c r="F29" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="G29" t="s">
         <v>14</v>
@@ -4182,7 +4182,7 @@
         <v>224</v>
       </c>
       <c r="F31" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="G31" t="s">
         <v>213</v>
@@ -4248,7 +4248,7 @@
         <v>138</v>
       </c>
       <c r="F33" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="H33">
         <v>7</v>
@@ -4281,7 +4281,7 @@
         <v>172</v>
       </c>
       <c r="F34" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="G34" t="s">
         <v>14</v>
@@ -4353,7 +4353,7 @@
         <v>171</v>
       </c>
       <c r="F36" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="L36">
         <v>1</v>
@@ -4380,7 +4380,7 @@
         <v>139</v>
       </c>
       <c r="F37" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="H37">
         <v>3</v>
@@ -4413,10 +4413,10 @@
         <v>141</v>
       </c>
       <c r="F38" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G38" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H38">
         <v>-9</v>
@@ -4548,10 +4548,10 @@
         <v>141</v>
       </c>
       <c r="F42" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="G42" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H42">
         <v>-12</v>
@@ -4617,7 +4617,7 @@
         <v>171</v>
       </c>
       <c r="F44" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="K44">
         <v>1</v>
@@ -4677,7 +4677,7 @@
         <v>138</v>
       </c>
       <c r="F46" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="H46">
         <v>5</v>
@@ -4710,7 +4710,7 @@
         <v>173</v>
       </c>
       <c r="F47" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="H47">
         <v>4</v>
@@ -4749,7 +4749,7 @@
         <v>171</v>
       </c>
       <c r="F48" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="J48">
         <v>1</v>
@@ -4776,7 +4776,7 @@
         <v>138</v>
       </c>
       <c r="F49" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H49">
         <v>7</v>
@@ -4845,10 +4845,10 @@
         <v>141</v>
       </c>
       <c r="F51" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="G51" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H51">
         <v>-9</v>
@@ -4887,7 +4887,7 @@
         <v>171</v>
       </c>
       <c r="F52" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J52">
         <v>1</v>
@@ -4914,7 +4914,7 @@
         <v>146</v>
       </c>
       <c r="F53" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="H53">
         <v>1</v>
@@ -5079,7 +5079,7 @@
         <v>326</v>
       </c>
       <c r="G58" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H58">
         <v>-9</v>
@@ -5112,7 +5112,7 @@
         <v>138</v>
       </c>
       <c r="F59" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H59">
         <v>3</v>
@@ -5145,7 +5145,7 @@
         <v>149</v>
       </c>
       <c r="F60" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="H60">
         <v>0</v>
@@ -5223,7 +5223,7 @@
         <v>342</v>
       </c>
       <c r="B63" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -5235,7 +5235,7 @@
         <v>149</v>
       </c>
       <c r="F63" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="H63">
         <v>0</v>
@@ -5268,7 +5268,7 @@
         <v>220</v>
       </c>
       <c r="F64" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="H64">
         <v>0</v>
@@ -5286,7 +5286,7 @@
         <v>342</v>
       </c>
       <c r="B65" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -5298,7 +5298,7 @@
         <v>366</v>
       </c>
       <c r="F65" t="s">
-        <v>367</v>
+        <v>511</v>
       </c>
       <c r="H65">
         <v>0</v>
@@ -5433,7 +5433,7 @@
         <v>147</v>
       </c>
       <c r="F69" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="H69">
         <v>7</v>
@@ -5508,7 +5508,7 @@
         <v>276</v>
       </c>
       <c r="F71" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="H71">
         <v>15</v>
@@ -5778,7 +5778,7 @@
         <v>144</v>
       </c>
       <c r="F79" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="H79">
         <v>7</v>
@@ -5811,7 +5811,7 @@
         <v>144</v>
       </c>
       <c r="F80" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="H80">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>244</v>
       </c>
       <c r="F85" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="H85">
         <v>8</v>
@@ -6054,7 +6054,7 @@
         <v>232</v>
       </c>
       <c r="F87" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G87" t="s">
         <v>83</v>
@@ -6093,10 +6093,10 @@
         <v>142</v>
       </c>
       <c r="F88" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="G88" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H88">
         <v>-9</v>
@@ -6129,7 +6129,7 @@
         <v>142</v>
       </c>
       <c r="F89" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G89" t="s">
         <v>83</v>
@@ -6168,10 +6168,10 @@
         <v>142</v>
       </c>
       <c r="F90" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G90" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H90">
         <v>-12</v>
@@ -6207,10 +6207,10 @@
         <v>142</v>
       </c>
       <c r="F91" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G91" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="H91">
         <v>-12</v>
@@ -6246,7 +6246,7 @@
         <v>225</v>
       </c>
       <c r="F92" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="G92" t="s">
         <v>62</v>
@@ -6285,10 +6285,10 @@
         <v>232</v>
       </c>
       <c r="F93" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="G93" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="H93">
         <v>-12</v>
@@ -6321,7 +6321,7 @@
         <v>232</v>
       </c>
       <c r="F94" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="G94" t="s">
         <v>237</v>
@@ -6363,7 +6363,7 @@
         <v>173</v>
       </c>
       <c r="F95" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H95">
         <v>1</v>
@@ -6399,7 +6399,7 @@
         <v>173</v>
       </c>
       <c r="F96" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="H96">
         <v>0</v>
@@ -6438,7 +6438,7 @@
         <v>173</v>
       </c>
       <c r="F97" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="H97">
         <v>1</v>
@@ -6477,7 +6477,7 @@
         <v>173</v>
       </c>
       <c r="F98" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="H98">
         <v>0</v>
@@ -6516,7 +6516,7 @@
         <v>317</v>
       </c>
       <c r="F99" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="H99">
         <v>3</v>
@@ -6540,7 +6540,7 @@
         <v>342</v>
       </c>
       <c r="B100" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -6552,7 +6552,7 @@
         <v>288</v>
       </c>
       <c r="F100" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H100">
         <v>1</v>
@@ -6576,7 +6576,7 @@
         <v>342</v>
       </c>
       <c r="B101" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -6585,10 +6585,10 @@
         <v>365</v>
       </c>
       <c r="E101" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F101" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="H101">
         <v>0</v>
@@ -6623,7 +6623,7 @@
         <v>271</v>
       </c>
       <c r="F102" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="H102">
         <v>2</v>
@@ -6701,7 +6701,7 @@
         <v>148</v>
       </c>
       <c r="F104" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H104">
         <v>0</v>
@@ -6734,7 +6734,7 @@
         <v>148</v>
       </c>
       <c r="F105" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H105">
         <v>0</v>
@@ -6761,13 +6761,13 @@
         <v>1</v>
       </c>
       <c r="D106" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E106" t="s">
         <v>140</v>
       </c>
       <c r="F106" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="H106">
         <v>3</v>
@@ -6800,7 +6800,7 @@
         <v>145</v>
       </c>
       <c r="F107" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H107">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>145</v>
       </c>
       <c r="F108" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="H108">
         <v>5</v>
@@ -6872,7 +6872,7 @@
         <v>252</v>
       </c>
       <c r="F109" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H109">
         <v>0</v>
@@ -6908,7 +6908,7 @@
         <v>252</v>
       </c>
       <c r="F110" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H110">
         <v>6</v>
@@ -6944,7 +6944,7 @@
         <v>182</v>
       </c>
       <c r="F111" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H111">
         <v>6</v>
@@ -7043,7 +7043,7 @@
         <v>177</v>
       </c>
       <c r="F114" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="H114">
         <v>1</v>
@@ -7079,7 +7079,7 @@
         <v>177</v>
       </c>
       <c r="F115" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="H115">
         <v>1</v>
@@ -7112,7 +7112,7 @@
         <v>183</v>
       </c>
       <c r="F116" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H116">
         <v>3</v>
@@ -7145,7 +7145,7 @@
         <v>183</v>
       </c>
       <c r="F117" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H117">
         <v>3</v>
@@ -7181,7 +7181,7 @@
         <v>140</v>
       </c>
       <c r="F118" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H118">
         <v>1</v>
@@ -7214,7 +7214,7 @@
         <v>205</v>
       </c>
       <c r="F119" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="H119">
         <v>3</v>
@@ -7283,7 +7283,7 @@
         <v>211</v>
       </c>
       <c r="F121" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="G121" t="s">
         <v>62</v>
@@ -7307,7 +7307,7 @@
         <v>342</v>
       </c>
       <c r="B122" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C122">
         <v>3</v>
@@ -7319,10 +7319,10 @@
         <v>141</v>
       </c>
       <c r="F122" t="s">
+        <v>386</v>
+      </c>
+      <c r="G122" t="s">
         <v>387</v>
-      </c>
-      <c r="G122" t="s">
-        <v>388</v>
       </c>
       <c r="H122">
         <v>-12</v>
@@ -7358,7 +7358,7 @@
         <v>211</v>
       </c>
       <c r="F123" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="G123" t="s">
         <v>213</v>
@@ -7382,7 +7382,7 @@
         <v>342</v>
       </c>
       <c r="B124" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C124">
         <v>3</v>
@@ -7394,10 +7394,10 @@
         <v>141</v>
       </c>
       <c r="F124" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="G124" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H124">
         <v>-9</v>
@@ -7430,7 +7430,7 @@
         <v>228</v>
       </c>
       <c r="F125" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="G125" t="s">
         <v>62</v>
@@ -7451,7 +7451,7 @@
     </row>
     <row r="126" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A126" s="4" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B126" t="s">
         <v>88</v>
@@ -7466,10 +7466,10 @@
         <v>143</v>
       </c>
       <c r="F126" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="G126" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H126">
         <v>-6</v>
@@ -7502,7 +7502,7 @@
         <v>238</v>
       </c>
       <c r="F127" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="G127" t="s">
         <v>213</v>
@@ -7538,7 +7538,7 @@
         <v>238</v>
       </c>
       <c r="F128" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="G128" t="s">
         <v>235</v>
@@ -7562,22 +7562,22 @@
         <v>342</v>
       </c>
       <c r="B129" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C129">
         <v>2</v>
       </c>
       <c r="D129" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E129" t="s">
         <v>143</v>
       </c>
       <c r="F129" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="G129" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H129">
         <v>-9</v>
@@ -7594,7 +7594,7 @@
         <v>342</v>
       </c>
       <c r="B130" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C130">
         <v>3</v>
@@ -7606,10 +7606,10 @@
         <v>141</v>
       </c>
       <c r="F130" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="G130" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="H130">
         <v>-9</v>
@@ -7642,7 +7642,7 @@
         <v>238</v>
       </c>
       <c r="F131" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="G131" t="s">
         <v>213</v>
@@ -7678,7 +7678,7 @@
         <v>143</v>
       </c>
       <c r="F132" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="G132" t="s">
         <v>235</v>
@@ -7735,7 +7735,7 @@
         <v>342</v>
       </c>
       <c r="B134" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C134">
         <v>3</v>
@@ -7747,7 +7747,7 @@
         <v>248</v>
       </c>
       <c r="F134" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="H134">
         <v>0</v>
@@ -7783,7 +7783,7 @@
         <v>248</v>
       </c>
       <c r="F135" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="H135">
         <v>0</v>
@@ -7819,7 +7819,7 @@
         <v>248</v>
       </c>
       <c r="F136" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H136">
         <v>12</v>
@@ -7852,7 +7852,7 @@
         <v>248</v>
       </c>
       <c r="F137" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H137">
         <v>0</v>
@@ -8017,7 +8017,7 @@
         <v>248</v>
       </c>
       <c r="F142" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H142">
         <v>0</v>
@@ -8122,7 +8122,7 @@
         <v>280</v>
       </c>
       <c r="F145" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H145">
         <v>0</v>
@@ -8158,7 +8158,7 @@
         <v>280</v>
       </c>
       <c r="F146" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="H146">
         <v>0</v>
@@ -8191,7 +8191,7 @@
         <v>280</v>
       </c>
       <c r="F147" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="H147">
         <v>0</v>
@@ -8224,7 +8224,7 @@
         <v>285</v>
       </c>
       <c r="F148" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="H148">
         <v>0</v>
@@ -8284,7 +8284,7 @@
         <v>343</v>
       </c>
       <c r="B150" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="C150">
         <v>1</v>
@@ -8296,7 +8296,7 @@
         <v>285</v>
       </c>
       <c r="F150" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="H150">
         <v>0</v>
@@ -8329,7 +8329,7 @@
         <v>285</v>
       </c>
       <c r="F151" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="H151">
         <v>0</v>
@@ -8356,7 +8356,7 @@
         <v>343</v>
       </c>
       <c r="B152" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C152">
         <v>3</v>
@@ -8368,7 +8368,7 @@
         <v>343</v>
       </c>
       <c r="F152" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H152">
         <v>0</v>
@@ -8923,7 +8923,7 @@
         <v>238</v>
       </c>
       <c r="F17" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G17" t="s">
         <v>213</v>
@@ -8998,7 +8998,7 @@
         <v>143</v>
       </c>
       <c r="F19" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="G19" t="s">
         <v>340</v>
@@ -9145,7 +9145,7 @@
         <v>336</v>
       </c>
       <c r="D8" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -9153,13 +9153,13 @@
         <v>111</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="C9" t="s">
+        <v>443</v>
+      </c>
+      <c r="D9" t="s">
         <v>402</v>
-      </c>
-      <c r="C9" t="s">
-        <v>445</v>
-      </c>
-      <c r="D9" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -9167,13 +9167,13 @@
         <v>111</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="C10" t="s">
+        <v>443</v>
+      </c>
+      <c r="D10" t="s">
         <v>402</v>
-      </c>
-      <c r="C10" t="s">
-        <v>445</v>
-      </c>
-      <c r="D10" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -9198,10 +9198,10 @@
         <v>131</v>
       </c>
       <c r="C12" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D12" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -9215,7 +9215,7 @@
         <v>355</v>
       </c>
       <c r="D13" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -9229,7 +9229,7 @@
         <v>356</v>
       </c>
       <c r="D14" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -9243,7 +9243,7 @@
         <v>357</v>
       </c>
       <c r="D15" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -9254,24 +9254,24 @@
         <v>337</v>
       </c>
       <c r="C16" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D16" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>395</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" t="s">
+        <v>398</v>
+      </c>
+      <c r="D17" t="s">
         <v>397</v>
-      </c>
-      <c r="C17" t="s">
-        <v>399</v>
-      </c>
-      <c r="D17" t="s">
-        <v>398</v>
       </c>
     </row>
   </sheetData>
@@ -9442,7 +9442,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="B6">
         <v>1</v>

--- a/card_design.xlsx
+++ b/card_design.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\life\board_game\project_six_dynasty\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF582C60-341D-479E-921B-0A9FDF6DE148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F814F7E-52E8-485E-8156-8AB63ACCC7ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="811" xr2:uid="{F283CFD4-9FFB-4A79-AF0F-7443CC209F7A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="811" activeTab="2" xr2:uid="{F283CFD4-9FFB-4A79-AF0F-7443CC209F7A}"/>
   </bookViews>
   <sheets>
     <sheet name="卡牌设计" sheetId="1" r:id="rId1"/>
@@ -1304,10 +1304,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>配享文庙</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>功绩大于等于7</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -2009,6 +2005,10 @@
   </si>
   <si>
     <t>强制：如果[儒学]等级&gt;=[玄学]等级，司马家威望+1；否则司马家威望-1。摸1张牌。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>配享太庙</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -3268,7 +3268,7 @@
         <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="P3">
         <f>SUM(Q3:AE3)</f>
@@ -3313,22 +3313,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5" t="s">
+        <v>404</v>
+      </c>
+      <c r="E5" t="s">
         <v>405</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>406</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>407</v>
-      </c>
-      <c r="G5" t="s">
-        <v>408</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -3357,7 +3357,7 @@
         <v>63</v>
       </c>
       <c r="G6" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -3387,10 +3387,10 @@
         <v>169</v>
       </c>
       <c r="F7" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="G7" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -3420,7 +3420,7 @@
         <v>169</v>
       </c>
       <c r="F8" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G8" t="s">
         <v>62</v>
@@ -3453,10 +3453,10 @@
         <v>169</v>
       </c>
       <c r="F9" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="G9" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -3477,7 +3477,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -3489,10 +3489,10 @@
         <v>169</v>
       </c>
       <c r="F10" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G10" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H10">
         <v>-9</v>
@@ -3522,7 +3522,7 @@
         <v>170</v>
       </c>
       <c r="F11" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="L11">
         <v>1</v>
@@ -3549,7 +3549,7 @@
         <v>138</v>
       </c>
       <c r="F12" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H12">
         <v>7</v>
@@ -3615,10 +3615,10 @@
         <v>143</v>
       </c>
       <c r="F14" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="G14" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H14">
         <v>-6</v>
@@ -3651,7 +3651,7 @@
         <v>170</v>
       </c>
       <c r="F15" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -3678,10 +3678,10 @@
         <v>143</v>
       </c>
       <c r="F16" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G16" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H16">
         <v>2</v>
@@ -3717,10 +3717,10 @@
         <v>141</v>
       </c>
       <c r="F17" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="G17" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H17">
         <v>-12</v>
@@ -3753,7 +3753,7 @@
         <v>138</v>
       </c>
       <c r="F18" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H18">
         <v>7</v>
@@ -3786,7 +3786,7 @@
         <v>170</v>
       </c>
       <c r="F19" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -3813,7 +3813,7 @@
         <v>143</v>
       </c>
       <c r="F20" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="G20" t="s">
         <v>62</v>
@@ -3852,7 +3852,7 @@
         <v>139</v>
       </c>
       <c r="F21" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H21">
         <v>5</v>
@@ -3918,7 +3918,7 @@
         <v>140</v>
       </c>
       <c r="F23" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H23">
         <v>5</v>
@@ -3951,7 +3951,7 @@
         <v>172</v>
       </c>
       <c r="F24" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H24">
         <v>5</v>
@@ -3984,7 +3984,7 @@
         <v>205</v>
       </c>
       <c r="F25" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H25">
         <v>3</v>
@@ -4017,7 +4017,7 @@
         <v>140</v>
       </c>
       <c r="F26" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H26">
         <v>3</v>
@@ -4050,7 +4050,7 @@
         <v>146</v>
       </c>
       <c r="F27" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>172</v>
       </c>
       <c r="F29" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="G29" t="s">
         <v>14</v>
@@ -4146,7 +4146,7 @@
         <v>140</v>
       </c>
       <c r="F30" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G30" t="s">
         <v>14</v>
@@ -4182,7 +4182,7 @@
         <v>224</v>
       </c>
       <c r="F31" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="G31" t="s">
         <v>213</v>
@@ -4221,7 +4221,7 @@
         <v>171</v>
       </c>
       <c r="F32" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="I32">
         <v>1</v>
@@ -4248,7 +4248,7 @@
         <v>138</v>
       </c>
       <c r="F33" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H33">
         <v>7</v>
@@ -4281,7 +4281,7 @@
         <v>172</v>
       </c>
       <c r="F34" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="G34" t="s">
         <v>14</v>
@@ -4317,7 +4317,7 @@
         <v>148</v>
       </c>
       <c r="F35" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G35" t="s">
         <v>14</v>
@@ -4353,7 +4353,7 @@
         <v>171</v>
       </c>
       <c r="F36" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L36">
         <v>1</v>
@@ -4380,7 +4380,7 @@
         <v>139</v>
       </c>
       <c r="F37" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H37">
         <v>3</v>
@@ -4413,10 +4413,10 @@
         <v>141</v>
       </c>
       <c r="F38" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="G38" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H38">
         <v>-9</v>
@@ -4548,10 +4548,10 @@
         <v>141</v>
       </c>
       <c r="F42" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="G42" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H42">
         <v>-12</v>
@@ -4617,7 +4617,7 @@
         <v>171</v>
       </c>
       <c r="F44" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="K44">
         <v>1</v>
@@ -4644,7 +4644,7 @@
         <v>148</v>
       </c>
       <c r="F45" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H45">
         <v>0</v>
@@ -4677,7 +4677,7 @@
         <v>138</v>
       </c>
       <c r="F46" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H46">
         <v>5</v>
@@ -4710,7 +4710,7 @@
         <v>173</v>
       </c>
       <c r="F47" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H47">
         <v>4</v>
@@ -4749,7 +4749,7 @@
         <v>171</v>
       </c>
       <c r="F48" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="J48">
         <v>1</v>
@@ -4776,7 +4776,7 @@
         <v>138</v>
       </c>
       <c r="F49" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H49">
         <v>7</v>
@@ -4845,10 +4845,10 @@
         <v>141</v>
       </c>
       <c r="F51" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="G51" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H51">
         <v>-9</v>
@@ -4887,7 +4887,7 @@
         <v>171</v>
       </c>
       <c r="F52" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="J52">
         <v>1</v>
@@ -4914,7 +4914,7 @@
         <v>146</v>
       </c>
       <c r="F53" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H53">
         <v>1</v>
@@ -5001,10 +5001,10 @@
     </row>
     <row r="56" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B56" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C56" t="s">
         <v>14</v>
@@ -5028,7 +5028,7 @@
     </row>
     <row r="57" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B57" t="s">
         <v>97</v>
@@ -5061,7 +5061,7 @@
     </row>
     <row r="58" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B58" t="s">
         <v>101</v>
@@ -5079,7 +5079,7 @@
         <v>326</v>
       </c>
       <c r="G58" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H58">
         <v>-9</v>
@@ -5097,7 +5097,7 @@
     </row>
     <row r="59" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B59" t="s">
         <v>99</v>
@@ -5112,7 +5112,7 @@
         <v>138</v>
       </c>
       <c r="F59" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H59">
         <v>3</v>
@@ -5130,10 +5130,10 @@
     </row>
     <row r="60" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B60" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -5145,7 +5145,7 @@
         <v>149</v>
       </c>
       <c r="F60" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H60">
         <v>0</v>
@@ -5160,7 +5160,7 @@
     </row>
     <row r="61" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B61" t="s">
         <v>59</v>
@@ -5175,7 +5175,7 @@
         <v>149</v>
       </c>
       <c r="F61" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H61">
         <v>0</v>
@@ -5190,7 +5190,7 @@
     </row>
     <row r="62" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B62" t="s">
         <v>60</v>
@@ -5220,10 +5220,10 @@
     </row>
     <row r="63" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B63" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -5235,7 +5235,7 @@
         <v>149</v>
       </c>
       <c r="F63" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H63">
         <v>0</v>
@@ -5253,10 +5253,10 @@
     </row>
     <row r="64" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B64" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -5268,7 +5268,7 @@
         <v>220</v>
       </c>
       <c r="F64" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H64">
         <v>0</v>
@@ -5283,22 +5283,22 @@
     </row>
     <row r="65" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B65" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C65">
         <v>0</v>
       </c>
       <c r="D65" t="s">
+        <v>364</v>
+      </c>
+      <c r="E65" t="s">
         <v>365</v>
       </c>
-      <c r="E65" t="s">
-        <v>366</v>
-      </c>
       <c r="F65" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H65">
         <v>0</v>
@@ -5319,7 +5319,7 @@
     </row>
     <row r="66" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B66" t="s">
         <v>61</v>
@@ -5352,7 +5352,7 @@
     </row>
     <row r="67" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B67" t="s">
         <v>86</v>
@@ -5385,7 +5385,7 @@
     </row>
     <row r="68" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B68" t="s">
         <v>87</v>
@@ -5418,7 +5418,7 @@
     </row>
     <row r="69" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B69" t="s">
         <v>103</v>
@@ -5433,7 +5433,7 @@
         <v>147</v>
       </c>
       <c r="F69" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H69">
         <v>7</v>
@@ -5457,7 +5457,7 @@
     </row>
     <row r="70" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B70" t="s">
         <v>275</v>
@@ -5472,7 +5472,7 @@
         <v>276</v>
       </c>
       <c r="F70" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H70">
         <v>3</v>
@@ -5493,7 +5493,7 @@
     </row>
     <row r="71" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B71" t="s">
         <v>277</v>
@@ -5508,7 +5508,7 @@
         <v>276</v>
       </c>
       <c r="F71" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H71">
         <v>15</v>
@@ -5526,7 +5526,7 @@
     </row>
     <row r="72" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B72" t="s">
         <v>278</v>
@@ -5559,7 +5559,7 @@
     </row>
     <row r="73" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B73" t="s">
         <v>283</v>
@@ -5574,7 +5574,7 @@
         <v>276</v>
       </c>
       <c r="F73" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H73">
         <v>11</v>
@@ -5592,7 +5592,7 @@
     </row>
     <row r="74" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B74" t="s">
         <v>72</v>
@@ -5625,7 +5625,7 @@
     </row>
     <row r="75" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B75" t="s">
         <v>152</v>
@@ -5658,7 +5658,7 @@
     </row>
     <row r="76" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B76" t="s">
         <v>154</v>
@@ -5691,7 +5691,7 @@
     </row>
     <row r="77" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B77" t="s">
         <v>73</v>
@@ -5706,7 +5706,7 @@
         <v>144</v>
       </c>
       <c r="F77" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H77">
         <v>6</v>
@@ -5727,7 +5727,7 @@
     </row>
     <row r="78" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B78" t="s">
         <v>74</v>
@@ -5742,7 +5742,7 @@
         <v>144</v>
       </c>
       <c r="F78" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H78">
         <v>6</v>
@@ -5763,7 +5763,7 @@
     </row>
     <row r="79" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B79" t="s">
         <v>75</v>
@@ -5778,7 +5778,7 @@
         <v>144</v>
       </c>
       <c r="F79" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H79">
         <v>7</v>
@@ -5796,7 +5796,7 @@
     </row>
     <row r="80" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B80" t="s">
         <v>85</v>
@@ -5811,7 +5811,7 @@
         <v>144</v>
       </c>
       <c r="F80" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H80">
         <v>8</v>
@@ -5829,7 +5829,7 @@
     </row>
     <row r="81" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B81" t="s">
         <v>93</v>
@@ -5865,7 +5865,7 @@
     </row>
     <row r="82" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B82" t="s">
         <v>185</v>
@@ -5898,7 +5898,7 @@
     </row>
     <row r="83" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B83" t="s">
         <v>249</v>
@@ -5913,7 +5913,7 @@
         <v>244</v>
       </c>
       <c r="F83" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H83">
         <v>3</v>
@@ -5934,7 +5934,7 @@
     </row>
     <row r="84" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B84" t="s">
         <v>245</v>
@@ -5949,7 +5949,7 @@
         <v>244</v>
       </c>
       <c r="F84" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H84">
         <v>3</v>
@@ -5970,7 +5970,7 @@
     </row>
     <row r="85" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B85" t="s">
         <v>246</v>
@@ -5985,7 +5985,7 @@
         <v>244</v>
       </c>
       <c r="F85" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H85">
         <v>8</v>
@@ -6003,7 +6003,7 @@
     </row>
     <row r="86" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B86" t="s">
         <v>247</v>
@@ -6018,7 +6018,7 @@
         <v>244</v>
       </c>
       <c r="F86" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H86">
         <v>5</v>
@@ -6039,7 +6039,7 @@
     </row>
     <row r="87" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B87" t="s">
         <v>231</v>
@@ -6054,7 +6054,7 @@
         <v>232</v>
       </c>
       <c r="F87" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G87" t="s">
         <v>83</v>
@@ -6078,7 +6078,7 @@
     </row>
     <row r="88" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B88" t="s">
         <v>233</v>
@@ -6093,10 +6093,10 @@
         <v>142</v>
       </c>
       <c r="F88" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="G88" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H88">
         <v>-9</v>
@@ -6114,7 +6114,7 @@
     </row>
     <row r="89" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B89" t="s">
         <v>136</v>
@@ -6129,7 +6129,7 @@
         <v>142</v>
       </c>
       <c r="F89" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="G89" t="s">
         <v>83</v>
@@ -6153,7 +6153,7 @@
     </row>
     <row r="90" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B90" t="s">
         <v>161</v>
@@ -6168,10 +6168,10 @@
         <v>142</v>
       </c>
       <c r="F90" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="G90" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H90">
         <v>-12</v>
@@ -6192,7 +6192,7 @@
     </row>
     <row r="91" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B91" t="s">
         <v>162</v>
@@ -6207,10 +6207,10 @@
         <v>142</v>
       </c>
       <c r="F91" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G91" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H91">
         <v>-12</v>
@@ -6231,7 +6231,7 @@
     </row>
     <row r="92" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B92" t="s">
         <v>327</v>
@@ -6246,7 +6246,7 @@
         <v>225</v>
       </c>
       <c r="F92" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="G92" t="s">
         <v>62</v>
@@ -6270,7 +6270,7 @@
     </row>
     <row r="93" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B93" t="s">
         <v>234</v>
@@ -6285,10 +6285,10 @@
         <v>232</v>
       </c>
       <c r="F93" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="G93" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H93">
         <v>-12</v>
@@ -6306,7 +6306,7 @@
     </row>
     <row r="94" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B94" t="s">
         <v>236</v>
@@ -6321,7 +6321,7 @@
         <v>232</v>
       </c>
       <c r="F94" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G94" t="s">
         <v>237</v>
@@ -6348,7 +6348,7 @@
     </row>
     <row r="95" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B95" t="s">
         <v>89</v>
@@ -6363,7 +6363,7 @@
         <v>173</v>
       </c>
       <c r="F95" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H95">
         <v>1</v>
@@ -6384,7 +6384,7 @@
     </row>
     <row r="96" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B96" t="s">
         <v>90</v>
@@ -6399,7 +6399,7 @@
         <v>173</v>
       </c>
       <c r="F96" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H96">
         <v>0</v>
@@ -6423,7 +6423,7 @@
     </row>
     <row r="97" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B97" t="s">
         <v>92</v>
@@ -6438,7 +6438,7 @@
         <v>173</v>
       </c>
       <c r="F97" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H97">
         <v>1</v>
@@ -6462,7 +6462,7 @@
     </row>
     <row r="98" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B98" t="s">
         <v>102</v>
@@ -6477,7 +6477,7 @@
         <v>173</v>
       </c>
       <c r="F98" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H98">
         <v>0</v>
@@ -6501,7 +6501,7 @@
     </row>
     <row r="99" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B99" t="s">
         <v>318</v>
@@ -6516,7 +6516,7 @@
         <v>317</v>
       </c>
       <c r="F99" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H99">
         <v>3</v>
@@ -6537,10 +6537,10 @@
     </row>
     <row r="100" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B100" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -6552,7 +6552,7 @@
         <v>288</v>
       </c>
       <c r="F100" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H100">
         <v>1</v>
@@ -6573,22 +6573,22 @@
     </row>
     <row r="101" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B101" t="s">
+        <v>373</v>
+      </c>
+      <c r="C101">
+        <v>0</v>
+      </c>
+      <c r="D101" t="s">
+        <v>364</v>
+      </c>
+      <c r="E101" t="s">
         <v>374</v>
       </c>
-      <c r="C101">
-        <v>0</v>
-      </c>
-      <c r="D101" t="s">
-        <v>365</v>
-      </c>
-      <c r="E101" t="s">
-        <v>375</v>
-      </c>
       <c r="F101" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H101">
         <v>0</v>
@@ -6608,7 +6608,7 @@
     </row>
     <row r="102" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B102" t="s">
         <v>272</v>
@@ -6623,7 +6623,7 @@
         <v>271</v>
       </c>
       <c r="F102" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H102">
         <v>2</v>
@@ -6647,7 +6647,7 @@
     </row>
     <row r="103" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B103" t="s">
         <v>273</v>
@@ -6686,7 +6686,7 @@
     </row>
     <row r="104" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B104" t="s">
         <v>96</v>
@@ -6701,7 +6701,7 @@
         <v>148</v>
       </c>
       <c r="F104" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H104">
         <v>0</v>
@@ -6719,7 +6719,7 @@
     </row>
     <row r="105" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B105" t="s">
         <v>163</v>
@@ -6734,7 +6734,7 @@
         <v>148</v>
       </c>
       <c r="F105" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H105">
         <v>0</v>
@@ -6752,7 +6752,7 @@
     </row>
     <row r="106" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B106" t="s">
         <v>164</v>
@@ -6761,13 +6761,13 @@
         <v>1</v>
       </c>
       <c r="D106" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E106" t="s">
         <v>140</v>
       </c>
       <c r="F106" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H106">
         <v>3</v>
@@ -6785,7 +6785,7 @@
     </row>
     <row r="107" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B107" t="s">
         <v>155</v>
@@ -6800,7 +6800,7 @@
         <v>145</v>
       </c>
       <c r="F107" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H107">
         <v>0</v>
@@ -6821,7 +6821,7 @@
     </row>
     <row r="108" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B108" t="s">
         <v>156</v>
@@ -6836,7 +6836,7 @@
         <v>145</v>
       </c>
       <c r="F108" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H108">
         <v>5</v>
@@ -6857,7 +6857,7 @@
     </row>
     <row r="109" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B109" t="s">
         <v>253</v>
@@ -6872,7 +6872,7 @@
         <v>252</v>
       </c>
       <c r="F109" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H109">
         <v>0</v>
@@ -6893,7 +6893,7 @@
     </row>
     <row r="110" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B110" t="s">
         <v>254</v>
@@ -6908,7 +6908,7 @@
         <v>252</v>
       </c>
       <c r="F110" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H110">
         <v>6</v>
@@ -6929,7 +6929,7 @@
     </row>
     <row r="111" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B111" t="s">
         <v>251</v>
@@ -6944,7 +6944,7 @@
         <v>182</v>
       </c>
       <c r="F111" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H111">
         <v>6</v>
@@ -6962,7 +6962,7 @@
     </row>
     <row r="112" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B112" t="s">
         <v>175</v>
@@ -6995,7 +6995,7 @@
     </row>
     <row r="113" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B113" t="s">
         <v>307</v>
@@ -7028,7 +7028,7 @@
     </row>
     <row r="114" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B114" t="s">
         <v>180</v>
@@ -7043,7 +7043,7 @@
         <v>177</v>
       </c>
       <c r="F114" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H114">
         <v>1</v>
@@ -7064,7 +7064,7 @@
     </row>
     <row r="115" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B115" t="s">
         <v>181</v>
@@ -7079,7 +7079,7 @@
         <v>177</v>
       </c>
       <c r="F115" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H115">
         <v>1</v>
@@ -7097,7 +7097,7 @@
     </row>
     <row r="116" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B116" t="s">
         <v>257</v>
@@ -7112,7 +7112,7 @@
         <v>183</v>
       </c>
       <c r="F116" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H116">
         <v>3</v>
@@ -7130,7 +7130,7 @@
     </row>
     <row r="117" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B117" t="s">
         <v>187</v>
@@ -7145,7 +7145,7 @@
         <v>183</v>
       </c>
       <c r="F117" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H117">
         <v>3</v>
@@ -7166,7 +7166,7 @@
     </row>
     <row r="118" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B118" t="s">
         <v>256</v>
@@ -7181,7 +7181,7 @@
         <v>140</v>
       </c>
       <c r="F118" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H118">
         <v>1</v>
@@ -7199,7 +7199,7 @@
     </row>
     <row r="119" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B119" t="s">
         <v>206</v>
@@ -7214,7 +7214,7 @@
         <v>205</v>
       </c>
       <c r="F119" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H119">
         <v>3</v>
@@ -7232,7 +7232,7 @@
     </row>
     <row r="120" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B120" t="s">
         <v>209</v>
@@ -7268,7 +7268,7 @@
     </row>
     <row r="121" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B121" t="s">
         <v>212</v>
@@ -7283,7 +7283,7 @@
         <v>211</v>
       </c>
       <c r="F121" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G121" t="s">
         <v>62</v>
@@ -7304,10 +7304,10 @@
     </row>
     <row r="122" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B122" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C122">
         <v>3</v>
@@ -7319,10 +7319,10 @@
         <v>141</v>
       </c>
       <c r="F122" t="s">
+        <v>385</v>
+      </c>
+      <c r="G122" t="s">
         <v>386</v>
-      </c>
-      <c r="G122" t="s">
-        <v>387</v>
       </c>
       <c r="H122">
         <v>-12</v>
@@ -7343,7 +7343,7 @@
     </row>
     <row r="123" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B123" t="s">
         <v>214</v>
@@ -7358,7 +7358,7 @@
         <v>211</v>
       </c>
       <c r="F123" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="G123" t="s">
         <v>213</v>
@@ -7379,10 +7379,10 @@
     </row>
     <row r="124" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B124" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C124">
         <v>3</v>
@@ -7394,10 +7394,10 @@
         <v>141</v>
       </c>
       <c r="F124" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G124" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H124">
         <v>-9</v>
@@ -7415,7 +7415,7 @@
     </row>
     <row r="125" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B125" t="s">
         <v>226</v>
@@ -7430,7 +7430,7 @@
         <v>228</v>
       </c>
       <c r="F125" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="G125" t="s">
         <v>62</v>
@@ -7451,7 +7451,7 @@
     </row>
     <row r="126" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A126" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B126" t="s">
         <v>88</v>
@@ -7466,10 +7466,10 @@
         <v>143</v>
       </c>
       <c r="F126" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="G126" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H126">
         <v>-6</v>
@@ -7487,7 +7487,7 @@
     </row>
     <row r="127" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B127" t="s">
         <v>331</v>
@@ -7502,7 +7502,7 @@
         <v>238</v>
       </c>
       <c r="F127" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G127" t="s">
         <v>213</v>
@@ -7523,7 +7523,7 @@
     </row>
     <row r="128" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B128" t="s">
         <v>239</v>
@@ -7538,7 +7538,7 @@
         <v>238</v>
       </c>
       <c r="F128" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="G128" t="s">
         <v>235</v>
@@ -7559,25 +7559,25 @@
     </row>
     <row r="129" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B129" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C129">
         <v>2</v>
       </c>
       <c r="D129" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E129" t="s">
         <v>143</v>
       </c>
       <c r="F129" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="G129" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H129">
         <v>-9</v>
@@ -7591,10 +7591,10 @@
     </row>
     <row r="130" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B130" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C130">
         <v>3</v>
@@ -7606,10 +7606,10 @@
         <v>141</v>
       </c>
       <c r="F130" t="s">
+        <v>436</v>
+      </c>
+      <c r="G130" t="s">
         <v>437</v>
-      </c>
-      <c r="G130" t="s">
-        <v>438</v>
       </c>
       <c r="H130">
         <v>-9</v>
@@ -7627,7 +7627,7 @@
     </row>
     <row r="131" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B131" t="s">
         <v>242</v>
@@ -7642,7 +7642,7 @@
         <v>238</v>
       </c>
       <c r="F131" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="G131" t="s">
         <v>213</v>
@@ -7663,7 +7663,7 @@
     </row>
     <row r="132" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B132" t="s">
         <v>81</v>
@@ -7678,7 +7678,7 @@
         <v>143</v>
       </c>
       <c r="F132" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G132" t="s">
         <v>235</v>
@@ -7699,7 +7699,7 @@
     </row>
     <row r="133" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B133" t="s">
         <v>165</v>
@@ -7732,10 +7732,10 @@
     </row>
     <row r="134" spans="1:34" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B134" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C134">
         <v>3</v>
@@ -7747,7 +7747,7 @@
         <v>248</v>
       </c>
       <c r="F134" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H134">
         <v>0</v>
@@ -7768,7 +7768,7 @@
     </row>
     <row r="135" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B135" t="s">
         <v>250</v>
@@ -7783,7 +7783,7 @@
         <v>248</v>
       </c>
       <c r="F135" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H135">
         <v>0</v>
@@ -7804,7 +7804,7 @@
     </row>
     <row r="136" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B136" t="s">
         <v>255</v>
@@ -7819,7 +7819,7 @@
         <v>248</v>
       </c>
       <c r="F136" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H136">
         <v>12</v>
@@ -7837,7 +7837,7 @@
     </row>
     <row r="137" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B137" t="s">
         <v>258</v>
@@ -7852,7 +7852,7 @@
         <v>248</v>
       </c>
       <c r="F137" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H137">
         <v>0</v>
@@ -7870,7 +7870,7 @@
     </row>
     <row r="138" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B138" t="s">
         <v>259</v>
@@ -7885,7 +7885,7 @@
         <v>248</v>
       </c>
       <c r="F138" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H138">
         <v>10</v>
@@ -7903,7 +7903,7 @@
     </row>
     <row r="139" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B139" t="s">
         <v>260</v>
@@ -7936,7 +7936,7 @@
     </row>
     <row r="140" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A140" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B140" t="s">
         <v>262</v>
@@ -7969,7 +7969,7 @@
     </row>
     <row r="141" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B141" t="s">
         <v>264</v>
@@ -7984,7 +7984,7 @@
         <v>248</v>
       </c>
       <c r="F141" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H141">
         <v>8</v>
@@ -8002,7 +8002,7 @@
     </row>
     <row r="142" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B142" t="s">
         <v>265</v>
@@ -8017,7 +8017,7 @@
         <v>248</v>
       </c>
       <c r="F142" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H142">
         <v>0</v>
@@ -8041,7 +8041,7 @@
     </row>
     <row r="143" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B143" t="s">
         <v>266</v>
@@ -8074,7 +8074,7 @@
     </row>
     <row r="144" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A144" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B144" t="s">
         <v>279</v>
@@ -8107,7 +8107,7 @@
     </row>
     <row r="145" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B145" t="s">
         <v>269</v>
@@ -8122,7 +8122,7 @@
         <v>280</v>
       </c>
       <c r="F145" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H145">
         <v>0</v>
@@ -8143,7 +8143,7 @@
     </row>
     <row r="146" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A146" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B146" t="s">
         <v>281</v>
@@ -8158,7 +8158,7 @@
         <v>280</v>
       </c>
       <c r="F146" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H146">
         <v>0</v>
@@ -8176,7 +8176,7 @@
     </row>
     <row r="147" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B147" t="s">
         <v>282</v>
@@ -8191,7 +8191,7 @@
         <v>280</v>
       </c>
       <c r="F147" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H147">
         <v>0</v>
@@ -8209,7 +8209,7 @@
     </row>
     <row r="148" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B148" t="s">
         <v>286</v>
@@ -8224,7 +8224,7 @@
         <v>285</v>
       </c>
       <c r="F148" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H148">
         <v>0</v>
@@ -8248,7 +8248,7 @@
     </row>
     <row r="149" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B149" t="s">
         <v>316</v>
@@ -8263,7 +8263,7 @@
         <v>285</v>
       </c>
       <c r="F149" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H149">
         <v>0</v>
@@ -8281,10 +8281,10 @@
     </row>
     <row r="150" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A150" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B150" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C150">
         <v>1</v>
@@ -8296,7 +8296,7 @@
         <v>285</v>
       </c>
       <c r="F150" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H150">
         <v>0</v>
@@ -8314,7 +8314,7 @@
     </row>
     <row r="151" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A151" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B151" t="s">
         <v>287</v>
@@ -8329,7 +8329,7 @@
         <v>285</v>
       </c>
       <c r="F151" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H151">
         <v>0</v>
@@ -8353,22 +8353,22 @@
     </row>
     <row r="152" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A152" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B152" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C152">
         <v>3</v>
       </c>
       <c r="D152" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E152" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F152" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H152">
         <v>0</v>
@@ -8628,7 +8628,7 @@
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B6" t="s">
         <v>231</v>
@@ -8667,7 +8667,7 @@
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B7" t="s">
         <v>267</v>
@@ -8703,7 +8703,7 @@
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B8" t="s">
         <v>289</v>
@@ -8736,7 +8736,7 @@
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B9" t="s">
         <v>256</v>
@@ -8830,7 +8830,7 @@
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B15" t="s">
         <v>230</v>
@@ -8866,7 +8866,7 @@
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B16" t="s">
         <v>55</v>
@@ -8908,7 +8908,7 @@
     </row>
     <row r="17" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B17" t="s">
         <v>241</v>
@@ -8923,7 +8923,7 @@
         <v>238</v>
       </c>
       <c r="F17" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="G17" t="s">
         <v>213</v>
@@ -8950,7 +8950,7 @@
     </row>
     <row r="18" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B18" t="s">
         <v>307</v>
@@ -8998,10 +8998,10 @@
         <v>143</v>
       </c>
       <c r="F19" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="G19" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H19">
         <v>2</v>
@@ -9136,16 +9136,16 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>511</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="C8" t="s">
         <v>335</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="C8" t="s">
-        <v>336</v>
-      </c>
       <c r="D8" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -9153,13 +9153,13 @@
         <v>111</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="C9" t="s">
+        <v>442</v>
+      </c>
+      <c r="D9" t="s">
         <v>401</v>
-      </c>
-      <c r="C9" t="s">
-        <v>443</v>
-      </c>
-      <c r="D9" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -9167,27 +9167,27 @@
         <v>111</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="C10" t="s">
+        <v>442</v>
+      </c>
+      <c r="D10" t="s">
         <v>401</v>
-      </c>
-      <c r="C10" t="s">
-        <v>443</v>
-      </c>
-      <c r="D10" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>350</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" t="s">
         <v>352</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>353</v>
-      </c>
-      <c r="D11" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -9198,10 +9198,10 @@
         <v>131</v>
       </c>
       <c r="C12" t="s">
+        <v>440</v>
+      </c>
+      <c r="D12" t="s">
         <v>441</v>
-      </c>
-      <c r="D12" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -9212,10 +9212,10 @@
         <v>309</v>
       </c>
       <c r="C13" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D13" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -9226,10 +9226,10 @@
         <v>309</v>
       </c>
       <c r="C14" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -9240,38 +9240,38 @@
         <v>309</v>
       </c>
       <c r="C15" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D15" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C16" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D16" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>394</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" t="s">
+        <v>397</v>
+      </c>
+      <c r="D17" t="s">
         <v>396</v>
-      </c>
-      <c r="C17" t="s">
-        <v>398</v>
-      </c>
-      <c r="D17" t="s">
-        <v>397</v>
       </c>
     </row>
   </sheetData>
@@ -9332,7 +9332,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E2" t="s">
         <v>191</v>
@@ -9442,7 +9442,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B6">
         <v>1</v>

--- a/card_design.xlsx
+++ b/card_design.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\life\board_game\project_six_dynasty\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F814F7E-52E8-485E-8156-8AB63ACCC7ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3C286D7-84BB-48A8-BCE1-B8AA1F62F2AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="811" activeTab="2" xr2:uid="{F283CFD4-9FFB-4A79-AF0F-7443CC209F7A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="811" xr2:uid="{F283CFD4-9FFB-4A79-AF0F-7443CC209F7A}"/>
   </bookViews>
   <sheets>
     <sheet name="卡牌设计" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1067" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="510">
   <si>
     <t>归属</t>
   </si>
@@ -80,9 +80,6 @@
     <t>策略牌</t>
   </si>
   <si>
-    <t>被动：[流民]被存档时，自动放置回供应堆。存档[流民]的玩家获得2vp。</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -419,10 +416,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>东晋控制[巴蜀]区域</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>加九锡</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -433,10 +426,6 @@
     <t>河洛旧都</t>
   </si>
   <si>
-    <t>东晋控制[中原]区域</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>玩家控制[中原]区域</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -444,10 +433,6 @@
     <t>关中故畿</t>
   </si>
   <si>
-    <t>东晋控制[关中]区域</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>玩家控制[关中]区域</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -471,17 +456,9 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>东晋控制[山东]区域</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>赵魏雄藩</t>
   </si>
   <si>
-    <t>东晋控制[河北]区域</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>玩家控制[河北]区域</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -490,10 +467,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>东晋控制[山西]区域</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>玩家控制[山西]区域</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1144,10 +1117,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>被动：任意玩家提高行动顺位时，获得2vp。登场：先动值1。获得2顺位，2功绩和2威望，转化[合肥][寿春]。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>主动：选择1项：弃1张手牌，然后摸1张牌；或者弃置1张候选策略牌，然后补充1张牌到朝堂区。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1344,10 +1313,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>被动：每次获得功绩后，摸1张牌。登场：先动值8。获得2功绩（不触发被动效果）。在其他东晋玩家完成登场效果后，转化2个[建康]以外的司马家地点。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>检索2次[策略]，然后存档此牌。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1620,10 +1585,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>行动：获得5军力。被动：占据[京口]时，才能打出、执行或征发。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>被动：每次存档1张牌时，获得2vp。登场：先动值4。转化[南郡][襄阳]。获得1功绩和1威望。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1648,10 +1609,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>主动：弃1张手牌，然后摸1张牌，可以执行1个牌组行动。登场：转化[蓟][龙城][中山]（不获得vp）</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>行动：传播1次[佛学]，获得2vp。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1780,10 +1737,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>被动：幕僚区空位总数为6。主动：如果拥有4种不同的标记各1个，获得1个朝堂行动；否则，可以打出1张幕僚牌。登场：先动值7。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>强制：选择1个[幕僚]区空位最少的玩家，该玩家选择1个费用最高的[幕僚]存档。摸1张牌。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1804,10 +1757,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>-</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>行动：支付1张手牌，提高1级顺位，传播1次[玄学]。被动：[加官进爵]不能被存档、征发或弃置。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1820,10 +1769,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>行动：2军力。本回合执行[进军]时，获得1vp。被动：需要控制[幽燕]，才能打出、执行或征发。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>行动：2军力。本回合执行[进军]时，获得1vp。被动：控制[西凉]时，才能打出、执行或征发。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1852,10 +1797,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>被动：每次存档或弃置[流民]时，获得1军力。登场：先动值5。转化[京口][广陵]。获得1功绩和1威望。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>主动：打出1张[文化]牌或征发1张[文化]候选策略牌。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1980,14 +1921,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>主动：弃1张手牌，然后获得X军力，X=[军事]标记数（最多5）。登场：转化[盛乐][平城]（不获得vp），获得4军力。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>主动：弃1张手牌，然后摸1张牌，可以执行1个手牌行动。登场：转化[长安][弘农][安定][平阳]（不获得vp）</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>行动：3军力，存档此牌。被动：每回合前2次[进军]时，费用减1。区域奖励改为0/1vp。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -2009,6 +1942,66 @@
   </si>
   <si>
     <t>配享太庙</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>被动：每次获得功绩后，摸1张牌。登场：先动值7。获得1威望和1功绩（不触发被动效果）。在其他东晋玩家完成登场效果后，转化2个[建康]以外的司马家地点。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>被动：幕僚区空位总数为5。主动：如果拥有4种不同的标记，获得1个朝堂行动；否则，可以打出1张幕僚牌。登场：先动值8。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>被动：任意玩家提高行动顺位时，获得2vp。每次打出[权谋]标记时，获得2vp。登场：先动值1。获得2顺位，2功绩和2威望，转化[合肥][寿春]。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>被动：每次存档或弃置[流民]时，获得1军力或2vp。登场：先动值5。转化[京口][广陵]。获得1功绩和1威望。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>友方控制[巴蜀]区域</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>友方控制[中原]区域</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>友方控制[关中]区域</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>友方控制[山东]区域</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>友方控制[河北]区域</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>友方控制[山西]区域</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>主动：弃1张手牌，然后摸1张牌，可以执行1个手牌行动。登场：转化[长安][弘农][安定][平阳]</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>主动：弃1张手牌，然后摸1张牌，可以执行1个牌组行动。登场：转化[蓟][龙城][中山]</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>主动：弃1张手牌，然后获得X军力，X=[军事]标记数（最多5）。登场：转化[盛乐][平城]，获得4军力。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动：2军力。本回合执行[进军]时，获得1vp。限定：需要控制[幽燕]，才能打出、执行或征发。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动：获得5军力。限定：占据[京口]时，才能打出、执行或征发。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -3032,10 +3025,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="F1" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="G1" t="s">
         <v>4</v>
@@ -3050,82 +3043,82 @@
         <v>7</v>
       </c>
       <c r="K1" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="L1" t="s">
         <v>8</v>
       </c>
       <c r="M1" t="s">
+        <v>78</v>
+      </c>
+      <c r="N1" t="s">
         <v>79</v>
       </c>
-      <c r="N1" t="s">
-        <v>80</v>
-      </c>
       <c r="O1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P1" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="Q1" t="s">
+        <v>131</v>
+      </c>
+      <c r="R1" t="s">
+        <v>132</v>
+      </c>
+      <c r="S1" t="s">
+        <v>133</v>
+      </c>
+      <c r="T1" t="s">
+        <v>165</v>
+      </c>
+      <c r="U1" t="s">
+        <v>134</v>
+      </c>
+      <c r="V1" t="s">
+        <v>135</v>
+      </c>
+      <c r="W1" t="s">
+        <v>136</v>
+      </c>
+      <c r="X1" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y1" t="s">
         <v>138</v>
       </c>
-      <c r="R1" t="s">
+      <c r="Z1" t="s">
         <v>139</v>
       </c>
-      <c r="S1" t="s">
+      <c r="AA1" t="s">
         <v>140</v>
       </c>
-      <c r="T1" t="s">
-        <v>172</v>
-      </c>
-      <c r="U1" t="s">
+      <c r="AB1" t="s">
         <v>141</v>
       </c>
-      <c r="V1" t="s">
+      <c r="AC1" t="s">
+        <v>144</v>
+      </c>
+      <c r="AD1" t="s">
         <v>142</v>
       </c>
-      <c r="W1" t="s">
+      <c r="AE1" t="s">
+        <v>166</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>278</v>
+      </c>
+      <c r="AG1" t="s">
         <v>143</v>
       </c>
-      <c r="X1" t="s">
-        <v>144</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>145</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>146</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>147</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>148</v>
-      </c>
-      <c r="AC1" t="s">
+      <c r="AH1" t="s">
         <v>151</v>
       </c>
-      <c r="AD1" t="s">
-        <v>149</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>173</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>285</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>150</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>158</v>
-      </c>
       <c r="AI1" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="AJ1" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.3">
@@ -3259,16 +3252,13 @@
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>169</v>
-      </c>
-      <c r="F3" t="s">
+        <v>162</v>
+      </c>
+      <c r="G3" t="s">
         <v>13</v>
       </c>
-      <c r="G3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" t="s">
-        <v>460</v>
+      <c r="H3">
+        <v>2</v>
       </c>
       <c r="P3">
         <f>SUM(Q3:AE3)</f>
@@ -3280,7 +3270,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -3289,13 +3279,13 @@
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
         <v>16</v>
-      </c>
-      <c r="G4" t="s">
-        <v>17</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -3313,22 +3303,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="E5" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="F5" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="G5" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -3342,7 +3332,7 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -3351,13 +3341,13 @@
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G6" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -3375,7 +3365,7 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -3384,13 +3374,13 @@
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="F7" t="s">
-        <v>494</v>
+        <v>479</v>
       </c>
       <c r="G7" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -3408,7 +3398,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -3417,13 +3407,13 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="F8" t="s">
-        <v>463</v>
+        <v>450</v>
       </c>
       <c r="G8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -3441,7 +3431,7 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -3450,13 +3440,13 @@
         <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="F9" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
       <c r="G9" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -3477,7 +3467,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -3486,13 +3476,13 @@
         <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="F10" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="G10" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="H10">
         <v>-9</v>
@@ -3507,19 +3497,19 @@
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" t="s">
         <v>23</v>
       </c>
-      <c r="B11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" t="s">
-        <v>24</v>
-      </c>
       <c r="E11" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="F11" t="s">
         <v>505</v>
@@ -3534,22 +3524,22 @@
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C12">
         <v>3</v>
       </c>
       <c r="D12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E12" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="F12" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="H12">
         <v>7</v>
@@ -3567,22 +3557,22 @@
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C13">
         <v>2</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E13" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="F13" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="H13">
         <v>5</v>
@@ -3600,25 +3590,25 @@
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E14" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="F14" t="s">
-        <v>471</v>
+        <v>457</v>
       </c>
       <c r="G14" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="H14">
         <v>-6</v>
@@ -3636,22 +3626,22 @@
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" t="s">
         <v>27</v>
       </c>
-      <c r="B15" t="s">
-        <v>28</v>
-      </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E15" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="F15" t="s">
-        <v>421</v>
+        <v>506</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -3663,10 +3653,10 @@
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -3675,13 +3665,13 @@
         <v>12</v>
       </c>
       <c r="E16" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="F16" t="s">
-        <v>499</v>
+        <v>484</v>
       </c>
       <c r="G16" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="H16">
         <v>2</v>
@@ -3702,10 +3692,10 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C17">
         <v>3</v>
@@ -3714,13 +3704,13 @@
         <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="F17" t="s">
-        <v>464</v>
+        <v>508</v>
       </c>
       <c r="G17" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="H17">
         <v>-12</v>
@@ -3738,22 +3728,22 @@
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C18">
         <v>3</v>
       </c>
       <c r="D18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E18" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="F18" t="s">
-        <v>468</v>
+        <v>454</v>
       </c>
       <c r="H18">
         <v>7</v>
@@ -3771,22 +3761,22 @@
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" t="s">
         <v>31</v>
       </c>
-      <c r="B19" t="s">
-        <v>32</v>
-      </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E19" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="F19" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -3798,10 +3788,10 @@
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -3810,13 +3800,13 @@
         <v>12</v>
       </c>
       <c r="E20" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="F20" t="s">
-        <v>506</v>
+        <v>489</v>
       </c>
       <c r="G20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H20">
         <v>4</v>
@@ -3837,22 +3827,22 @@
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C21">
         <v>2</v>
       </c>
       <c r="D21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E21" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="F21" t="s">
-        <v>469</v>
+        <v>455</v>
       </c>
       <c r="H21">
         <v>5</v>
@@ -3870,22 +3860,22 @@
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E22" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="F22" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="H22">
         <v>4</v>
@@ -3903,22 +3893,22 @@
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" t="s">
         <v>34</v>
-      </c>
-      <c r="B23" t="s">
-        <v>35</v>
       </c>
       <c r="C23">
         <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E23" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="F23" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="H23">
         <v>5</v>
@@ -3936,22 +3926,22 @@
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C24">
         <v>2</v>
       </c>
       <c r="D24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E24" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="F24" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="H24">
         <v>5</v>
@@ -3969,22 +3959,22 @@
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B25" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="C25">
         <v>1</v>
       </c>
       <c r="D25" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="E25" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="F25" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="H25">
         <v>3</v>
@@ -4002,22 +3992,22 @@
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C26">
         <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="E26" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="F26" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="H26">
         <v>3</v>
@@ -4035,22 +4025,22 @@
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C27">
         <v>3</v>
       </c>
       <c r="D27" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E27" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="F27" t="s">
-        <v>503</v>
+        <v>488</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -4068,22 +4058,22 @@
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C28" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E28" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="F28" t="s">
-        <v>295</v>
+        <v>497</v>
       </c>
       <c r="K28">
         <v>1</v>
@@ -4095,25 +4085,25 @@
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" t="s">
         <v>37</v>
-      </c>
-      <c r="B29" t="s">
-        <v>38</v>
       </c>
       <c r="C29">
         <v>3</v>
       </c>
       <c r="D29" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E29" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="F29" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="G29" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H29">
         <v>7</v>
@@ -4131,25 +4121,25 @@
     </row>
     <row r="30" spans="1:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C30">
         <v>3</v>
       </c>
       <c r="D30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E30" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="F30" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="G30" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H30">
         <v>7</v>
@@ -4167,25 +4157,25 @@
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="C31">
         <v>2</v>
       </c>
       <c r="D31" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="E31" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="F31" t="s">
-        <v>470</v>
+        <v>456</v>
       </c>
       <c r="G31" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="H31">
         <v>-6</v>
@@ -4206,22 +4196,22 @@
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C32" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D32" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E32" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="F32" t="s">
-        <v>345</v>
+        <v>495</v>
       </c>
       <c r="I32">
         <v>1</v>
@@ -4233,22 +4223,22 @@
     </row>
     <row r="33" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" t="s">
         <v>40</v>
-      </c>
-      <c r="B33" t="s">
-        <v>41</v>
       </c>
       <c r="C33">
         <v>3</v>
       </c>
       <c r="D33" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E33" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="F33" t="s">
-        <v>462</v>
+        <v>449</v>
       </c>
       <c r="H33">
         <v>7</v>
@@ -4266,25 +4256,25 @@
     </row>
     <row r="34" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C34">
         <v>2</v>
       </c>
       <c r="D34" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E34" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="F34" t="s">
-        <v>473</v>
+        <v>458</v>
       </c>
       <c r="G34" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H34">
         <v>5</v>
@@ -4302,25 +4292,25 @@
     </row>
     <row r="35" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B35" t="s">
+        <v>42</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35" t="s">
         <v>43</v>
       </c>
-      <c r="C35">
-        <v>0</v>
-      </c>
-      <c r="D35" t="s">
-        <v>44</v>
-      </c>
       <c r="E35" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="F35" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="G35" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H35">
         <v>0</v>
@@ -4338,22 +4328,22 @@
     </row>
     <row r="36" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B36" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C36" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D36" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E36" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="F36" t="s">
-        <v>472</v>
+        <v>498</v>
       </c>
       <c r="L36">
         <v>1</v>
@@ -4365,22 +4355,22 @@
     </row>
     <row r="37" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B37" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C37">
         <v>1</v>
       </c>
       <c r="D37" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E37" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="F37" t="s">
-        <v>474</v>
+        <v>459</v>
       </c>
       <c r="H37">
         <v>3</v>
@@ -4398,10 +4388,10 @@
     </row>
     <row r="38" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="C38">
         <v>2</v>
@@ -4410,13 +4400,13 @@
         <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="F38" t="s">
-        <v>414</v>
+        <v>509</v>
       </c>
       <c r="G38" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="H38">
         <v>-9</v>
@@ -4434,22 +4424,22 @@
     </row>
     <row r="39" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C39">
         <v>0</v>
       </c>
       <c r="D39" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="E39" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="F39" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="H39">
         <v>0</v>
@@ -4467,22 +4457,22 @@
     </row>
     <row r="40" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C40" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D40" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E40" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="F40" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="I40">
         <v>1</v>
@@ -4494,25 +4484,25 @@
     </row>
     <row r="41" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" t="s">
         <v>46</v>
       </c>
-      <c r="B41" t="s">
-        <v>47</v>
-      </c>
       <c r="C41">
         <v>1</v>
       </c>
       <c r="D41" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E41" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="F41" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="G41" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H41">
         <v>10</v>
@@ -4533,10 +4523,10 @@
     </row>
     <row r="42" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C42">
         <v>3</v>
@@ -4545,13 +4535,13 @@
         <v>12</v>
       </c>
       <c r="E42" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="F42" t="s">
-        <v>465</v>
+        <v>451</v>
       </c>
       <c r="G42" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="H42">
         <v>-12</v>
@@ -4569,22 +4559,22 @@
     </row>
     <row r="43" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B43" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C43">
         <v>2</v>
       </c>
       <c r="D43" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E43" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="F43" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="H43">
         <v>5</v>
@@ -4602,22 +4592,22 @@
     </row>
     <row r="44" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B44" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C44" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D44" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E44" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="F44" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="K44">
         <v>1</v>
@@ -4629,22 +4619,22 @@
     </row>
     <row r="45" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B45" t="s">
         <v>49</v>
       </c>
-      <c r="B45" t="s">
-        <v>50</v>
-      </c>
       <c r="C45">
         <v>0</v>
       </c>
       <c r="D45" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E45" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="F45" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="H45">
         <v>0</v>
@@ -4662,22 +4652,22 @@
     </row>
     <row r="46" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C46">
         <v>2</v>
       </c>
       <c r="D46" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E46" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="F46" t="s">
-        <v>475</v>
+        <v>460</v>
       </c>
       <c r="H46">
         <v>5</v>
@@ -4695,22 +4685,22 @@
     </row>
     <row r="47" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="C47">
         <v>1</v>
       </c>
       <c r="D47" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E47" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="F47" t="s">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="H47">
         <v>4</v>
@@ -4734,22 +4724,22 @@
     </row>
     <row r="48" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C48" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D48" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E48" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="F48" t="s">
-        <v>454</v>
+        <v>496</v>
       </c>
       <c r="J48">
         <v>1</v>
@@ -4761,22 +4751,22 @@
     </row>
     <row r="49" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B49" t="s">
         <v>52</v>
-      </c>
-      <c r="B49" t="s">
-        <v>53</v>
       </c>
       <c r="C49">
         <v>3</v>
       </c>
       <c r="D49" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E49" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="F49" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="H49">
         <v>7</v>
@@ -4794,25 +4784,25 @@
     </row>
     <row r="50" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C50">
         <v>2</v>
       </c>
       <c r="D50" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E50" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="F50" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="G50" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H50">
         <v>5</v>
@@ -4830,10 +4820,10 @@
     </row>
     <row r="51" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C51">
         <v>2</v>
@@ -4842,13 +4832,13 @@
         <v>12</v>
       </c>
       <c r="E51" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="F51" t="s">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="G51" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="H51">
         <v>-9</v>
@@ -4872,22 +4862,22 @@
     </row>
     <row r="52" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C52" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D52" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E52" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="F52" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="J52">
         <v>1</v>
@@ -4899,22 +4889,22 @@
     </row>
     <row r="53" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B53" t="s">
         <v>56</v>
-      </c>
-      <c r="B53" t="s">
-        <v>57</v>
       </c>
       <c r="C53">
         <v>2</v>
       </c>
       <c r="D53" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="E53" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="F53" t="s">
-        <v>478</v>
+        <v>463</v>
       </c>
       <c r="H53">
         <v>1</v>
@@ -4935,22 +4925,22 @@
     </row>
     <row r="54" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C54">
         <v>1</v>
       </c>
       <c r="D54" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E54" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="F54" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="H54">
         <v>3</v>
@@ -4968,22 +4958,22 @@
     </row>
     <row r="55" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B55" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C55">
         <v>3</v>
       </c>
       <c r="D55" t="s">
+        <v>66</v>
+      </c>
+      <c r="E55" t="s">
+        <v>139</v>
+      </c>
+      <c r="F55" t="s">
         <v>67</v>
-      </c>
-      <c r="E55" t="s">
-        <v>146</v>
-      </c>
-      <c r="F55" t="s">
-        <v>68</v>
       </c>
       <c r="H55">
         <v>1</v>
@@ -5001,22 +4991,22 @@
     </row>
     <row r="56" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="B56" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="C56" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D56" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E56" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="F56" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="L56">
         <v>1</v>
@@ -5028,22 +5018,22 @@
     </row>
     <row r="57" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="B57" t="s">
+        <v>96</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+      <c r="D57" t="s">
+        <v>66</v>
+      </c>
+      <c r="E57" t="s">
+        <v>144</v>
+      </c>
+      <c r="F57" t="s">
         <v>97</v>
-      </c>
-      <c r="C57">
-        <v>1</v>
-      </c>
-      <c r="D57" t="s">
-        <v>67</v>
-      </c>
-      <c r="E57" t="s">
-        <v>151</v>
-      </c>
-      <c r="F57" t="s">
-        <v>98</v>
       </c>
       <c r="H57">
         <v>0</v>
@@ -5061,25 +5051,25 @@
     </row>
     <row r="58" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="B58" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C58">
         <v>2</v>
       </c>
       <c r="D58" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E58" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="F58" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="G58" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="H58">
         <v>-9</v>
@@ -5097,22 +5087,22 @@
     </row>
     <row r="59" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="B59" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C59">
         <v>1</v>
       </c>
       <c r="D59" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E59" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="F59" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="H59">
         <v>3</v>
@@ -5130,22 +5120,22 @@
     </row>
     <row r="60" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B60" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="C60">
         <v>0</v>
       </c>
       <c r="D60" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E60" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="F60" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="H60">
         <v>0</v>
@@ -5160,22 +5150,22 @@
     </row>
     <row r="61" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B61" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C61">
         <v>0</v>
       </c>
       <c r="D61" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E61" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="F61" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="H61">
         <v>0</v>
@@ -5190,22 +5180,22 @@
     </row>
     <row r="62" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B62" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C62">
         <v>0</v>
       </c>
       <c r="D62" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E62" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="F62" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="H62">
         <v>0</v>
@@ -5220,22 +5210,22 @@
     </row>
     <row r="63" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B63" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="C63">
         <v>0</v>
       </c>
       <c r="D63" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E63" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="F63" t="s">
-        <v>501</v>
+        <v>486</v>
       </c>
       <c r="H63">
         <v>0</v>
@@ -5253,22 +5243,22 @@
     </row>
     <row r="64" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B64" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="C64">
         <v>0</v>
       </c>
       <c r="D64" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="E64" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="F64" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="H64">
         <v>0</v>
@@ -5283,22 +5273,22 @@
     </row>
     <row r="65" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B65" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="C65">
         <v>0</v>
       </c>
       <c r="D65" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="E65" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="F65" t="s">
-        <v>510</v>
+        <v>493</v>
       </c>
       <c r="H65">
         <v>0</v>
@@ -5319,22 +5309,22 @@
     </row>
     <row r="66" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B66" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C66">
         <v>1</v>
       </c>
       <c r="D66" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E66" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="F66" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="H66">
         <v>9</v>
@@ -5352,22 +5342,22 @@
     </row>
     <row r="67" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B67" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C67">
         <v>3</v>
       </c>
       <c r="D67" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E67" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="F67" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="H67">
         <v>8</v>
@@ -5385,22 +5375,22 @@
     </row>
     <row r="68" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B68" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C68">
         <v>3</v>
       </c>
       <c r="D68" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E68" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="F68" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="H68">
         <v>8</v>
@@ -5418,22 +5408,22 @@
     </row>
     <row r="69" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B69" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C69">
         <v>1</v>
       </c>
       <c r="D69" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E69" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="F69" t="s">
-        <v>477</v>
+        <v>462</v>
       </c>
       <c r="H69">
         <v>7</v>
@@ -5457,22 +5447,22 @@
     </row>
     <row r="70" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B70" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="C70">
         <v>2</v>
       </c>
       <c r="D70" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E70" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="F70" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="H70">
         <v>3</v>
@@ -5493,22 +5483,22 @@
     </row>
     <row r="71" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B71" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="C71">
         <v>3</v>
       </c>
       <c r="D71" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E71" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="F71" t="s">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="H71">
         <v>15</v>
@@ -5526,22 +5516,22 @@
     </row>
     <row r="72" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B72" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="C72">
         <v>2</v>
       </c>
       <c r="D72" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E72" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="F72" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="H72">
         <v>12</v>
@@ -5559,22 +5549,22 @@
     </row>
     <row r="73" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B73" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="C73">
         <v>2</v>
       </c>
       <c r="D73" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E73" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="F73" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="H73">
         <v>11</v>
@@ -5592,22 +5582,22 @@
     </row>
     <row r="74" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B74" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C74">
         <v>1</v>
       </c>
       <c r="D74" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E74" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="F74" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H74">
         <v>3</v>
@@ -5625,22 +5615,22 @@
     </row>
     <row r="75" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B75" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C75">
         <v>2</v>
       </c>
       <c r="D75" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E75" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="F75" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="H75">
         <v>5</v>
@@ -5658,22 +5648,22 @@
     </row>
     <row r="76" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B76" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="C76">
         <v>3</v>
       </c>
       <c r="D76" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E76" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="F76" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="H76">
         <v>7</v>
@@ -5691,22 +5681,22 @@
     </row>
     <row r="77" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B77" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C77">
         <v>3</v>
       </c>
       <c r="D77" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E77" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="F77" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="H77">
         <v>6</v>
@@ -5727,22 +5717,22 @@
     </row>
     <row r="78" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B78" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C78">
         <v>3</v>
       </c>
       <c r="D78" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E78" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="F78" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="H78">
         <v>6</v>
@@ -5763,22 +5753,22 @@
     </row>
     <row r="79" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B79" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C79">
         <v>1</v>
       </c>
       <c r="D79" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E79" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="F79" t="s">
-        <v>482</v>
+        <v>467</v>
       </c>
       <c r="H79">
         <v>7</v>
@@ -5796,22 +5786,22 @@
     </row>
     <row r="80" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B80" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C80">
         <v>3</v>
       </c>
       <c r="D80" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E80" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="F80" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="H80">
         <v>8</v>
@@ -5829,22 +5819,22 @@
     </row>
     <row r="81" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B81" t="s">
+        <v>92</v>
+      </c>
+      <c r="C81">
+        <v>0</v>
+      </c>
+      <c r="D81" t="s">
+        <v>66</v>
+      </c>
+      <c r="E81" t="s">
+        <v>137</v>
+      </c>
+      <c r="F81" t="s">
         <v>93</v>
-      </c>
-      <c r="C81">
-        <v>0</v>
-      </c>
-      <c r="D81" t="s">
-        <v>67</v>
-      </c>
-      <c r="E81" t="s">
-        <v>144</v>
-      </c>
-      <c r="F81" t="s">
-        <v>94</v>
       </c>
       <c r="H81">
         <v>5</v>
@@ -5865,22 +5855,22 @@
     </row>
     <row r="82" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B82" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C82">
         <v>1</v>
       </c>
       <c r="D82" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="E82" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="F82" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="H82">
         <v>5</v>
@@ -5898,22 +5888,22 @@
     </row>
     <row r="83" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B83" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="C83">
         <v>2</v>
       </c>
       <c r="D83" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="E83" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="F83" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="H83">
         <v>3</v>
@@ -5934,22 +5924,22 @@
     </row>
     <row r="84" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B84" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="C84">
         <v>2</v>
       </c>
       <c r="D84" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="E84" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="F84" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="H84">
         <v>3</v>
@@ -5970,22 +5960,22 @@
     </row>
     <row r="85" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B85" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="C85">
         <v>3</v>
       </c>
       <c r="D85" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="E85" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="F85" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="H85">
         <v>8</v>
@@ -6003,22 +5993,22 @@
     </row>
     <row r="86" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B86" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="C86">
         <v>2</v>
       </c>
       <c r="D86" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="E86" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="F86" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="H86">
         <v>5</v>
@@ -6039,25 +6029,25 @@
     </row>
     <row r="87" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B87" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="C87">
         <v>1</v>
       </c>
       <c r="D87" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E87" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="F87" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="G87" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H87">
         <v>-6</v>
@@ -6078,25 +6068,25 @@
     </row>
     <row r="88" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B88" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="C88">
         <v>3</v>
       </c>
       <c r="D88" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E88" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="F88" t="s">
-        <v>481</v>
+        <v>466</v>
       </c>
       <c r="G88" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="H88">
         <v>-9</v>
@@ -6114,25 +6104,25 @@
     </row>
     <row r="89" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B89" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C89">
         <v>1</v>
       </c>
       <c r="D89" t="s">
+        <v>81</v>
+      </c>
+      <c r="E89" t="s">
+        <v>135</v>
+      </c>
+      <c r="F89" t="s">
+        <v>411</v>
+      </c>
+      <c r="G89" t="s">
         <v>82</v>
-      </c>
-      <c r="E89" t="s">
-        <v>142</v>
-      </c>
-      <c r="F89" t="s">
-        <v>422</v>
-      </c>
-      <c r="G89" t="s">
-        <v>83</v>
       </c>
       <c r="H89">
         <v>-6</v>
@@ -6153,10 +6143,10 @@
     </row>
     <row r="90" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B90" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="C90">
         <v>3</v>
@@ -6165,13 +6155,13 @@
         <v>12</v>
       </c>
       <c r="E90" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="F90" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="G90" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="H90">
         <v>-12</v>
@@ -6192,10 +6182,10 @@
     </row>
     <row r="91" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B91" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C91">
         <v>3</v>
@@ -6204,13 +6194,13 @@
         <v>12</v>
       </c>
       <c r="E91" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="F91" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="G91" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="H91">
         <v>-12</v>
@@ -6231,25 +6221,25 @@
     </row>
     <row r="92" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B92" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="C92">
         <v>1</v>
       </c>
       <c r="D92" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="E92" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F92" t="s">
-        <v>483</v>
+        <v>468</v>
       </c>
       <c r="G92" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H92">
         <v>-6</v>
@@ -6270,25 +6260,25 @@
     </row>
     <row r="93" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B93" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="C93">
         <v>3</v>
       </c>
       <c r="D93" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E93" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="F93" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="G93" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="H93">
         <v>-12</v>
@@ -6306,25 +6296,25 @@
     </row>
     <row r="94" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B94" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="C94">
         <v>2</v>
       </c>
       <c r="D94" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E94" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="F94" t="s">
-        <v>500</v>
+        <v>485</v>
       </c>
       <c r="G94" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="H94">
         <v>-9</v>
@@ -6348,22 +6338,22 @@
     </row>
     <row r="95" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B95" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C95">
         <v>0</v>
       </c>
       <c r="D95" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E95" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="F95" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="H95">
         <v>1</v>
@@ -6384,22 +6374,22 @@
     </row>
     <row r="96" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B96" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C96">
         <v>0</v>
       </c>
       <c r="D96" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E96" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="F96" t="s">
-        <v>484</v>
+        <v>469</v>
       </c>
       <c r="H96">
         <v>0</v>
@@ -6423,22 +6413,22 @@
     </row>
     <row r="97" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B97" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C97">
         <v>2</v>
       </c>
       <c r="D97" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E97" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="F97" t="s">
-        <v>485</v>
+        <v>470</v>
       </c>
       <c r="H97">
         <v>1</v>
@@ -6462,22 +6452,22 @@
     </row>
     <row r="98" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B98" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C98">
         <v>0</v>
       </c>
       <c r="D98" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E98" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="F98" t="s">
-        <v>486</v>
+        <v>471</v>
       </c>
       <c r="H98">
         <v>0</v>
@@ -6501,22 +6491,22 @@
     </row>
     <row r="99" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B99" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C99">
         <v>0</v>
       </c>
       <c r="D99" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="E99" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="F99" t="s">
-        <v>487</v>
+        <v>472</v>
       </c>
       <c r="H99">
         <v>3</v>
@@ -6537,22 +6527,22 @@
     </row>
     <row r="100" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B100" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="C100">
         <v>0</v>
       </c>
       <c r="D100" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="E100" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="F100" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="H100">
         <v>1</v>
@@ -6573,22 +6563,22 @@
     </row>
     <row r="101" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B101" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="C101">
         <v>0</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="E101" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="F101" t="s">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="H101">
         <v>0</v>
@@ -6608,22 +6598,22 @@
     </row>
     <row r="102" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B102" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="C102">
         <v>0</v>
       </c>
       <c r="D102" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E102" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="F102" t="s">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="H102">
         <v>2</v>
@@ -6647,22 +6637,22 @@
     </row>
     <row r="103" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B103" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="C103">
         <v>0</v>
       </c>
       <c r="D103" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E103" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="F103" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="H103">
         <v>1</v>
@@ -6686,22 +6676,22 @@
     </row>
     <row r="104" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B104" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C104">
         <v>0</v>
       </c>
       <c r="D104" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E104" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="F104" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="H104">
         <v>0</v>
@@ -6719,22 +6709,22 @@
     </row>
     <row r="105" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B105" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="C105">
         <v>0</v>
       </c>
       <c r="D105" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E105" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="F105" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="H105">
         <v>0</v>
@@ -6752,22 +6742,22 @@
     </row>
     <row r="106" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B106" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="C106">
         <v>1</v>
       </c>
       <c r="D106" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="E106" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="F106" t="s">
-        <v>427</v>
+        <v>416</v>
       </c>
       <c r="H106">
         <v>3</v>
@@ -6785,22 +6775,22 @@
     </row>
     <row r="107" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B107" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C107">
         <v>2</v>
       </c>
       <c r="D107" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E107" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="F107" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="H107">
         <v>0</v>
@@ -6821,22 +6811,22 @@
     </row>
     <row r="108" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B108" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="C108">
         <v>2</v>
       </c>
       <c r="D108" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E108" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="F108" t="s">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="H108">
         <v>5</v>
@@ -6857,22 +6847,22 @@
     </row>
     <row r="109" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B109" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="C109">
         <v>2</v>
       </c>
       <c r="D109" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="E109" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="F109" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="H109">
         <v>0</v>
@@ -6893,22 +6883,22 @@
     </row>
     <row r="110" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B110" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="C110">
         <v>3</v>
       </c>
       <c r="D110" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="E110" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="F110" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="H110">
         <v>6</v>
@@ -6929,22 +6919,22 @@
     </row>
     <row r="111" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B111" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="C111">
         <v>0</v>
       </c>
       <c r="D111" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="E111" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="F111" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="H111">
         <v>6</v>
@@ -6962,22 +6952,22 @@
     </row>
     <row r="112" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B112" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="C112">
         <v>0</v>
       </c>
       <c r="D112" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="E112" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="F112" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="H112">
         <v>1</v>
@@ -6995,22 +6985,22 @@
     </row>
     <row r="113" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B113" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="C113">
         <v>0</v>
       </c>
       <c r="D113" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="E113" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="F113" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="H113">
         <v>1</v>
@@ -7028,22 +7018,22 @@
     </row>
     <row r="114" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B114" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C114">
         <v>0</v>
       </c>
       <c r="D114" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="E114" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="F114" t="s">
-        <v>502</v>
+        <v>487</v>
       </c>
       <c r="H114">
         <v>1</v>
@@ -7064,22 +7054,22 @@
     </row>
     <row r="115" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B115" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C115">
         <v>0</v>
       </c>
       <c r="D115" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="E115" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="F115" t="s">
-        <v>488</v>
+        <v>473</v>
       </c>
       <c r="H115">
         <v>1</v>
@@ -7097,22 +7087,22 @@
     </row>
     <row r="116" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B116" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="C116">
         <v>1</v>
       </c>
       <c r="D116" t="s">
+        <v>169</v>
+      </c>
+      <c r="E116" t="s">
         <v>176</v>
       </c>
-      <c r="E116" t="s">
-        <v>183</v>
-      </c>
       <c r="F116" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="H116">
         <v>3</v>
@@ -7130,22 +7120,22 @@
     </row>
     <row r="117" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B117" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C117">
         <v>1</v>
       </c>
       <c r="D117" t="s">
+        <v>169</v>
+      </c>
+      <c r="E117" t="s">
         <v>176</v>
       </c>
-      <c r="E117" t="s">
-        <v>183</v>
-      </c>
       <c r="F117" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="H117">
         <v>3</v>
@@ -7166,22 +7156,22 @@
     </row>
     <row r="118" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B118" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="C118">
         <v>0</v>
       </c>
       <c r="D118" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="E118" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="F118" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="H118">
         <v>1</v>
@@ -7199,22 +7189,22 @@
     </row>
     <row r="119" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B119" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="C119">
         <v>1</v>
       </c>
       <c r="D119" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="E119" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="F119" t="s">
-        <v>489</v>
+        <v>474</v>
       </c>
       <c r="H119">
         <v>3</v>
@@ -7232,25 +7222,25 @@
     </row>
     <row r="120" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B120" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C120">
         <v>1</v>
       </c>
       <c r="D120" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="E120" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="F120" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="G120" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H120">
         <v>-6</v>
@@ -7268,25 +7258,25 @@
     </row>
     <row r="121" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B121" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C121">
         <v>1</v>
       </c>
       <c r="D121" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="E121" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="F121" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="G121" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H121">
         <v>-6</v>
@@ -7304,10 +7294,10 @@
     </row>
     <row r="122" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B122" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="C122">
         <v>3</v>
@@ -7316,13 +7306,13 @@
         <v>12</v>
       </c>
       <c r="E122" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="F122" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="G122" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="H122">
         <v>-12</v>
@@ -7343,25 +7333,25 @@
     </row>
     <row r="123" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B123" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="C123">
         <v>2</v>
       </c>
       <c r="D123" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="E123" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="F123" t="s">
-        <v>490</v>
+        <v>475</v>
       </c>
       <c r="G123" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="H123">
         <v>-9</v>
@@ -7379,10 +7369,10 @@
     </row>
     <row r="124" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B124" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="C124">
         <v>3</v>
@@ -7391,13 +7381,13 @@
         <v>12</v>
       </c>
       <c r="E124" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="F124" t="s">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="G124" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="H124">
         <v>-9</v>
@@ -7415,25 +7405,25 @@
     </row>
     <row r="125" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B125" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C125">
         <v>1</v>
       </c>
       <c r="D125" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E125" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="F125" t="s">
-        <v>491</v>
+        <v>476</v>
       </c>
       <c r="G125" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H125">
         <v>-6</v>
@@ -7451,25 +7441,25 @@
     </row>
     <row r="126" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A126" s="4" t="s">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="B126" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C126">
         <v>1</v>
       </c>
       <c r="D126" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E126" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="F126" t="s">
-        <v>471</v>
+        <v>457</v>
       </c>
       <c r="G126" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="H126">
         <v>-6</v>
@@ -7487,25 +7477,25 @@
     </row>
     <row r="127" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B127" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="C127">
         <v>2</v>
       </c>
       <c r="D127" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E127" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="F127" t="s">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="G127" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="H127">
         <v>-9</v>
@@ -7523,25 +7513,25 @@
     </row>
     <row r="128" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B128" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="C128">
         <v>2</v>
       </c>
       <c r="D128" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E128" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="F128" t="s">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="G128" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="H128">
         <v>-9</v>
@@ -7559,25 +7549,25 @@
     </row>
     <row r="129" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B129" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="C129">
         <v>2</v>
       </c>
       <c r="D129" t="s">
+        <v>395</v>
+      </c>
+      <c r="E129" t="s">
+        <v>136</v>
+      </c>
+      <c r="F129" t="s">
+        <v>478</v>
+      </c>
+      <c r="G129" t="s">
         <v>404</v>
-      </c>
-      <c r="E129" t="s">
-        <v>143</v>
-      </c>
-      <c r="F129" t="s">
-        <v>493</v>
-      </c>
-      <c r="G129" t="s">
-        <v>413</v>
       </c>
       <c r="H129">
         <v>-9</v>
@@ -7591,10 +7581,10 @@
     </row>
     <row r="130" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B130" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="C130">
         <v>3</v>
@@ -7603,13 +7593,13 @@
         <v>12</v>
       </c>
       <c r="E130" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="F130" t="s">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="G130" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="H130">
         <v>-9</v>
@@ -7627,25 +7617,25 @@
     </row>
     <row r="131" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B131" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="C131">
         <v>2</v>
       </c>
       <c r="D131" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E131" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="F131" t="s">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="G131" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="H131">
         <v>-9</v>
@@ -7663,25 +7653,25 @@
     </row>
     <row r="132" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B132" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C132">
         <v>2</v>
       </c>
       <c r="D132" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E132" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="F132" t="s">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="G132" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="H132">
         <v>-9</v>
@@ -7699,22 +7689,22 @@
     </row>
     <row r="133" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B133" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="C133">
         <v>0</v>
       </c>
       <c r="D133" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E133" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="F133" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="H133">
         <v>1</v>
@@ -7732,22 +7722,22 @@
     </row>
     <row r="134" spans="1:34" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B134" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="C134">
         <v>3</v>
       </c>
       <c r="D134" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="E134" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="F134" t="s">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="H134">
         <v>0</v>
@@ -7768,22 +7758,22 @@
     </row>
     <row r="135" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B135" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="C135">
         <v>3</v>
       </c>
       <c r="D135" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="E135" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="F135" t="s">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="H135">
         <v>0</v>
@@ -7804,22 +7794,22 @@
     </row>
     <row r="136" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B136" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="C136">
         <v>0</v>
       </c>
       <c r="D136" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="E136" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="F136" t="s">
-        <v>507</v>
+        <v>490</v>
       </c>
       <c r="H136">
         <v>12</v>
@@ -7837,22 +7827,22 @@
     </row>
     <row r="137" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B137" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C137">
         <v>0</v>
       </c>
       <c r="D137" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="E137" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="F137" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="H137">
         <v>0</v>
@@ -7870,22 +7860,22 @@
     </row>
     <row r="138" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B138" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C138">
         <v>0</v>
       </c>
       <c r="D138" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="E138" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="F138" t="s">
-        <v>508</v>
+        <v>491</v>
       </c>
       <c r="H138">
         <v>10</v>
@@ -7903,22 +7893,22 @@
     </row>
     <row r="139" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B139" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="C139">
         <v>0</v>
       </c>
       <c r="D139" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="E139" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="F139" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="H139">
         <v>0</v>
@@ -7936,22 +7926,22 @@
     </row>
     <row r="140" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A140" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B140" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="C140">
         <v>1</v>
       </c>
       <c r="D140" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="E140" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="F140" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="H140">
         <v>11</v>
@@ -7969,22 +7959,22 @@
     </row>
     <row r="141" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B141" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="C141">
         <v>0</v>
       </c>
       <c r="D141" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="E141" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="F141" t="s">
-        <v>509</v>
+        <v>492</v>
       </c>
       <c r="H141">
         <v>8</v>
@@ -8002,22 +7992,22 @@
     </row>
     <row r="142" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B142" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="C142">
         <v>1</v>
       </c>
       <c r="D142" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="E142" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="F142" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="H142">
         <v>0</v>
@@ -8041,22 +8031,22 @@
     </row>
     <row r="143" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B143" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="C143">
         <v>0</v>
       </c>
       <c r="D143" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="E143" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="F143" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="H143">
         <v>0</v>
@@ -8074,22 +8064,22 @@
     </row>
     <row r="144" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A144" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B144" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="C144">
         <v>0</v>
       </c>
       <c r="D144" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E144" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="F144" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="H144">
         <v>1</v>
@@ -8107,22 +8097,22 @@
     </row>
     <row r="145" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B145" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="C145">
         <v>2</v>
       </c>
       <c r="D145" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E145" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="F145" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="H145">
         <v>0</v>
@@ -8143,22 +8133,22 @@
     </row>
     <row r="146" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A146" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B146" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="C146">
         <v>0</v>
       </c>
       <c r="D146" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E146" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="F146" t="s">
-        <v>480</v>
+        <v>465</v>
       </c>
       <c r="H146">
         <v>0</v>
@@ -8176,22 +8166,22 @@
     </row>
     <row r="147" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B147" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="C147">
         <v>0</v>
       </c>
       <c r="D147" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E147" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="F147" t="s">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="H147">
         <v>0</v>
@@ -8209,22 +8199,22 @@
     </row>
     <row r="148" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="B148" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="C148">
         <v>0</v>
       </c>
       <c r="D148" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="E148" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="F148" t="s">
-        <v>496</v>
+        <v>481</v>
       </c>
       <c r="H148">
         <v>0</v>
@@ -8248,22 +8238,22 @@
     </row>
     <row r="149" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="B149" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="C149">
         <v>3</v>
       </c>
       <c r="D149" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="E149" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="F149" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="H149">
         <v>0</v>
@@ -8281,22 +8271,22 @@
     </row>
     <row r="150" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A150" s="4" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="B150" t="s">
-        <v>467</v>
+        <v>453</v>
       </c>
       <c r="C150">
         <v>1</v>
       </c>
       <c r="D150" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="E150" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="F150" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="H150">
         <v>0</v>
@@ -8314,22 +8304,22 @@
     </row>
     <row r="151" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A151" s="4" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="B151" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="C151">
         <v>0</v>
       </c>
       <c r="D151" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="E151" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="F151" t="s">
-        <v>497</v>
+        <v>482</v>
       </c>
       <c r="H151">
         <v>0</v>
@@ -8353,22 +8343,22 @@
     </row>
     <row r="152" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A152" s="4" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="B152" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="C152">
         <v>3</v>
       </c>
       <c r="D152" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="E152" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="F152" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="H152">
         <v>0</v>
@@ -8407,10 +8397,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="F1" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="G1" t="s">
         <v>4</v>
@@ -8425,99 +8415,99 @@
         <v>7</v>
       </c>
       <c r="K1" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="L1" t="s">
         <v>8</v>
       </c>
       <c r="M1" t="s">
+        <v>78</v>
+      </c>
+      <c r="N1" t="s">
         <v>79</v>
       </c>
-      <c r="N1" t="s">
-        <v>80</v>
-      </c>
       <c r="O1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P1" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="Q1" t="s">
+        <v>131</v>
+      </c>
+      <c r="R1" t="s">
+        <v>132</v>
+      </c>
+      <c r="S1" t="s">
+        <v>133</v>
+      </c>
+      <c r="T1" t="s">
+        <v>165</v>
+      </c>
+      <c r="U1" t="s">
+        <v>134</v>
+      </c>
+      <c r="V1" t="s">
+        <v>135</v>
+      </c>
+      <c r="W1" t="s">
+        <v>136</v>
+      </c>
+      <c r="X1" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y1" t="s">
         <v>138</v>
       </c>
-      <c r="R1" t="s">
+      <c r="Z1" t="s">
         <v>139</v>
       </c>
-      <c r="S1" t="s">
+      <c r="AA1" t="s">
         <v>140</v>
       </c>
-      <c r="T1" t="s">
-        <v>172</v>
-      </c>
-      <c r="U1" t="s">
+      <c r="AB1" t="s">
         <v>141</v>
       </c>
-      <c r="V1" t="s">
+      <c r="AC1" t="s">
+        <v>144</v>
+      </c>
+      <c r="AD1" t="s">
         <v>142</v>
       </c>
-      <c r="W1" t="s">
+      <c r="AE1" t="s">
+        <v>166</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>278</v>
+      </c>
+      <c r="AG1" t="s">
         <v>143</v>
       </c>
-      <c r="X1" t="s">
-        <v>144</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>145</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>146</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>147</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>148</v>
-      </c>
-      <c r="AC1" t="s">
+      <c r="AH1" t="s">
         <v>151</v>
       </c>
-      <c r="AD1" t="s">
-        <v>149</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>173</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>285</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>150</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>158</v>
-      </c>
       <c r="AI1" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="AJ1" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E2" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="F2" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -8535,19 +8525,19 @@
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E3" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="F3" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="L3">
         <v>1</v>
@@ -8565,22 +8555,22 @@
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
       <c r="D4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E4" t="s">
+        <v>136</v>
+      </c>
+      <c r="F4" t="s">
+        <v>300</v>
+      </c>
+      <c r="G4" t="s">
         <v>82</v>
-      </c>
-      <c r="E4" t="s">
-        <v>143</v>
-      </c>
-      <c r="F4" t="s">
-        <v>308</v>
-      </c>
-      <c r="G4" t="s">
-        <v>83</v>
       </c>
       <c r="H4">
         <v>-9</v>
@@ -8601,19 +8591,19 @@
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="E5" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="F5" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -8628,25 +8618,25 @@
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B6" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E6" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="F6" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="G6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H6">
         <v>-6</v>
@@ -8667,22 +8657,22 @@
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B7" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="E7" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="F7" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -8703,22 +8693,22 @@
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B8" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E8" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="F8" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -8736,22 +8726,22 @@
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B9" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E9" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="F9" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="H9">
         <v>2</v>
@@ -8766,22 +8756,22 @@
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
       <c r="D10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E10" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="F10" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="H10">
         <v>6</v>
@@ -8802,53 +8792,53 @@
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="C12" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D12" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="C13" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="D13" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B15" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="C15">
         <v>2</v>
       </c>
       <c r="D15" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E15" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="F15" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="G15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H15">
         <v>-9</v>
@@ -8866,10 +8856,10 @@
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C16">
         <v>2</v>
@@ -8878,13 +8868,13 @@
         <v>12</v>
       </c>
       <c r="E16" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="F16" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="G16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H16">
         <v>-9</v>
@@ -8908,25 +8898,25 @@
     </row>
     <row r="17" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B17" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="C17">
         <v>3</v>
       </c>
       <c r="D17" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E17" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="F17" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="G17" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="H17">
         <v>-12</v>
@@ -8950,22 +8940,22 @@
     </row>
     <row r="18" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B18" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E18" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="F18" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="H18">
         <v>3</v>
@@ -8983,10 +8973,10 @@
     </row>
     <row r="19" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -8995,13 +8985,13 @@
         <v>12</v>
       </c>
       <c r="E19" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="F19" t="s">
-        <v>466</v>
+        <v>452</v>
       </c>
       <c r="G19" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="H19">
         <v>2</v>
@@ -9038,240 +9028,240 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" t="s">
         <v>105</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>106</v>
-      </c>
-      <c r="D1" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C2" t="s">
+        <v>499</v>
+      </c>
+      <c r="D2" t="s">
         <v>108</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="C3" t="s">
-        <v>114</v>
+        <v>500</v>
       </c>
       <c r="D3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="C4" t="s">
-        <v>117</v>
+        <v>501</v>
       </c>
       <c r="D4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="C5" t="s">
-        <v>124</v>
+        <v>502</v>
       </c>
       <c r="D5" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="C6" t="s">
-        <v>126</v>
+        <v>503</v>
       </c>
       <c r="D6" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="C7" t="s">
-        <v>129</v>
+        <v>504</v>
       </c>
       <c r="D7" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>511</v>
+        <v>494</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="C8" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="D8" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="C9" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="D9" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="C10" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="D10" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="C11" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="D11" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="C12" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="D12" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="C13" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="D13" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="C14" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="D14" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="C15" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="D15" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="C16" t="s">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="D16" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="C17" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="D17" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>
@@ -9291,16 +9281,16 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="B1" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D1" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="E1">
         <v>1</v>
@@ -9323,7 +9313,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -9332,30 +9322,30 @@
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="E2" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="F2" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="G2" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="H2" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="I2" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="J2" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -9364,27 +9354,27 @@
         <v>6</v>
       </c>
       <c r="E3" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="F3" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="G3" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="H3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="I3" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="J3" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -9393,27 +9383,27 @@
         <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="F4" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="G4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="H4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="I4" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="J4" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -9422,27 +9412,27 @@
         <v>7</v>
       </c>
       <c r="E5" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="F5" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="G5" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H5" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="I5" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="J5" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>498</v>
+        <v>483</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -9451,22 +9441,22 @@
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="F6" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="G6" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="H6" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="I6" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="J6" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>

--- a/card_design.xlsx
+++ b/card_design.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\life\board_game\project_six_dynasty\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3C286D7-84BB-48A8-BCE1-B8AA1F62F2AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D406DC93-0F2B-4478-A71E-B51D7DC4B038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="811" xr2:uid="{F283CFD4-9FFB-4A79-AF0F-7443CC209F7A}"/>
   </bookViews>
@@ -1121,10 +1121,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>被动：每次打出[文化]牌或者执行[文化]策略时，获得2vp。登场：先动值3。转化[张掖][姑臧]。获得1功绩和1威望。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>如果有一条从[姑臧]到[建康]的全部地点被东晋势力占据的线路，可以打出，然后存档此牌。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1141,10 +1137,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>被动：每次执行[内政]策略或者打出[内政]牌时，获得2vp。登场：先动值2。转化[吴][会稽]。获得1功绩和1威望。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>存档此牌。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1585,18 +1577,10 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>被动：每次存档1张牌时，获得2vp。登场：先动值4。转化[南郡][襄阳]。获得1功绩和1威望。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>主动：[进军]1次，费用减2。被动：每次结算[进军]后，获得1vp。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>被动：每次结算[转化]后，摸1张牌并获得1vp。登场：先动值6。获得4军力。获得2威望。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>主动：免费[加固]友方地点1次。如果[加固]的目标不是你占据的地点，额外获得1vp。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1945,22 +1929,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>被动：每次获得功绩后，摸1张牌。登场：先动值7。获得1威望和1功绩（不触发被动效果）。在其他东晋玩家完成登场效果后，转化2个[建康]以外的司马家地点。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>被动：幕僚区空位总数为5。主动：如果拥有4种不同的标记，获得1个朝堂行动；否则，可以打出1张幕僚牌。登场：先动值8。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>被动：任意玩家提高行动顺位时，获得2vp。每次打出[权谋]标记时，获得2vp。登场：先动值1。获得2顺位，2功绩和2威望，转化[合肥][寿春]。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>被动：每次存档或弃置[流民]时，获得1军力或2vp。登场：先动值5。转化[京口][广陵]。获得1功绩和1威望。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>友方控制[巴蜀]区域</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -2002,6 +1970,38 @@
   </si>
   <si>
     <t>行动：获得5军力。限定：占据[京口]时，才能打出、执行或征发。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>被动：任意玩家提高行动顺位时，获得2vp。每次打出[权谋]标记时，获得2vp。登场：先动值8。获得2顺位，2功绩和2威望，转化[合肥][寿春]。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>被动：每次获得功绩后，摸1张牌。登场：先动值2。获得1威望和1功绩（不触发被动效果）。在其他东晋玩家完成登场效果后，转化2个[建康]以外的司马家地点。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>被动：每次存档或弃置[流民]时，获得1军力或2vp。登场：先动值4。转化[京口][广陵]。获得1功绩和1威望。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>被动：每次打出[文化]牌或者执行[文化]策略时，获得2vp。登场：先动值6。转化[张掖][姑臧]。获得1功绩和1威望。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>被动：每次存档1张牌时，获得2vp。登场：先动值5。转化[南郡][襄阳]。获得1功绩和1威望。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>被动：幕僚区空位总数为5。主动：如果拥有4种不同的标记，获得1个朝堂行动；否则，可以打出1张幕僚牌。登场：先动值1。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>被动：每次结算[转化]后，摸1张牌并获得1vp。登场：先动值3。获得4军力。获得2威望。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>被动：每次执行[内政]策略或者打出[内政]牌时，获得2vp。登场：先动值7。转化[吴][会稽]。获得1功绩和1威望。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -3303,22 +3303,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5" t="s">
+        <v>393</v>
+      </c>
+      <c r="E5" t="s">
+        <v>394</v>
+      </c>
+      <c r="F5" t="s">
         <v>395</v>
       </c>
-      <c r="E5" t="s">
+      <c r="G5" t="s">
         <v>396</v>
-      </c>
-      <c r="F5" t="s">
-        <v>397</v>
-      </c>
-      <c r="G5" t="s">
-        <v>398</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -3347,7 +3347,7 @@
         <v>62</v>
       </c>
       <c r="G6" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -3377,10 +3377,10 @@
         <v>162</v>
       </c>
       <c r="F7" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="G7" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -3410,7 +3410,7 @@
         <v>162</v>
       </c>
       <c r="F8" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="G8" t="s">
         <v>61</v>
@@ -3443,10 +3443,10 @@
         <v>162</v>
       </c>
       <c r="F9" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="G9" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -3467,7 +3467,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -3479,10 +3479,10 @@
         <v>162</v>
       </c>
       <c r="F10" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="G10" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="H10">
         <v>-9</v>
@@ -3512,7 +3512,7 @@
         <v>163</v>
       </c>
       <c r="F11" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="L11">
         <v>1</v>
@@ -3539,7 +3539,7 @@
         <v>131</v>
       </c>
       <c r="F12" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="H12">
         <v>7</v>
@@ -3572,7 +3572,7 @@
         <v>133</v>
       </c>
       <c r="F13" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="H13">
         <v>5</v>
@@ -3605,10 +3605,10 @@
         <v>136</v>
       </c>
       <c r="F14" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="G14" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="H14">
         <v>-6</v>
@@ -3641,7 +3641,7 @@
         <v>163</v>
       </c>
       <c r="F15" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -3668,10 +3668,10 @@
         <v>136</v>
       </c>
       <c r="F16" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="G16" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="H16">
         <v>2</v>
@@ -3707,10 +3707,10 @@
         <v>134</v>
       </c>
       <c r="F17" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="G17" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H17">
         <v>-12</v>
@@ -3743,7 +3743,7 @@
         <v>131</v>
       </c>
       <c r="F18" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="H18">
         <v>7</v>
@@ -3776,7 +3776,7 @@
         <v>163</v>
       </c>
       <c r="F19" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -3803,7 +3803,7 @@
         <v>136</v>
       </c>
       <c r="F20" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="G20" t="s">
         <v>61</v>
@@ -3842,7 +3842,7 @@
         <v>132</v>
       </c>
       <c r="F21" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="H21">
         <v>5</v>
@@ -3908,7 +3908,7 @@
         <v>133</v>
       </c>
       <c r="F23" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H23">
         <v>5</v>
@@ -3941,7 +3941,7 @@
         <v>165</v>
       </c>
       <c r="F24" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="H24">
         <v>5</v>
@@ -3974,7 +3974,7 @@
         <v>198</v>
       </c>
       <c r="F25" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H25">
         <v>3</v>
@@ -4007,7 +4007,7 @@
         <v>133</v>
       </c>
       <c r="F26" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="H26">
         <v>3</v>
@@ -4040,7 +4040,7 @@
         <v>139</v>
       </c>
       <c r="F27" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -4073,7 +4073,7 @@
         <v>164</v>
       </c>
       <c r="F28" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="K28">
         <v>1</v>
@@ -4100,7 +4100,7 @@
         <v>165</v>
       </c>
       <c r="F29" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="G29" t="s">
         <v>13</v>
@@ -4136,7 +4136,7 @@
         <v>133</v>
       </c>
       <c r="F30" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="G30" t="s">
         <v>13</v>
@@ -4172,7 +4172,7 @@
         <v>217</v>
       </c>
       <c r="F31" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="G31" t="s">
         <v>206</v>
@@ -4211,7 +4211,7 @@
         <v>164</v>
       </c>
       <c r="F32" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="I32">
         <v>1</v>
@@ -4238,7 +4238,7 @@
         <v>131</v>
       </c>
       <c r="F33" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="H33">
         <v>7</v>
@@ -4271,7 +4271,7 @@
         <v>165</v>
       </c>
       <c r="F34" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="G34" t="s">
         <v>13</v>
@@ -4307,7 +4307,7 @@
         <v>141</v>
       </c>
       <c r="F35" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G35" t="s">
         <v>13</v>
@@ -4343,7 +4343,7 @@
         <v>164</v>
       </c>
       <c r="F36" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="L36">
         <v>1</v>
@@ -4370,7 +4370,7 @@
         <v>132</v>
       </c>
       <c r="F37" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="H37">
         <v>3</v>
@@ -4403,10 +4403,10 @@
         <v>134</v>
       </c>
       <c r="F38" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="G38" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="H38">
         <v>-9</v>
@@ -4439,7 +4439,7 @@
         <v>210</v>
       </c>
       <c r="F39" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="H39">
         <v>0</v>
@@ -4472,7 +4472,7 @@
         <v>164</v>
       </c>
       <c r="F40" t="s">
-        <v>289</v>
+        <v>505</v>
       </c>
       <c r="I40">
         <v>1</v>
@@ -4499,7 +4499,7 @@
         <v>140</v>
       </c>
       <c r="F41" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G41" t="s">
         <v>13</v>
@@ -4538,10 +4538,10 @@
         <v>134</v>
       </c>
       <c r="F42" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="G42" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H42">
         <v>-12</v>
@@ -4574,7 +4574,7 @@
         <v>131</v>
       </c>
       <c r="F43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H43">
         <v>5</v>
@@ -4607,7 +4607,7 @@
         <v>164</v>
       </c>
       <c r="F44" t="s">
-        <v>405</v>
+        <v>506</v>
       </c>
       <c r="K44">
         <v>1</v>
@@ -4634,7 +4634,7 @@
         <v>141</v>
       </c>
       <c r="F45" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="H45">
         <v>0</v>
@@ -4667,7 +4667,7 @@
         <v>131</v>
       </c>
       <c r="F46" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="H46">
         <v>5</v>
@@ -4700,7 +4700,7 @@
         <v>166</v>
       </c>
       <c r="F47" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="H47">
         <v>4</v>
@@ -4739,7 +4739,7 @@
         <v>164</v>
       </c>
       <c r="F48" t="s">
-        <v>496</v>
+        <v>507</v>
       </c>
       <c r="J48">
         <v>1</v>
@@ -4766,7 +4766,7 @@
         <v>131</v>
       </c>
       <c r="F49" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="H49">
         <v>7</v>
@@ -4799,7 +4799,7 @@
         <v>132</v>
       </c>
       <c r="F50" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G50" t="s">
         <v>13</v>
@@ -4835,10 +4835,10 @@
         <v>134</v>
       </c>
       <c r="F51" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="G51" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H51">
         <v>-9</v>
@@ -4877,7 +4877,7 @@
         <v>164</v>
       </c>
       <c r="F52" t="s">
-        <v>407</v>
+        <v>508</v>
       </c>
       <c r="J52">
         <v>1</v>
@@ -4904,7 +4904,7 @@
         <v>139</v>
       </c>
       <c r="F53" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="H53">
         <v>1</v>
@@ -4940,7 +4940,7 @@
         <v>133</v>
       </c>
       <c r="F54" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H54">
         <v>3</v>
@@ -4991,10 +4991,10 @@
     </row>
     <row r="56" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B56" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C56" t="s">
         <v>13</v>
@@ -5006,7 +5006,7 @@
         <v>164</v>
       </c>
       <c r="F56" t="s">
-        <v>294</v>
+        <v>509</v>
       </c>
       <c r="L56">
         <v>1</v>
@@ -5018,7 +5018,7 @@
     </row>
     <row r="57" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B57" t="s">
         <v>96</v>
@@ -5051,7 +5051,7 @@
     </row>
     <row r="58" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B58" t="s">
         <v>100</v>
@@ -5066,10 +5066,10 @@
         <v>134</v>
       </c>
       <c r="F58" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G58" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="H58">
         <v>-9</v>
@@ -5087,7 +5087,7 @@
     </row>
     <row r="59" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B59" t="s">
         <v>98</v>
@@ -5102,7 +5102,7 @@
         <v>131</v>
       </c>
       <c r="F59" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="H59">
         <v>3</v>
@@ -5120,10 +5120,10 @@
     </row>
     <row r="60" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B60" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -5135,7 +5135,7 @@
         <v>142</v>
       </c>
       <c r="F60" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="H60">
         <v>0</v>
@@ -5150,7 +5150,7 @@
     </row>
     <row r="61" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B61" t="s">
         <v>58</v>
@@ -5165,7 +5165,7 @@
         <v>142</v>
       </c>
       <c r="F61" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H61">
         <v>0</v>
@@ -5180,7 +5180,7 @@
     </row>
     <row r="62" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B62" t="s">
         <v>59</v>
@@ -5210,10 +5210,10 @@
     </row>
     <row r="63" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B63" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -5225,7 +5225,7 @@
         <v>142</v>
       </c>
       <c r="F63" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="H63">
         <v>0</v>
@@ -5243,10 +5243,10 @@
     </row>
     <row r="64" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B64" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -5258,7 +5258,7 @@
         <v>213</v>
       </c>
       <c r="F64" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="H64">
         <v>0</v>
@@ -5273,22 +5273,22 @@
     </row>
     <row r="65" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B65" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C65">
         <v>0</v>
       </c>
       <c r="D65" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E65" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F65" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="H65">
         <v>0</v>
@@ -5309,7 +5309,7 @@
     </row>
     <row r="66" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B66" t="s">
         <v>60</v>
@@ -5342,7 +5342,7 @@
     </row>
     <row r="67" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B67" t="s">
         <v>85</v>
@@ -5357,7 +5357,7 @@
         <v>140</v>
       </c>
       <c r="F67" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H67">
         <v>8</v>
@@ -5375,7 +5375,7 @@
     </row>
     <row r="68" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B68" t="s">
         <v>86</v>
@@ -5390,7 +5390,7 @@
         <v>140</v>
       </c>
       <c r="F68" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H68">
         <v>8</v>
@@ -5408,7 +5408,7 @@
     </row>
     <row r="69" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B69" t="s">
         <v>102</v>
@@ -5423,7 +5423,7 @@
         <v>140</v>
       </c>
       <c r="F69" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="H69">
         <v>7</v>
@@ -5447,7 +5447,7 @@
     </row>
     <row r="70" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B70" t="s">
         <v>268</v>
@@ -5462,7 +5462,7 @@
         <v>269</v>
       </c>
       <c r="F70" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="H70">
         <v>3</v>
@@ -5483,7 +5483,7 @@
     </row>
     <row r="71" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B71" t="s">
         <v>270</v>
@@ -5498,7 +5498,7 @@
         <v>269</v>
       </c>
       <c r="F71" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="H71">
         <v>15</v>
@@ -5516,7 +5516,7 @@
     </row>
     <row r="72" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B72" t="s">
         <v>271</v>
@@ -5549,7 +5549,7 @@
     </row>
     <row r="73" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B73" t="s">
         <v>276</v>
@@ -5564,7 +5564,7 @@
         <v>269</v>
       </c>
       <c r="F73" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="H73">
         <v>11</v>
@@ -5582,7 +5582,7 @@
     </row>
     <row r="74" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B74" t="s">
         <v>71</v>
@@ -5615,7 +5615,7 @@
     </row>
     <row r="75" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B75" t="s">
         <v>145</v>
@@ -5648,7 +5648,7 @@
     </row>
     <row r="76" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B76" t="s">
         <v>147</v>
@@ -5663,7 +5663,7 @@
         <v>131</v>
       </c>
       <c r="F76" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="H76">
         <v>7</v>
@@ -5681,7 +5681,7 @@
     </row>
     <row r="77" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B77" t="s">
         <v>72</v>
@@ -5696,7 +5696,7 @@
         <v>137</v>
       </c>
       <c r="F77" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="H77">
         <v>6</v>
@@ -5717,7 +5717,7 @@
     </row>
     <row r="78" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B78" t="s">
         <v>73</v>
@@ -5732,7 +5732,7 @@
         <v>137</v>
       </c>
       <c r="F78" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="H78">
         <v>6</v>
@@ -5753,7 +5753,7 @@
     </row>
     <row r="79" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B79" t="s">
         <v>74</v>
@@ -5768,7 +5768,7 @@
         <v>137</v>
       </c>
       <c r="F79" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="H79">
         <v>7</v>
@@ -5786,7 +5786,7 @@
     </row>
     <row r="80" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B80" t="s">
         <v>84</v>
@@ -5801,7 +5801,7 @@
         <v>137</v>
       </c>
       <c r="F80" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="H80">
         <v>8</v>
@@ -5819,7 +5819,7 @@
     </row>
     <row r="81" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B81" t="s">
         <v>92</v>
@@ -5855,7 +5855,7 @@
     </row>
     <row r="82" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B82" t="s">
         <v>178</v>
@@ -5870,7 +5870,7 @@
         <v>179</v>
       </c>
       <c r="F82" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="H82">
         <v>5</v>
@@ -5888,7 +5888,7 @@
     </row>
     <row r="83" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B83" t="s">
         <v>242</v>
@@ -5903,7 +5903,7 @@
         <v>237</v>
       </c>
       <c r="F83" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="H83">
         <v>3</v>
@@ -5924,7 +5924,7 @@
     </row>
     <row r="84" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B84" t="s">
         <v>238</v>
@@ -5939,7 +5939,7 @@
         <v>237</v>
       </c>
       <c r="F84" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="H84">
         <v>3</v>
@@ -5960,7 +5960,7 @@
     </row>
     <row r="85" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B85" t="s">
         <v>239</v>
@@ -5975,7 +5975,7 @@
         <v>237</v>
       </c>
       <c r="F85" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="H85">
         <v>8</v>
@@ -5993,7 +5993,7 @@
     </row>
     <row r="86" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B86" t="s">
         <v>240</v>
@@ -6008,7 +6008,7 @@
         <v>237</v>
       </c>
       <c r="F86" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="H86">
         <v>5</v>
@@ -6029,7 +6029,7 @@
     </row>
     <row r="87" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B87" t="s">
         <v>224</v>
@@ -6044,7 +6044,7 @@
         <v>225</v>
       </c>
       <c r="F87" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G87" t="s">
         <v>82</v>
@@ -6068,7 +6068,7 @@
     </row>
     <row r="88" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B88" t="s">
         <v>226</v>
@@ -6083,10 +6083,10 @@
         <v>135</v>
       </c>
       <c r="F88" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="G88" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="H88">
         <v>-9</v>
@@ -6104,7 +6104,7 @@
     </row>
     <row r="89" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B89" t="s">
         <v>129</v>
@@ -6119,7 +6119,7 @@
         <v>135</v>
       </c>
       <c r="F89" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="G89" t="s">
         <v>82</v>
@@ -6143,7 +6143,7 @@
     </row>
     <row r="90" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B90" t="s">
         <v>154</v>
@@ -6158,10 +6158,10 @@
         <v>135</v>
       </c>
       <c r="F90" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="G90" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="H90">
         <v>-12</v>
@@ -6182,7 +6182,7 @@
     </row>
     <row r="91" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B91" t="s">
         <v>155</v>
@@ -6197,10 +6197,10 @@
         <v>135</v>
       </c>
       <c r="F91" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="G91" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="H91">
         <v>-12</v>
@@ -6221,10 +6221,10 @@
     </row>
     <row r="92" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B92" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C92">
         <v>1</v>
@@ -6236,7 +6236,7 @@
         <v>218</v>
       </c>
       <c r="F92" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="G92" t="s">
         <v>61</v>
@@ -6260,7 +6260,7 @@
     </row>
     <row r="93" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B93" t="s">
         <v>227</v>
@@ -6275,10 +6275,10 @@
         <v>225</v>
       </c>
       <c r="F93" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="G93" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="H93">
         <v>-12</v>
@@ -6296,7 +6296,7 @@
     </row>
     <row r="94" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B94" t="s">
         <v>229</v>
@@ -6311,7 +6311,7 @@
         <v>225</v>
       </c>
       <c r="F94" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="G94" t="s">
         <v>230</v>
@@ -6338,7 +6338,7 @@
     </row>
     <row r="95" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B95" t="s">
         <v>88</v>
@@ -6353,7 +6353,7 @@
         <v>166</v>
       </c>
       <c r="F95" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="H95">
         <v>1</v>
@@ -6374,7 +6374,7 @@
     </row>
     <row r="96" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B96" t="s">
         <v>89</v>
@@ -6389,7 +6389,7 @@
         <v>166</v>
       </c>
       <c r="F96" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="H96">
         <v>0</v>
@@ -6413,7 +6413,7 @@
     </row>
     <row r="97" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B97" t="s">
         <v>91</v>
@@ -6428,7 +6428,7 @@
         <v>166</v>
       </c>
       <c r="F97" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="H97">
         <v>1</v>
@@ -6452,7 +6452,7 @@
     </row>
     <row r="98" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B98" t="s">
         <v>101</v>
@@ -6467,7 +6467,7 @@
         <v>166</v>
       </c>
       <c r="F98" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="H98">
         <v>0</v>
@@ -6491,22 +6491,22 @@
     </row>
     <row r="99" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B99" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C99">
         <v>0</v>
       </c>
       <c r="D99" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E99" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F99" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="H99">
         <v>3</v>
@@ -6527,10 +6527,10 @@
     </row>
     <row r="100" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B100" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -6542,7 +6542,7 @@
         <v>281</v>
       </c>
       <c r="F100" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="H100">
         <v>1</v>
@@ -6563,22 +6563,22 @@
     </row>
     <row r="101" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B101" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C101">
         <v>0</v>
       </c>
       <c r="D101" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E101" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F101" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="H101">
         <v>0</v>
@@ -6598,7 +6598,7 @@
     </row>
     <row r="102" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B102" t="s">
         <v>265</v>
@@ -6613,7 +6613,7 @@
         <v>264</v>
       </c>
       <c r="F102" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="H102">
         <v>2</v>
@@ -6637,7 +6637,7 @@
     </row>
     <row r="103" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B103" t="s">
         <v>266</v>
@@ -6676,7 +6676,7 @@
     </row>
     <row r="104" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B104" t="s">
         <v>95</v>
@@ -6691,7 +6691,7 @@
         <v>141</v>
       </c>
       <c r="F104" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="H104">
         <v>0</v>
@@ -6709,7 +6709,7 @@
     </row>
     <row r="105" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B105" t="s">
         <v>156</v>
@@ -6724,7 +6724,7 @@
         <v>141</v>
       </c>
       <c r="F105" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="H105">
         <v>0</v>
@@ -6742,7 +6742,7 @@
     </row>
     <row r="106" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B106" t="s">
         <v>157</v>
@@ -6751,13 +6751,13 @@
         <v>1</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E106" t="s">
         <v>133</v>
       </c>
       <c r="F106" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="H106">
         <v>3</v>
@@ -6775,7 +6775,7 @@
     </row>
     <row r="107" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B107" t="s">
         <v>148</v>
@@ -6790,7 +6790,7 @@
         <v>138</v>
       </c>
       <c r="F107" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="H107">
         <v>0</v>
@@ -6811,7 +6811,7 @@
     </row>
     <row r="108" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B108" t="s">
         <v>149</v>
@@ -6826,7 +6826,7 @@
         <v>138</v>
       </c>
       <c r="F108" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="H108">
         <v>5</v>
@@ -6847,7 +6847,7 @@
     </row>
     <row r="109" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B109" t="s">
         <v>246</v>
@@ -6862,7 +6862,7 @@
         <v>245</v>
       </c>
       <c r="F109" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="H109">
         <v>0</v>
@@ -6883,7 +6883,7 @@
     </row>
     <row r="110" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B110" t="s">
         <v>247</v>
@@ -6898,7 +6898,7 @@
         <v>245</v>
       </c>
       <c r="F110" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="H110">
         <v>6</v>
@@ -6919,7 +6919,7 @@
     </row>
     <row r="111" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B111" t="s">
         <v>244</v>
@@ -6934,7 +6934,7 @@
         <v>175</v>
       </c>
       <c r="F111" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="H111">
         <v>6</v>
@@ -6952,7 +6952,7 @@
     </row>
     <row r="112" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B112" t="s">
         <v>168</v>
@@ -6985,10 +6985,10 @@
     </row>
     <row r="113" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B113" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -7018,7 +7018,7 @@
     </row>
     <row r="114" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B114" t="s">
         <v>173</v>
@@ -7033,7 +7033,7 @@
         <v>170</v>
       </c>
       <c r="F114" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="H114">
         <v>1</v>
@@ -7054,7 +7054,7 @@
     </row>
     <row r="115" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B115" t="s">
         <v>174</v>
@@ -7069,7 +7069,7 @@
         <v>170</v>
       </c>
       <c r="F115" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="H115">
         <v>1</v>
@@ -7087,7 +7087,7 @@
     </row>
     <row r="116" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B116" t="s">
         <v>250</v>
@@ -7102,7 +7102,7 @@
         <v>176</v>
       </c>
       <c r="F116" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="H116">
         <v>3</v>
@@ -7120,7 +7120,7 @@
     </row>
     <row r="117" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B117" t="s">
         <v>180</v>
@@ -7135,7 +7135,7 @@
         <v>176</v>
       </c>
       <c r="F117" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="H117">
         <v>3</v>
@@ -7156,7 +7156,7 @@
     </row>
     <row r="118" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B118" t="s">
         <v>249</v>
@@ -7171,7 +7171,7 @@
         <v>133</v>
       </c>
       <c r="F118" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="H118">
         <v>1</v>
@@ -7189,7 +7189,7 @@
     </row>
     <row r="119" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B119" t="s">
         <v>199</v>
@@ -7204,7 +7204,7 @@
         <v>198</v>
       </c>
       <c r="F119" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="H119">
         <v>3</v>
@@ -7222,7 +7222,7 @@
     </row>
     <row r="120" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B120" t="s">
         <v>202</v>
@@ -7237,7 +7237,7 @@
         <v>204</v>
       </c>
       <c r="F120" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="G120" t="s">
         <v>61</v>
@@ -7258,7 +7258,7 @@
     </row>
     <row r="121" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B121" t="s">
         <v>205</v>
@@ -7273,7 +7273,7 @@
         <v>204</v>
       </c>
       <c r="F121" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="G121" t="s">
         <v>61</v>
@@ -7294,10 +7294,10 @@
     </row>
     <row r="122" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B122" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C122">
         <v>3</v>
@@ -7309,10 +7309,10 @@
         <v>134</v>
       </c>
       <c r="F122" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="G122" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="H122">
         <v>-12</v>
@@ -7333,7 +7333,7 @@
     </row>
     <row r="123" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B123" t="s">
         <v>207</v>
@@ -7348,7 +7348,7 @@
         <v>204</v>
       </c>
       <c r="F123" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="G123" t="s">
         <v>206</v>
@@ -7369,10 +7369,10 @@
     </row>
     <row r="124" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B124" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="C124">
         <v>3</v>
@@ -7384,10 +7384,10 @@
         <v>134</v>
       </c>
       <c r="F124" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="G124" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H124">
         <v>-9</v>
@@ -7405,7 +7405,7 @@
     </row>
     <row r="125" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B125" t="s">
         <v>219</v>
@@ -7420,7 +7420,7 @@
         <v>221</v>
       </c>
       <c r="F125" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="G125" t="s">
         <v>61</v>
@@ -7441,7 +7441,7 @@
     </row>
     <row r="126" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A126" s="4" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="B126" t="s">
         <v>87</v>
@@ -7456,10 +7456,10 @@
         <v>136</v>
       </c>
       <c r="F126" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="G126" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="H126">
         <v>-6</v>
@@ -7477,10 +7477,10 @@
     </row>
     <row r="127" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B127" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C127">
         <v>2</v>
@@ -7492,7 +7492,7 @@
         <v>231</v>
       </c>
       <c r="F127" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="G127" t="s">
         <v>206</v>
@@ -7513,7 +7513,7 @@
     </row>
     <row r="128" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B128" t="s">
         <v>232</v>
@@ -7528,7 +7528,7 @@
         <v>231</v>
       </c>
       <c r="F128" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="G128" t="s">
         <v>228</v>
@@ -7549,25 +7549,25 @@
     </row>
     <row r="129" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B129" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="C129">
         <v>2</v>
       </c>
       <c r="D129" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E129" t="s">
         <v>136</v>
       </c>
       <c r="F129" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="G129" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="H129">
         <v>-9</v>
@@ -7581,10 +7581,10 @@
     </row>
     <row r="130" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B130" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="C130">
         <v>3</v>
@@ -7596,10 +7596,10 @@
         <v>134</v>
       </c>
       <c r="F130" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="G130" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="H130">
         <v>-9</v>
@@ -7617,7 +7617,7 @@
     </row>
     <row r="131" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B131" t="s">
         <v>235</v>
@@ -7632,7 +7632,7 @@
         <v>231</v>
       </c>
       <c r="F131" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="G131" t="s">
         <v>206</v>
@@ -7653,7 +7653,7 @@
     </row>
     <row r="132" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B132" t="s">
         <v>80</v>
@@ -7668,7 +7668,7 @@
         <v>136</v>
       </c>
       <c r="F132" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="G132" t="s">
         <v>228</v>
@@ -7689,7 +7689,7 @@
     </row>
     <row r="133" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B133" t="s">
         <v>158</v>
@@ -7704,7 +7704,7 @@
         <v>139</v>
       </c>
       <c r="F133" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="H133">
         <v>1</v>
@@ -7722,10 +7722,10 @@
     </row>
     <row r="134" spans="1:34" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B134" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C134">
         <v>3</v>
@@ -7737,7 +7737,7 @@
         <v>241</v>
       </c>
       <c r="F134" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="H134">
         <v>0</v>
@@ -7758,7 +7758,7 @@
     </row>
     <row r="135" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B135" t="s">
         <v>243</v>
@@ -7773,7 +7773,7 @@
         <v>241</v>
       </c>
       <c r="F135" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="H135">
         <v>0</v>
@@ -7794,7 +7794,7 @@
     </row>
     <row r="136" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B136" t="s">
         <v>248</v>
@@ -7809,7 +7809,7 @@
         <v>241</v>
       </c>
       <c r="F136" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="H136">
         <v>12</v>
@@ -7827,7 +7827,7 @@
     </row>
     <row r="137" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B137" t="s">
         <v>251</v>
@@ -7842,7 +7842,7 @@
         <v>241</v>
       </c>
       <c r="F137" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="H137">
         <v>0</v>
@@ -7860,7 +7860,7 @@
     </row>
     <row r="138" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B138" t="s">
         <v>252</v>
@@ -7875,7 +7875,7 @@
         <v>241</v>
       </c>
       <c r="F138" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="H138">
         <v>10</v>
@@ -7893,7 +7893,7 @@
     </row>
     <row r="139" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B139" t="s">
         <v>253</v>
@@ -7926,7 +7926,7 @@
     </row>
     <row r="140" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A140" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B140" t="s">
         <v>255</v>
@@ -7959,7 +7959,7 @@
     </row>
     <row r="141" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B141" t="s">
         <v>257</v>
@@ -7974,7 +7974,7 @@
         <v>241</v>
       </c>
       <c r="F141" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="H141">
         <v>8</v>
@@ -7992,7 +7992,7 @@
     </row>
     <row r="142" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B142" t="s">
         <v>258</v>
@@ -8007,7 +8007,7 @@
         <v>241</v>
       </c>
       <c r="F142" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="H142">
         <v>0</v>
@@ -8031,7 +8031,7 @@
     </row>
     <row r="143" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B143" t="s">
         <v>259</v>
@@ -8046,7 +8046,7 @@
         <v>241</v>
       </c>
       <c r="F143" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="H143">
         <v>0</v>
@@ -8064,7 +8064,7 @@
     </row>
     <row r="144" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A144" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B144" t="s">
         <v>272</v>
@@ -8079,7 +8079,7 @@
         <v>273</v>
       </c>
       <c r="F144" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="H144">
         <v>1</v>
@@ -8097,7 +8097,7 @@
     </row>
     <row r="145" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B145" t="s">
         <v>262</v>
@@ -8112,7 +8112,7 @@
         <v>273</v>
       </c>
       <c r="F145" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="H145">
         <v>0</v>
@@ -8133,7 +8133,7 @@
     </row>
     <row r="146" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A146" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B146" t="s">
         <v>274</v>
@@ -8148,7 +8148,7 @@
         <v>273</v>
       </c>
       <c r="F146" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="H146">
         <v>0</v>
@@ -8166,7 +8166,7 @@
     </row>
     <row r="147" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B147" t="s">
         <v>275</v>
@@ -8181,7 +8181,7 @@
         <v>273</v>
       </c>
       <c r="F147" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="H147">
         <v>0</v>
@@ -8199,7 +8199,7 @@
     </row>
     <row r="148" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B148" t="s">
         <v>279</v>
@@ -8214,7 +8214,7 @@
         <v>278</v>
       </c>
       <c r="F148" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="H148">
         <v>0</v>
@@ -8238,10 +8238,10 @@
     </row>
     <row r="149" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B149" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C149">
         <v>3</v>
@@ -8253,7 +8253,7 @@
         <v>278</v>
       </c>
       <c r="F149" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="H149">
         <v>0</v>
@@ -8271,10 +8271,10 @@
     </row>
     <row r="150" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A150" s="4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B150" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="C150">
         <v>1</v>
@@ -8286,7 +8286,7 @@
         <v>278</v>
       </c>
       <c r="F150" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="H150">
         <v>0</v>
@@ -8304,7 +8304,7 @@
     </row>
     <row r="151" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A151" s="4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B151" t="s">
         <v>280</v>
@@ -8319,7 +8319,7 @@
         <v>278</v>
       </c>
       <c r="F151" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="H151">
         <v>0</v>
@@ -8343,22 +8343,22 @@
     </row>
     <row r="152" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A152" s="4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B152" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C152">
         <v>3</v>
       </c>
       <c r="D152" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E152" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F152" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="H152">
         <v>0</v>
@@ -8567,7 +8567,7 @@
         <v>136</v>
       </c>
       <c r="F4" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G4" t="s">
         <v>82</v>
@@ -8603,7 +8603,7 @@
         <v>278</v>
       </c>
       <c r="F5" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -8618,7 +8618,7 @@
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B6" t="s">
         <v>224</v>
@@ -8633,7 +8633,7 @@
         <v>135</v>
       </c>
       <c r="F6" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G6" t="s">
         <v>63</v>
@@ -8657,7 +8657,7 @@
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B7" t="s">
         <v>260</v>
@@ -8672,7 +8672,7 @@
         <v>261</v>
       </c>
       <c r="F7" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -8693,7 +8693,7 @@
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B8" t="s">
         <v>282</v>
@@ -8708,7 +8708,7 @@
         <v>166</v>
       </c>
       <c r="F8" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -8726,7 +8726,7 @@
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B9" t="s">
         <v>249</v>
@@ -8741,7 +8741,7 @@
         <v>165</v>
       </c>
       <c r="F9" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H9">
         <v>2</v>
@@ -8809,18 +8809,18 @@
         <v>110</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C13" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D13" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B15" t="s">
         <v>223</v>
@@ -8835,7 +8835,7 @@
         <v>221</v>
       </c>
       <c r="F15" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="G15" t="s">
         <v>61</v>
@@ -8856,7 +8856,7 @@
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B16" t="s">
         <v>54</v>
@@ -8871,7 +8871,7 @@
         <v>136</v>
       </c>
       <c r="F16" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G16" t="s">
         <v>20</v>
@@ -8898,7 +8898,7 @@
     </row>
     <row r="17" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B17" t="s">
         <v>234</v>
@@ -8913,7 +8913,7 @@
         <v>231</v>
       </c>
       <c r="F17" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="G17" t="s">
         <v>206</v>
@@ -8940,10 +8940,10 @@
     </row>
     <row r="18" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B18" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -8988,10 +8988,10 @@
         <v>136</v>
       </c>
       <c r="F19" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="G19" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="H19">
         <v>2</v>
@@ -9048,7 +9048,7 @@
         <v>124</v>
       </c>
       <c r="C2" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="D2" t="s">
         <v>108</v>
@@ -9059,10 +9059,10 @@
         <v>111</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C3" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="D3" t="s">
         <v>112</v>
@@ -9073,10 +9073,10 @@
         <v>113</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C4" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="D4" t="s">
         <v>114</v>
@@ -9090,7 +9090,7 @@
         <v>124</v>
       </c>
       <c r="C5" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="D5" t="s">
         <v>116</v>
@@ -9101,10 +9101,10 @@
         <v>120</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C6" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="D6" t="s">
         <v>121</v>
@@ -9115,10 +9115,10 @@
         <v>122</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C7" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="D7" t="s">
         <v>123</v>
@@ -9126,16 +9126,16 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C8" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D8" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -9143,13 +9143,13 @@
         <v>109</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C9" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="D9" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -9157,27 +9157,27 @@
         <v>109</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C10" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="D10" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>339</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C11" t="s">
         <v>341</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="D11" t="s">
         <v>342</v>
-      </c>
-      <c r="C11" t="s">
-        <v>343</v>
-      </c>
-      <c r="D11" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -9188,10 +9188,10 @@
         <v>124</v>
       </c>
       <c r="C12" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="D12" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -9199,13 +9199,13 @@
         <v>125</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C13" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D13" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -9213,13 +9213,13 @@
         <v>127</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C14" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D14" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -9227,41 +9227,41 @@
         <v>128</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C15" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D15" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C16" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D16" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>383</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C17" t="s">
+        <v>386</v>
+      </c>
+      <c r="D17" t="s">
         <v>385</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="C17" t="s">
-        <v>388</v>
-      </c>
-      <c r="D17" t="s">
-        <v>387</v>
       </c>
     </row>
   </sheetData>
@@ -9322,7 +9322,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E2" t="s">
         <v>184</v>
@@ -9432,7 +9432,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="B6">
         <v>1</v>

--- a/card_design.xlsx
+++ b/card_design.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\life\board_game\project_six_dynasty\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D406DC93-0F2B-4478-A71E-B51D7DC4B038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B84494A2-0963-4EA5-95BC-0359BDDBCFFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="811" xr2:uid="{F283CFD4-9FFB-4A79-AF0F-7443CC209F7A}"/>
   </bookViews>
@@ -17,11 +17,13 @@
     <sheet name="后备" sheetId="4" r:id="rId2"/>
     <sheet name="目标牌" sheetId="2" r:id="rId3"/>
     <sheet name="君主牌" sheetId="3" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">卡牌设计!$A$1:$AJ$152</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -8579,7 +8581,7 @@
         <v>1</v>
       </c>
       <c r="P4">
-        <f t="shared" ref="P4" si="0">SUM(Q4:AE4)</f>
+        <f>SUM(Q4:AE4)</f>
         <v>1</v>
       </c>
       <c r="W4">
@@ -8964,7 +8966,7 @@
         <v>1</v>
       </c>
       <c r="P18">
-        <f t="shared" ref="P18:P19" si="1">SUM(Q18:AE18)</f>
+        <f>SUM(Q18:AE18)</f>
         <v>1</v>
       </c>
       <c r="R18">
@@ -9003,7 +9005,7 @@
         <v>1</v>
       </c>
       <c r="P19">
-        <f t="shared" si="1"/>
+        <f>SUM(Q19:AE19)</f>
         <v>1</v>
       </c>
       <c r="W19">
@@ -9463,4 +9465,14 @@
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D71AA02-D86F-4E87-93A0-310458B0B3FB}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>